--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -2,19 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C6B80F4-0D5F-454C-BDB8-782F73EE8765}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$321</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -56,7 +59,10 @@
     <t>RC</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>Novo Pedido</t>
+  </si>
+  <si>
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -64,10 +70,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Novo Pedido</t>
-  </si>
-  <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -75,7 +78,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.836,48_x000D_
@@ -83,7 +86,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -91,7 +94,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.744,32_x000D_
@@ -99,7 +102,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 34.772,49_x000D_
@@ -107,7 +110,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.169,40_x000D_
@@ -115,7 +118,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -123,7 +126,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.472,17_x000D_
@@ -131,7 +134,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 19.609,92_x000D_
@@ -139,7 +142,7 @@
 • Valor mínimo de frete: R$ 9.225,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.458,80_x000D_
@@ -147,7 +150,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -155,7 +158,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.959,16_x000D_
@@ -163,7 +166,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -171,7 +174,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -179,7 +182,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 565,76_x000D_
@@ -187,7 +190,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -195,7 +198,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -203,7 +206,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -211,7 +214,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -219,7 +222,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -227,7 +230,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.203,35_x000D_
@@ -235,7 +238,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.271,67_x000D_
@@ -243,7 +246,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 40.883,52_x000D_
@@ -251,7 +254,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 14.595,14_x000D_
@@ -259,7 +262,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.968,87_x000D_
@@ -267,7 +270,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -275,7 +278,7 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.681,80_x000D_
@@ -283,7 +286,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 33.862,88_x000D_
@@ -291,7 +294,7 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 614,20_x000D_
@@ -299,7 +302,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.125,75_x000D_
@@ -307,7 +310,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.321,68_x000D_
@@ -315,7 +318,7 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.341,80_x000D_
@@ -323,7 +326,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.026,08_x000D_
@@ -331,7 +334,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.205,40_x000D_
@@ -339,7 +342,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -347,7 +350,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.314,64_x000D_
@@ -355,7 +358,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.281,24_x000D_
@@ -363,7 +366,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.340,96_x000D_
@@ -371,7 +374,7 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.085,43_x000D_
@@ -379,7 +382,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.101,16_x000D_
@@ -387,7 +390,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.286,32_x000D_
@@ -395,7 +398,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.315,68_x000D_
@@ -403,7 +406,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.366,32_x000D_
@@ -411,7 +414,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.006,90_x000D_
@@ -419,7 +422,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 14.206,96_x000D_
@@ -427,7 +430,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.853,32_x000D_
@@ -435,7 +438,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 48.513,56_x000D_
@@ -443,7 +446,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.901,28_x000D_
@@ -451,7 +454,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.218,74_x000D_
@@ -459,7 +462,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.699,88_x000D_
@@ -467,7 +470,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.750,00_x000D_
@@ -475,7 +478,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -483,7 +486,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.404,30_x000D_
@@ -491,7 +494,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.238,16_x000D_
@@ -499,7 +502,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.262,92_x000D_
@@ -507,7 +510,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.335,96_x000D_
@@ -515,7 +518,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.530,76_x000D_
@@ -523,7 +526,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.829,48_x000D_
@@ -531,7 +534,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.488,42_x000D_
@@ -539,7 +542,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.500,84_x000D_
@@ -547,7 +550,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.535,36_x000D_
@@ -555,7 +558,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.379,50_x000D_
@@ -563,7 +566,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.049,19_x000D_
@@ -571,7 +574,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.525,96_x000D_
@@ -579,7 +582,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.756,60_x000D_
@@ -587,7 +590,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 160,56_x000D_
@@ -595,7 +598,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.608,31_x000D_
@@ -603,7 +606,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.263,31_x000D_
@@ -611,7 +614,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.618,84_x000D_
@@ -619,7 +622,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.471,04_x000D_
@@ -627,7 +630,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -635,7 +638,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.396,00_x000D_
@@ -643,7 +646,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 17.660,39_x000D_
@@ -651,7 +654,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.411,03_x000D_
@@ -659,7 +662,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.106,23_x000D_
@@ -667,7 +670,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.384,80_x000D_
@@ -675,7 +678,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.987,14_x000D_
@@ -683,7 +686,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.242,24_x000D_
@@ -691,7 +694,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.131,12_x000D_
@@ -699,7 +702,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.058,56_x000D_
@@ -707,7 +710,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.023,68_x000D_
@@ -715,7 +718,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 20.336,10_x000D_
@@ -723,7 +726,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 10.023,90_x000D_
@@ -731,7 +734,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 25.657,14_x000D_
@@ -739,7 +742,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.504,84_x000D_
@@ -747,7 +750,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.894,24_x000D_
@@ -755,7 +758,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.353,24_x000D_
@@ -763,7 +766,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.453,40_x000D_
@@ -771,7 +774,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.680,48_x000D_
@@ -779,7 +782,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.906,80_x000D_
@@ -787,7 +790,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.967,56_x000D_
@@ -795,7 +798,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.275,20_x000D_
@@ -803,7 +806,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 898,56_x000D_
@@ -811,7 +814,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.912,32_x000D_
@@ -819,7 +822,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.744,14_x000D_
@@ -827,7 +830,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 12.648,84_x000D_
@@ -835,7 +838,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 8.302,32_x000D_
@@ -843,7 +846,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.270,08_x000D_
@@ -851,7 +854,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.191,68_x000D_
@@ -859,7 +862,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.372,76_x000D_
@@ -867,7 +870,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 897,36_x000D_
@@ -875,7 +878,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.656,80_x000D_
@@ -883,7 +886,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.594,08_x000D_
@@ -891,7 +894,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.780,83_x000D_
@@ -899,7 +902,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.920,32_x000D_
@@ -907,7 +910,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 12.480,75_x000D_
@@ -915,7 +918,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.038,10_x000D_
@@ -923,7 +926,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.299,38_x000D_
@@ -931,7 +934,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.391,04_x000D_
@@ -939,7 +942,7 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.885,68_x000D_
@@ -947,7 +950,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 253,80_x000D_
@@ -955,7 +958,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 19.020,56_x000D_
@@ -963,7 +966,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.642,32_x000D_
@@ -971,7 +974,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -979,7 +982,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.646,32_x000D_
@@ -987,7 +990,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.699,36_x000D_
@@ -995,7 +998,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1003,7 +1006,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1011,7 +1014,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1019,7 +1022,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.206,40_x000D_
@@ -1027,7 +1030,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1035,7 +1038,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.617,23_x000D_
@@ -1043,7 +1046,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.942,92_x000D_
@@ -1051,7 +1054,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.245,32_x000D_
@@ -1059,7 +1062,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 664,32_x000D_
@@ -1067,7 +1070,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 748,44_x000D_
@@ -1075,7 +1078,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 602,28_x000D_
@@ -1083,7 +1086,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 997,92_x000D_
@@ -1091,7 +1094,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.885,64_x000D_
@@ -1099,7 +1102,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.110,60_x000D_
@@ -1107,7 +1110,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.824,68_x000D_
@@ -1115,7 +1118,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.917,50_x000D_
@@ -1123,7 +1126,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.899,60_x000D_
@@ -1131,7 +1134,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 489,60_x000D_
@@ -1139,7 +1142,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.714,80_x000D_
@@ -1147,7 +1150,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.785,28_x000D_
@@ -1155,7 +1158,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1163,7 +1166,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 545,83_x000D_
@@ -1171,7 +1174,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.546,86_x000D_
@@ -1179,7 +1182,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.142,20_x000D_
@@ -1187,7 +1190,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 23.514,08_x000D_
@@ -1195,7 +1198,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.155,76_x000D_
@@ -1203,7 +1206,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1211,7 +1214,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.408,12_x000D_
@@ -1219,7 +1222,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.328,40_x000D_
@@ -1227,7 +1230,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.985,20_x000D_
@@ -1235,7 +1238,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.692,63_x000D_
@@ -1243,7 +1246,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.287,16_x000D_
@@ -1251,7 +1254,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.155,12_x000D_
@@ -1259,7 +1262,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.856,60_x000D_
@@ -1267,7 +1270,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.071,00_x000D_
@@ -1275,7 +1278,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.037,60_x000D_
@@ -1283,7 +1286,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 20.667,04_x000D_
@@ -1291,7 +1294,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.100,22_x000D_
@@ -1299,7 +1302,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.001,76_x000D_
@@ -1307,7 +1310,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1315,7 +1318,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 8.131,70_x000D_
@@ -1323,7 +1326,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.549,40_x000D_
@@ -1331,7 +1334,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.308,00_x000D_
@@ -1339,7 +1342,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.865,91_x000D_
@@ -1347,7 +1350,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.576,07_x000D_
@@ -1355,7 +1358,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.824,99_x000D_
@@ -1363,7 +1366,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.405,75_x000D_
@@ -1371,7 +1374,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.121,84_x000D_
@@ -1379,7 +1382,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.897,60_x000D_
@@ -1387,7 +1390,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1395,7 +1398,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.048,82_x000D_
@@ -1403,7 +1406,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 855,00_x000D_
@@ -1411,7 +1414,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 14.460,84_x000D_
@@ -1419,7 +1422,7 @@
 • Valor mínimo de frete: R$ 1.000,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 26.917,60_x000D_
@@ -1427,7 +1430,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 16.243,92_x000D_
@@ -1435,7 +1438,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.773,60_x000D_
@@ -1443,7 +1446,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.180,00_x000D_
@@ -1451,7 +1454,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 42.930,66_x000D_
@@ -1459,7 +1462,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 87.162,00_x000D_
@@ -1467,7 +1470,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1475,7 +1478,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.348,26_x000D_
@@ -1483,7 +1486,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1491,7 +1494,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 10.110,96_x000D_
@@ -1499,7 +1502,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.171,20_x000D_
@@ -1507,7 +1510,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 40.038,24_x000D_
@@ -1515,7 +1518,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.627,60_x000D_
@@ -1523,7 +1526,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 158.644,56_x000D_
@@ -1531,7 +1534,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 876,96_x000D_
@@ -1539,7 +1542,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1547,7 +1550,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1555,7 +1558,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.091,38_x000D_
@@ -1563,7 +1566,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 66.655,03_x000D_
@@ -1571,7 +1574,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.729,76_x000D_
@@ -1579,7 +1582,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 821,52_x000D_
@@ -1587,7 +1590,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.089,20_x000D_
@@ -1595,7 +1598,7 @@
 • Valor mínimo de frete: R$ 50,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1603,7 +1606,7 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 8.190,00_x000D_
@@ -1611,7 +1614,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.624,40_x000D_
@@ -1619,7 +1622,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1627,7 +1630,7 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 38.125,50_x000D_
@@ -1635,7 +1638,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.198,80_x000D_
@@ -1643,7 +1646,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 23.246,08_x000D_
@@ -1651,7 +1654,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.467,28_x000D_
@@ -1659,7 +1662,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.718,00_x000D_
@@ -1667,7 +1670,7 @@
 • Valor mínimo de frete: R$ 7.175,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.078,00_x000D_
@@ -1675,7 +1678,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.872,64_x000D_
@@ -1683,7 +1686,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.146,24_x000D_
@@ -1691,7 +1694,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.289,60_x000D_
@@ -1699,7 +1702,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 32.209,90_x000D_
@@ -1707,7 +1710,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.130,50_x000D_
@@ -1715,7 +1718,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.613,60_x000D_
@@ -1723,7 +1726,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1731,7 +1734,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.231,94_x000D_
@@ -1739,7 +1742,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.093,12_x000D_
@@ -1747,7 +1750,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.011,84_x000D_
@@ -1755,7 +1758,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 961,50_x000D_
@@ -1763,7 +1766,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 437,12_x000D_
@@ -1771,7 +1774,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.739,42_x000D_
@@ -1779,7 +1782,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.291,36_x000D_
@@ -1787,7 +1790,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.249,64_x000D_
@@ -1795,7 +1798,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 262,56_x000D_
@@ -1803,7 +1806,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.520,14_x000D_
@@ -1811,7 +1814,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.326,88_x000D_
@@ -1819,7 +1822,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.163,20_x000D_
@@ -1827,7 +1830,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.817,48_x000D_
@@ -1835,7 +1838,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1843,7 +1846,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.949,76_x000D_
@@ -1851,7 +1854,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.995,52_x000D_
@@ -1859,7 +1862,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.017,30_x000D_
@@ -1867,7 +1870,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.021,02_x000D_
@@ -1875,7 +1878,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.587,74_x000D_
@@ -1883,7 +1886,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1891,7 +1894,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.969,68_x000D_
@@ -1899,7 +1902,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.910,68_x000D_
@@ -1907,7 +1910,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.875,00_x000D_
@@ -1915,7 +1918,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.801,48_x000D_
@@ -1923,7 +1926,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1931,7 +1934,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 890,64_x000D_
@@ -1939,7 +1942,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.155,20_x000D_
@@ -1947,7 +1950,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.424,50_x000D_
@@ -1955,7 +1958,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.016,00_x000D_
@@ -1963,7 +1966,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.971,52_x000D_
@@ -1971,7 +1974,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -1979,7 +1982,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.541,60_x000D_
@@ -1987,7 +1990,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 871,56_x000D_
@@ -1995,7 +1998,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.143,12_x000D_
@@ -2003,7 +2006,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.468,88_x000D_
@@ -2011,7 +2014,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 986,76_x000D_
@@ -2019,7 +2022,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2027,7 +2030,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2035,7 +2038,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2043,7 +2046,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2051,7 +2054,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2059,7 +2062,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2067,7 +2070,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2075,7 +2078,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2083,7 +2086,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2091,7 +2094,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2099,7 +2102,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2107,7 +2110,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.954,01_x000D_
@@ -2115,7 +2118,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2123,7 +2126,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2131,7 +2134,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 360,30_x000D_
@@ -2139,7 +2142,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 924,00_x000D_
@@ -2147,7 +2150,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2155,7 +2158,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.228,48_x000D_
@@ -2163,7 +2166,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.872,00_x000D_
@@ -2171,7 +2174,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.645,60_x000D_
@@ -2179,7 +2182,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2187,7 +2190,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2195,7 +2198,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.362,98_x000D_
@@ -2203,7 +2206,7 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2211,7 +2214,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2219,7 +2222,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.342,38_x000D_
@@ -2227,7 +2230,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2235,7 +2238,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2243,7 +2246,7 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2251,7 +2254,7 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2259,7 +2262,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2267,7 +2270,7 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2275,7 +2278,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 19.572,11_x000D_
@@ -2283,7 +2286,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2291,7 +2294,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2299,7 +2302,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2307,7 +2310,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial e cancelar saldo?_x000D_
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.077,96_x000D_
@@ -2315,7 +2318,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.946,00_x000D_
@@ -2323,7 +2326,7 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2331,7 +2334,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2339,7 +2342,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2347,7 +2350,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2355,7 +2358,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.370,56_x000D_
@@ -2363,7 +2366,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 9.344,40_x000D_
@@ -2371,7 +2374,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.301,92_x000D_
@@ -2379,7 +2382,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2387,7 +2390,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Faturar parcial mantendo saldo?_x000D_
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.922,00_x000D_
@@ -2395,7 +2398,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2403,7 +2406,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2411,7 +2414,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2419,7 +2422,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2427,7 +2430,7 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2435,7 +2438,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2443,7 +2446,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2451,7 +2454,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2459,7 +2462,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2467,7 +2470,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2475,7 +2478,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2483,7 +2486,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2491,7 +2494,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2499,7 +2502,7 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2507,7 +2510,7 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2515,7 +2518,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2523,7 +2526,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar entrada dos itens em ruptura._x000D_
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2531,7 +2534,7 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Aguardar condições para faturamento._x000D_
+    <t>O pedido encontra-se abaixo do valor mínimo estabelecido para faturamento._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
@@ -2911,6 +2914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
+  <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:E321"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2942,10 +2946,10 @@
         <v>853850</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>773</v>
@@ -2959,13 +2963,13 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>773</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>853926</v>
       </c>
@@ -2973,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>773</v>
@@ -2987,7 +2991,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>773</v>
@@ -3001,13 +3005,13 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>853943</v>
       </c>
@@ -3015,13 +3019,13 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>773</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>853011</v>
       </c>
@@ -3029,7 +3033,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>409</v>
@@ -3043,13 +3047,13 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>1021</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>853567</v>
       </c>
@@ -3057,13 +3061,13 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>3060</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>854781</v>
       </c>
@@ -3071,7 +3075,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>3093</v>
@@ -3085,7 +3089,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>3075</v>
@@ -3099,7 +3103,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>3075</v>
@@ -3113,7 +3117,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>589</v>
@@ -3127,7 +3131,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>3058</v>
@@ -3141,7 +3145,7 @@
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>750</v>
@@ -3155,7 +3159,7 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>3089</v>
@@ -3169,7 +3173,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>1021</v>
@@ -3183,7 +3187,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>632</v>
@@ -3197,7 +3201,7 @@
         <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>3085</v>
@@ -3211,7 +3215,7 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>722</v>
@@ -3225,13 +3229,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>773</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>854237</v>
       </c>
@@ -3239,13 +3243,13 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>773</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>854330</v>
       </c>
@@ -3253,13 +3257,13 @@
         <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>854385</v>
       </c>
@@ -3267,13 +3271,13 @@
         <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>2090</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>853822</v>
       </c>
@@ -3281,13 +3285,13 @@
         <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>2084</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>854538</v>
       </c>
@@ -3295,7 +3299,7 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>1019</v>
@@ -3309,13 +3313,13 @@
         <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>2091</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>854594</v>
       </c>
@@ -3323,13 +3327,13 @@
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>2073</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>853694</v>
       </c>
@@ -3337,7 +3341,7 @@
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>3069</v>
@@ -3351,7 +3355,7 @@
         <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>3069</v>
@@ -3365,13 +3369,13 @@
         <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>2073</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>854225</v>
       </c>
@@ -3379,13 +3383,13 @@
         <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>3069</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>853956</v>
       </c>
@@ -3393,7 +3397,7 @@
         <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>614</v>
@@ -3407,7 +3411,7 @@
         <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>703</v>
@@ -3421,7 +3425,7 @@
         <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>642</v>
@@ -3435,13 +3439,13 @@
         <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>380</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>854578</v>
       </c>
@@ -3449,13 +3453,13 @@
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>948</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>854742</v>
       </c>
@@ -3463,13 +3467,13 @@
         <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>1021</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>854891</v>
       </c>
@@ -3477,13 +3481,13 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>2051</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>854080</v>
       </c>
@@ -3491,7 +3495,7 @@
         <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41">
         <v>580</v>
@@ -3505,7 +3509,7 @@
         <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>90</v>
@@ -3519,13 +3523,13 @@
         <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>614</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>854234</v>
       </c>
@@ -3533,13 +3537,13 @@
         <v>48</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>854016</v>
       </c>
@@ -3547,13 +3551,13 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>854678</v>
       </c>
@@ -3561,13 +3565,13 @@
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>1097</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>853816</v>
       </c>
@@ -3575,13 +3579,13 @@
         <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47">
         <v>880</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>853990</v>
       </c>
@@ -3589,13 +3593,13 @@
         <v>52</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48">
         <v>699</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>854747</v>
       </c>
@@ -3603,13 +3607,13 @@
         <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49">
         <v>388</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>854375</v>
       </c>
@@ -3617,7 +3621,7 @@
         <v>54</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50">
         <v>90</v>
@@ -3631,13 +3635,13 @@
         <v>55</v>
       </c>
       <c r="D51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E51">
         <v>3078</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>854534</v>
       </c>
@@ -3645,13 +3649,13 @@
         <v>56</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52">
         <v>3078</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>853813</v>
       </c>
@@ -3659,7 +3663,7 @@
         <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53">
         <v>90</v>
@@ -3673,13 +3677,13 @@
         <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E54">
         <v>614</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>853939</v>
       </c>
@@ -3687,13 +3691,13 @@
         <v>59</v>
       </c>
       <c r="D55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E55">
         <v>874</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>854669</v>
       </c>
@@ -3701,13 +3705,13 @@
         <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56">
         <v>614</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>854653</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>61</v>
       </c>
       <c r="D57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57">
         <v>614</v>
@@ -3729,7 +3733,7 @@
         <v>62</v>
       </c>
       <c r="D58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58">
         <v>134</v>
@@ -3743,7 +3747,7 @@
         <v>63</v>
       </c>
       <c r="D59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E59">
         <v>134</v>
@@ -3757,7 +3761,7 @@
         <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60">
         <v>134</v>
@@ -3771,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="D61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E61">
         <v>134</v>
@@ -3785,7 +3789,7 @@
         <v>66</v>
       </c>
       <c r="D62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62">
         <v>134</v>
@@ -3799,7 +3803,7 @@
         <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E63">
         <v>1097</v>
@@ -3813,7 +3817,7 @@
         <v>68</v>
       </c>
       <c r="D64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E64">
         <v>281</v>
@@ -3827,13 +3831,13 @@
         <v>69</v>
       </c>
       <c r="D65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65">
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>853715</v>
       </c>
@@ -3841,13 +3845,13 @@
         <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E66">
         <v>3092</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>853992</v>
       </c>
@@ -3855,7 +3859,7 @@
         <v>71</v>
       </c>
       <c r="D67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E67">
         <v>699</v>
@@ -3869,13 +3873,13 @@
         <v>72</v>
       </c>
       <c r="D68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E68">
         <v>2032</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>854691</v>
       </c>
@@ -3883,13 +3887,13 @@
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E69">
         <v>653</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>854773</v>
       </c>
@@ -3897,13 +3901,13 @@
         <v>74</v>
       </c>
       <c r="D70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70">
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>854812</v>
       </c>
@@ -3911,13 +3915,13 @@
         <v>75</v>
       </c>
       <c r="D71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E71">
         <v>664</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>854106</v>
       </c>
@@ -3925,7 +3929,7 @@
         <v>76</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E72">
         <v>580</v>
@@ -3939,13 +3943,13 @@
         <v>77</v>
       </c>
       <c r="D73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73">
         <v>377</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>853958</v>
       </c>
@@ -3953,13 +3957,13 @@
         <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E74">
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>854285</v>
       </c>
@@ -3967,7 +3971,7 @@
         <v>79</v>
       </c>
       <c r="D75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75">
         <v>737</v>
@@ -3981,7 +3985,7 @@
         <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E76">
         <v>737</v>
@@ -3995,7 +3999,7 @@
         <v>81</v>
       </c>
       <c r="D77" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E77">
         <v>737</v>
@@ -4009,7 +4013,7 @@
         <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E78">
         <v>3092</v>
@@ -4023,13 +4027,13 @@
         <v>83</v>
       </c>
       <c r="D79" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E79">
         <v>134</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>854632</v>
       </c>
@@ -4037,7 +4041,7 @@
         <v>84</v>
       </c>
       <c r="D80" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E80">
         <v>134</v>
@@ -4051,7 +4055,7 @@
         <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E81">
         <v>134</v>
@@ -4065,7 +4069,7 @@
         <v>86</v>
       </c>
       <c r="D82" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E82">
         <v>134</v>
@@ -4079,13 +4083,13 @@
         <v>87</v>
       </c>
       <c r="D83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E83">
         <v>134</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>854515</v>
       </c>
@@ -4093,13 +4097,13 @@
         <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E84">
         <v>593</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>854709</v>
       </c>
@@ -4107,13 +4111,13 @@
         <v>89</v>
       </c>
       <c r="D85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E85">
         <v>281</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>853770</v>
       </c>
@@ -4121,13 +4125,13 @@
         <v>90</v>
       </c>
       <c r="D86" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E86">
         <v>294</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>854693</v>
       </c>
@@ -4135,7 +4139,7 @@
         <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E87">
         <v>669</v>
@@ -4149,7 +4153,7 @@
         <v>92</v>
       </c>
       <c r="D88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88">
         <v>134</v>
@@ -4163,7 +4167,7 @@
         <v>93</v>
       </c>
       <c r="D89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89">
         <v>134</v>
@@ -4177,7 +4181,7 @@
         <v>94</v>
       </c>
       <c r="D90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E90">
         <v>933</v>
@@ -4191,13 +4195,13 @@
         <v>95</v>
       </c>
       <c r="D91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>854315</v>
       </c>
@@ -4205,13 +4209,13 @@
         <v>96</v>
       </c>
       <c r="D92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E92">
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>854320</v>
       </c>
@@ -4219,7 +4223,7 @@
         <v>97</v>
       </c>
       <c r="D93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E93">
         <v>281</v>
@@ -4233,7 +4237,7 @@
         <v>98</v>
       </c>
       <c r="D94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E94">
         <v>281</v>
@@ -4247,7 +4251,7 @@
         <v>99</v>
       </c>
       <c r="D95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E95">
         <v>281</v>
@@ -4261,7 +4265,7 @@
         <v>100</v>
       </c>
       <c r="D96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E96">
         <v>281</v>
@@ -4275,13 +4279,13 @@
         <v>101</v>
       </c>
       <c r="D97" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E97">
         <v>281</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>854241</v>
       </c>
@@ -4289,13 +4293,13 @@
         <v>102</v>
       </c>
       <c r="D98" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E98">
         <v>2027</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>854216</v>
       </c>
@@ -4303,7 +4307,7 @@
         <v>103</v>
       </c>
       <c r="D99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99">
         <v>1027</v>
@@ -4317,7 +4321,7 @@
         <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E100">
         <v>281</v>
@@ -4331,7 +4335,7 @@
         <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101">
         <v>951</v>
@@ -4345,7 +4349,7 @@
         <v>106</v>
       </c>
       <c r="D102" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E102">
         <v>593</v>
@@ -4359,7 +4363,7 @@
         <v>107</v>
       </c>
       <c r="D103" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E103">
         <v>614</v>
@@ -4373,7 +4377,7 @@
         <v>108</v>
       </c>
       <c r="D104" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E104">
         <v>703</v>
@@ -4387,7 +4391,7 @@
         <v>109</v>
       </c>
       <c r="D105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105">
         <v>699</v>
@@ -4401,7 +4405,7 @@
         <v>110</v>
       </c>
       <c r="D106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E106">
         <v>281</v>
@@ -4415,13 +4419,13 @@
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E107">
         <v>811</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>853867</v>
       </c>
@@ -4429,13 +4433,13 @@
         <v>112</v>
       </c>
       <c r="D108" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E108">
         <v>723</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>854062</v>
       </c>
@@ -4443,13 +4447,13 @@
         <v>113</v>
       </c>
       <c r="D109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E109">
         <v>2027</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>854683</v>
       </c>
@@ -4457,13 +4461,13 @@
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E110">
         <v>951</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>853489</v>
       </c>
@@ -4471,7 +4475,7 @@
         <v>115</v>
       </c>
       <c r="D111" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E111">
         <v>818</v>
@@ -4485,7 +4489,7 @@
         <v>116</v>
       </c>
       <c r="D112" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E112">
         <v>722</v>
@@ -4499,13 +4503,13 @@
         <v>117</v>
       </c>
       <c r="D113" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E113">
         <v>699</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>854193</v>
       </c>
@@ -4513,7 +4517,7 @@
         <v>118</v>
       </c>
       <c r="D114" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E114">
         <v>614</v>
@@ -4527,7 +4531,7 @@
         <v>119</v>
       </c>
       <c r="D115" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E115">
         <v>703</v>
@@ -4541,13 +4545,13 @@
         <v>120</v>
       </c>
       <c r="D116" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E116">
         <v>699</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>854543</v>
       </c>
@@ -4555,13 +4559,13 @@
         <v>121</v>
       </c>
       <c r="D117" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E117">
         <v>380</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>853459</v>
       </c>
@@ -4569,7 +4573,7 @@
         <v>122</v>
       </c>
       <c r="D118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E118">
         <v>2081</v>
@@ -4583,7 +4587,7 @@
         <v>123</v>
       </c>
       <c r="D119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E119">
         <v>2081</v>
@@ -4597,7 +4601,7 @@
         <v>124</v>
       </c>
       <c r="D120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E120">
         <v>2081</v>
@@ -4611,13 +4615,13 @@
         <v>125</v>
       </c>
       <c r="D121" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E121">
         <v>2081</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>854518</v>
       </c>
@@ -4625,7 +4629,7 @@
         <v>126</v>
       </c>
       <c r="D122" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E122">
         <v>593</v>
@@ -4639,13 +4643,13 @@
         <v>127</v>
       </c>
       <c r="D123" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E123">
         <v>951</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>854228</v>
       </c>
@@ -4653,13 +4657,13 @@
         <v>128</v>
       </c>
       <c r="D124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E124">
         <v>3078</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>854224</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>129</v>
       </c>
       <c r="D125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E125">
         <v>3078</v>
@@ -4681,7 +4685,7 @@
         <v>130</v>
       </c>
       <c r="D126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E126">
         <v>3078</v>
@@ -4695,7 +4699,7 @@
         <v>131</v>
       </c>
       <c r="D127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E127">
         <v>3078</v>
@@ -4709,7 +4713,7 @@
         <v>132</v>
       </c>
       <c r="D128" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E128">
         <v>3078</v>
@@ -4723,7 +4727,7 @@
         <v>133</v>
       </c>
       <c r="D129" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E129">
         <v>3078</v>
@@ -4737,13 +4741,13 @@
         <v>134</v>
       </c>
       <c r="D130" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E130">
         <v>3078</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>854692</v>
       </c>
@@ -4751,7 +4755,7 @@
         <v>135</v>
       </c>
       <c r="D131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E131">
         <v>642</v>
@@ -4765,7 +4769,7 @@
         <v>136</v>
       </c>
       <c r="D132" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E132">
         <v>811</v>
@@ -4779,7 +4783,7 @@
         <v>137</v>
       </c>
       <c r="D133" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E133">
         <v>2027</v>
@@ -4793,13 +4797,13 @@
         <v>138</v>
       </c>
       <c r="D134" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E134">
         <v>580</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>854013</v>
       </c>
@@ -4807,7 +4811,7 @@
         <v>139</v>
       </c>
       <c r="D135" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E135">
         <v>90</v>
@@ -4821,13 +4825,13 @@
         <v>140</v>
       </c>
       <c r="D136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E136">
         <v>90</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>853978</v>
       </c>
@@ -4835,13 +4839,13 @@
         <v>141</v>
       </c>
       <c r="D137" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E137">
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>853834</v>
       </c>
@@ -4849,7 +4853,7 @@
         <v>142</v>
       </c>
       <c r="D138" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E138">
         <v>90</v>
@@ -4863,7 +4867,7 @@
         <v>143</v>
       </c>
       <c r="D139" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E139">
         <v>90</v>
@@ -4877,13 +4881,13 @@
         <v>144</v>
       </c>
       <c r="D140" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E140">
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>854821</v>
       </c>
@@ -4891,7 +4895,7 @@
         <v>145</v>
       </c>
       <c r="D141" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E141">
         <v>699</v>
@@ -4905,7 +4909,7 @@
         <v>143</v>
       </c>
       <c r="D142" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E142">
         <v>90</v>
@@ -4919,13 +4923,13 @@
         <v>146</v>
       </c>
       <c r="D143" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E143">
         <v>811</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>854861</v>
       </c>
@@ -4933,13 +4937,13 @@
         <v>147</v>
       </c>
       <c r="D144" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E144">
         <v>951</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>854885</v>
       </c>
@@ -4947,7 +4951,7 @@
         <v>148</v>
       </c>
       <c r="D145" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E145">
         <v>2032</v>
@@ -4961,13 +4965,13 @@
         <v>149</v>
       </c>
       <c r="D146" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E146">
         <v>90</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>854775</v>
       </c>
@@ -4975,7 +4979,7 @@
         <v>150</v>
       </c>
       <c r="D147" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E147">
         <v>2032</v>
@@ -4989,13 +4993,13 @@
         <v>151</v>
       </c>
       <c r="D148" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E148">
         <v>703</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>854689</v>
       </c>
@@ -5003,7 +5007,7 @@
         <v>152</v>
       </c>
       <c r="D149" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E149">
         <v>874</v>
@@ -5017,13 +5021,13 @@
         <v>153</v>
       </c>
       <c r="D150" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E150">
         <v>737</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>854151</v>
       </c>
@@ -5031,7 +5035,7 @@
         <v>154</v>
       </c>
       <c r="D151" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E151">
         <v>90</v>
@@ -5045,7 +5049,7 @@
         <v>155</v>
       </c>
       <c r="D152" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E152">
         <v>699</v>
@@ -5059,7 +5063,7 @@
         <v>156</v>
       </c>
       <c r="D153" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E153">
         <v>699</v>
@@ -5073,7 +5077,7 @@
         <v>157</v>
       </c>
       <c r="D154" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E154">
         <v>380</v>
@@ -5087,13 +5091,13 @@
         <v>158</v>
       </c>
       <c r="D155" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E155">
         <v>90</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>854352</v>
       </c>
@@ -5101,7 +5105,7 @@
         <v>159</v>
       </c>
       <c r="D156" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E156">
         <v>377</v>
@@ -5115,13 +5119,13 @@
         <v>160</v>
       </c>
       <c r="D157" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E157">
         <v>811</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>854404</v>
       </c>
@@ -5129,7 +5133,7 @@
         <v>161</v>
       </c>
       <c r="D158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E158">
         <v>90</v>
@@ -5143,13 +5147,13 @@
         <v>162</v>
       </c>
       <c r="D159" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E159">
         <v>380</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>853976</v>
       </c>
@@ -5157,13 +5161,13 @@
         <v>163</v>
       </c>
       <c r="D160" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E160">
         <v>2055</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>854021</v>
       </c>
@@ -5171,13 +5175,13 @@
         <v>164</v>
       </c>
       <c r="D161" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E161">
         <v>951</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>854046</v>
       </c>
@@ -5185,13 +5189,13 @@
         <v>165</v>
       </c>
       <c r="D162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E162">
         <v>2036</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>854203</v>
       </c>
@@ -5199,7 +5203,7 @@
         <v>166</v>
       </c>
       <c r="D163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E163">
         <v>1021</v>
@@ -5213,7 +5217,7 @@
         <v>167</v>
       </c>
       <c r="D164" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E164">
         <v>281</v>
@@ -5227,7 +5231,7 @@
         <v>168</v>
       </c>
       <c r="D165" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E165">
         <v>281</v>
@@ -5241,7 +5245,7 @@
         <v>169</v>
       </c>
       <c r="D166" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E166">
         <v>281</v>
@@ -5255,13 +5259,13 @@
         <v>170</v>
       </c>
       <c r="D167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E167">
         <v>3098</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>854771</v>
       </c>
@@ -5269,7 +5273,7 @@
         <v>171</v>
       </c>
       <c r="D168" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E168">
         <v>1027</v>
@@ -5283,13 +5287,13 @@
         <v>172</v>
       </c>
       <c r="D169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E169">
         <v>951</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>854433</v>
       </c>
@@ -5297,7 +5301,7 @@
         <v>173</v>
       </c>
       <c r="D170" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E170">
         <v>742</v>
@@ -5311,13 +5315,13 @@
         <v>174</v>
       </c>
       <c r="D171" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171">
         <v>377</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>854434</v>
       </c>
@@ -5325,13 +5329,13 @@
         <v>175</v>
       </c>
       <c r="D172" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E172">
         <v>696</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>854436</v>
       </c>
@@ -5339,13 +5343,13 @@
         <v>176</v>
       </c>
       <c r="D173" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E173">
         <v>742</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>854302</v>
       </c>
@@ -5353,7 +5357,7 @@
         <v>177</v>
       </c>
       <c r="D174" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E174">
         <v>706</v>
@@ -5367,7 +5371,7 @@
         <v>178</v>
       </c>
       <c r="D175" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E175">
         <v>699</v>
@@ -5381,13 +5385,13 @@
         <v>179</v>
       </c>
       <c r="D176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E176">
         <v>614</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>854305</v>
       </c>
@@ -5395,13 +5399,13 @@
         <v>180</v>
       </c>
       <c r="D177" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E177">
         <v>574</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>854263</v>
       </c>
@@ -5409,7 +5413,7 @@
         <v>181</v>
       </c>
       <c r="D178" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E178">
         <v>574</v>
@@ -5423,13 +5427,13 @@
         <v>182</v>
       </c>
       <c r="D179" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E179">
         <v>90</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>854606</v>
       </c>
@@ -5437,7 +5441,7 @@
         <v>183</v>
       </c>
       <c r="D180" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E180">
         <v>2032</v>
@@ -5451,13 +5455,13 @@
         <v>184</v>
       </c>
       <c r="D181" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E181">
         <v>1021</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>854356</v>
       </c>
@@ -5465,13 +5469,13 @@
         <v>185</v>
       </c>
       <c r="D182" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E182">
         <v>867</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>854114</v>
       </c>
@@ -5479,13 +5483,13 @@
         <v>186</v>
       </c>
       <c r="D183" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E183">
         <v>90</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>853725</v>
       </c>
@@ -5493,13 +5497,13 @@
         <v>187</v>
       </c>
       <c r="D184" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E184">
         <v>614</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>854733</v>
       </c>
@@ -5507,13 +5511,13 @@
         <v>188</v>
       </c>
       <c r="D185" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E185">
         <v>836</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>845451</v>
       </c>
@@ -5521,7 +5525,7 @@
         <v>189</v>
       </c>
       <c r="D186" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E186">
         <v>1162</v>
@@ -5535,7 +5539,7 @@
         <v>190</v>
       </c>
       <c r="D187" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E187">
         <v>722</v>
@@ -5549,7 +5553,7 @@
         <v>191</v>
       </c>
       <c r="D188" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E188">
         <v>722</v>
@@ -5563,13 +5567,13 @@
         <v>192</v>
       </c>
       <c r="D189" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E189">
         <v>699</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>854443</v>
       </c>
@@ -5577,13 +5581,13 @@
         <v>193</v>
       </c>
       <c r="D190" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E190">
         <v>377</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>854387</v>
       </c>
@@ -5591,7 +5595,7 @@
         <v>194</v>
       </c>
       <c r="D191" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E191">
         <v>377</v>
@@ -5605,7 +5609,7 @@
         <v>195</v>
       </c>
       <c r="D192" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E192">
         <v>723</v>
@@ -5619,13 +5623,13 @@
         <v>196</v>
       </c>
       <c r="D193" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E193">
         <v>723</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>854148</v>
       </c>
@@ -5633,7 +5637,7 @@
         <v>197</v>
       </c>
       <c r="D194" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E194">
         <v>723</v>
@@ -5647,13 +5651,13 @@
         <v>198</v>
       </c>
       <c r="D195" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E195">
         <v>723</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>853783</v>
       </c>
@@ -5661,7 +5665,7 @@
         <v>199</v>
       </c>
       <c r="D196" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E196">
         <v>699</v>
@@ -5675,7 +5679,7 @@
         <v>200</v>
       </c>
       <c r="D197" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E197">
         <v>699</v>
@@ -5689,13 +5693,13 @@
         <v>201</v>
       </c>
       <c r="D198" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E198">
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>854314</v>
       </c>
@@ -5703,7 +5707,7 @@
         <v>202</v>
       </c>
       <c r="D199" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E199">
         <v>574</v>
@@ -5717,13 +5721,13 @@
         <v>203</v>
       </c>
       <c r="D200" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E200">
         <v>2027</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>854805</v>
       </c>
@@ -5731,13 +5735,13 @@
         <v>204</v>
       </c>
       <c r="D201" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E201">
         <v>2083</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>854807</v>
       </c>
@@ -5745,7 +5749,7 @@
         <v>205</v>
       </c>
       <c r="D202" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E202">
         <v>836</v>
@@ -5759,7 +5763,7 @@
         <v>206</v>
       </c>
       <c r="D203" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E203">
         <v>916</v>
@@ -5773,13 +5777,13 @@
         <v>207</v>
       </c>
       <c r="D204" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E204">
         <v>429</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>854728</v>
       </c>
@@ -5787,13 +5791,13 @@
         <v>208</v>
       </c>
       <c r="D205" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E205">
         <v>3089</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>854723</v>
       </c>
@@ -5801,7 +5805,7 @@
         <v>209</v>
       </c>
       <c r="D206" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E206">
         <v>3089</v>
@@ -5815,13 +5819,13 @@
         <v>210</v>
       </c>
       <c r="D207" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E207">
         <v>4005</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>854552</v>
       </c>
@@ -5829,13 +5833,13 @@
         <v>211</v>
       </c>
       <c r="D208" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E208">
         <v>3045</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>854537</v>
       </c>
@@ -5843,7 +5847,7 @@
         <v>212</v>
       </c>
       <c r="D209" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E209">
         <v>3045</v>
@@ -5857,7 +5861,7 @@
         <v>213</v>
       </c>
       <c r="D210" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E210">
         <v>699</v>
@@ -5871,7 +5875,7 @@
         <v>214</v>
       </c>
       <c r="D211" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E211">
         <v>943</v>
@@ -5885,7 +5889,7 @@
         <v>215</v>
       </c>
       <c r="D212" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E212">
         <v>703</v>
@@ -5899,13 +5903,13 @@
         <v>216</v>
       </c>
       <c r="D213" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E213">
         <v>3049</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>854768</v>
       </c>
@@ -5913,13 +5917,13 @@
         <v>217</v>
       </c>
       <c r="D214" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E214">
         <v>593</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>854769</v>
       </c>
@@ -5927,7 +5931,7 @@
         <v>217</v>
       </c>
       <c r="D215" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E215">
         <v>593</v>
@@ -5941,7 +5945,7 @@
         <v>218</v>
       </c>
       <c r="D216" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E216">
         <v>3060</v>
@@ -5955,13 +5959,13 @@
         <v>219</v>
       </c>
       <c r="D217" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E217">
         <v>3060</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>854616</v>
       </c>
@@ -5969,7 +5973,7 @@
         <v>220</v>
       </c>
       <c r="D218" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E218">
         <v>948</v>
@@ -5983,7 +5987,7 @@
         <v>221</v>
       </c>
       <c r="D219" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E219">
         <v>933</v>
@@ -5997,7 +6001,7 @@
         <v>222</v>
       </c>
       <c r="D220" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E220">
         <v>3037</v>
@@ -6011,7 +6015,7 @@
         <v>223</v>
       </c>
       <c r="D221" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E221">
         <v>377</v>
@@ -6025,13 +6029,13 @@
         <v>224</v>
       </c>
       <c r="D222" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E222">
         <v>3045</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>853476</v>
       </c>
@@ -6039,7 +6043,7 @@
         <v>225</v>
       </c>
       <c r="D223" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E223">
         <v>933</v>
@@ -6053,7 +6057,7 @@
         <v>226</v>
       </c>
       <c r="D224" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E224">
         <v>3045</v>
@@ -6067,7 +6071,7 @@
         <v>227</v>
       </c>
       <c r="D225" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E225">
         <v>614</v>
@@ -6081,13 +6085,13 @@
         <v>228</v>
       </c>
       <c r="D226" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E226">
         <v>3060</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>853742</v>
       </c>
@@ -6095,7 +6099,7 @@
         <v>229</v>
       </c>
       <c r="D227" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E227">
         <v>874</v>
@@ -6109,7 +6113,7 @@
         <v>230</v>
       </c>
       <c r="D228" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E228">
         <v>1097</v>
@@ -6123,7 +6127,7 @@
         <v>231</v>
       </c>
       <c r="D229" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E229">
         <v>3037</v>
@@ -6137,7 +6141,7 @@
         <v>232</v>
       </c>
       <c r="D230" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E230">
         <v>3060</v>
@@ -6151,7 +6155,7 @@
         <v>233</v>
       </c>
       <c r="D231" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E231">
         <v>967</v>
@@ -6165,13 +6169,13 @@
         <v>234</v>
       </c>
       <c r="D232" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E232">
         <v>3037</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>852644</v>
       </c>
@@ -6179,13 +6183,13 @@
         <v>235</v>
       </c>
       <c r="D233" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E233">
         <v>829</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>854666</v>
       </c>
@@ -6193,7 +6197,7 @@
         <v>236</v>
       </c>
       <c r="D234" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E234">
         <v>2027</v>
@@ -6207,7 +6211,7 @@
         <v>237</v>
       </c>
       <c r="D235" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E235">
         <v>90</v>
@@ -6221,7 +6225,7 @@
         <v>238</v>
       </c>
       <c r="D236" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E236">
         <v>737</v>
@@ -6235,7 +6239,7 @@
         <v>239</v>
       </c>
       <c r="D237" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E237">
         <v>874</v>
@@ -6249,13 +6253,13 @@
         <v>240</v>
       </c>
       <c r="D238" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E238">
         <v>1027</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>854347</v>
       </c>
@@ -6263,7 +6267,7 @@
         <v>241</v>
       </c>
       <c r="D239" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E239">
         <v>967</v>
@@ -6277,7 +6281,7 @@
         <v>242</v>
       </c>
       <c r="D240" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E240">
         <v>3034</v>
@@ -6291,7 +6295,7 @@
         <v>243</v>
       </c>
       <c r="D241" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E241">
         <v>3060</v>
@@ -6305,7 +6309,7 @@
         <v>228</v>
       </c>
       <c r="D242" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E242">
         <v>3060</v>
@@ -6319,7 +6323,7 @@
         <v>244</v>
       </c>
       <c r="D243" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E243">
         <v>811</v>
@@ -6333,7 +6337,7 @@
         <v>245</v>
       </c>
       <c r="D244" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E244">
         <v>3055</v>
@@ -6347,7 +6351,7 @@
         <v>246</v>
       </c>
       <c r="D245" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E245">
         <v>3060</v>
@@ -6361,7 +6365,7 @@
         <v>247</v>
       </c>
       <c r="D246" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E246">
         <v>90</v>
@@ -6375,7 +6379,7 @@
         <v>248</v>
       </c>
       <c r="D247" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E247">
         <v>614</v>
@@ -6389,7 +6393,7 @@
         <v>249</v>
       </c>
       <c r="D248" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E248">
         <v>90</v>
@@ -6403,7 +6407,7 @@
         <v>250</v>
       </c>
       <c r="D249" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E249">
         <v>3</v>
@@ -6417,7 +6421,7 @@
         <v>251</v>
       </c>
       <c r="D250" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E250">
         <v>380</v>
@@ -6431,7 +6435,7 @@
         <v>252</v>
       </c>
       <c r="D251" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E251">
         <v>3055</v>
@@ -6445,7 +6449,7 @@
         <v>253</v>
       </c>
       <c r="D252" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E252">
         <v>60</v>
@@ -6459,7 +6463,7 @@
         <v>254</v>
       </c>
       <c r="D253" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -6473,7 +6477,7 @@
         <v>254</v>
       </c>
       <c r="D254" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E254">
         <v>60</v>
@@ -6487,7 +6491,7 @@
         <v>255</v>
       </c>
       <c r="D255" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E255">
         <v>60</v>
@@ -6501,7 +6505,7 @@
         <v>256</v>
       </c>
       <c r="D256" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E256">
         <v>60</v>
@@ -6515,7 +6519,7 @@
         <v>257</v>
       </c>
       <c r="D257" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E257">
         <v>60</v>
@@ -6529,7 +6533,7 @@
         <v>258</v>
       </c>
       <c r="D258" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E258">
         <v>60</v>
@@ -6543,7 +6547,7 @@
         <v>259</v>
       </c>
       <c r="D259" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E259">
         <v>60</v>
@@ -6557,7 +6561,7 @@
         <v>260</v>
       </c>
       <c r="D260" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E260">
         <v>60</v>
@@ -6571,7 +6575,7 @@
         <v>261</v>
       </c>
       <c r="D261" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E261">
         <v>60</v>
@@ -6585,7 +6589,7 @@
         <v>261</v>
       </c>
       <c r="D262" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E262">
         <v>60</v>
@@ -6599,7 +6603,7 @@
         <v>262</v>
       </c>
       <c r="D263" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E263">
         <v>936</v>
@@ -6613,7 +6617,7 @@
         <v>263</v>
       </c>
       <c r="D264" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E264">
         <v>906</v>
@@ -6627,7 +6631,7 @@
         <v>263</v>
       </c>
       <c r="D265" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E265">
         <v>906</v>
@@ -6641,7 +6645,7 @@
         <v>264</v>
       </c>
       <c r="D266" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E266">
         <v>979</v>
@@ -6655,7 +6659,7 @@
         <v>264</v>
       </c>
       <c r="D267" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E267">
         <v>979</v>
@@ -6669,7 +6673,7 @@
         <v>265</v>
       </c>
       <c r="D268" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E268">
         <v>967</v>
@@ -6683,7 +6687,7 @@
         <v>266</v>
       </c>
       <c r="D269" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E269">
         <v>293</v>
@@ -6697,13 +6701,13 @@
         <v>267</v>
       </c>
       <c r="D270" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E270">
         <v>694</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>854888</v>
       </c>
@@ -6711,13 +6715,13 @@
         <v>268</v>
       </c>
       <c r="D271" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E271">
         <v>614</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>854777</v>
       </c>
@@ -6725,7 +6729,7 @@
         <v>269</v>
       </c>
       <c r="D272" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E272">
         <v>3</v>
@@ -6739,7 +6743,7 @@
         <v>270</v>
       </c>
       <c r="D273" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E273">
         <v>966</v>
@@ -6753,7 +6757,7 @@
         <v>271</v>
       </c>
       <c r="D274" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E274">
         <v>694</v>
@@ -6767,13 +6771,13 @@
         <v>272</v>
       </c>
       <c r="D275" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E275">
         <v>639</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>854837</v>
       </c>
@@ -6781,7 +6785,7 @@
         <v>273</v>
       </c>
       <c r="D276" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E276">
         <v>2091</v>
@@ -6795,7 +6799,7 @@
         <v>274</v>
       </c>
       <c r="D277" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E277">
         <v>293</v>
@@ -6809,13 +6813,13 @@
         <v>275</v>
       </c>
       <c r="D278" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E278">
         <v>375</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>852605</v>
       </c>
@@ -6823,7 +6827,7 @@
         <v>276</v>
       </c>
       <c r="D279" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E279">
         <v>1807</v>
@@ -6837,7 +6841,7 @@
         <v>277</v>
       </c>
       <c r="D280" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E280">
         <v>2047</v>
@@ -6851,7 +6855,7 @@
         <v>278</v>
       </c>
       <c r="D281" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E281">
         <v>1019</v>
@@ -6865,7 +6869,7 @@
         <v>279</v>
       </c>
       <c r="D282" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E282">
         <v>1019</v>
@@ -6879,7 +6883,7 @@
         <v>279</v>
       </c>
       <c r="D283" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E283">
         <v>1019</v>
@@ -6893,7 +6897,7 @@
         <v>279</v>
       </c>
       <c r="D284" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E284">
         <v>1019</v>
@@ -6907,7 +6911,7 @@
         <v>280</v>
       </c>
       <c r="D285" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E285">
         <v>118</v>
@@ -6921,7 +6925,7 @@
         <v>281</v>
       </c>
       <c r="D286" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E286">
         <v>967</v>
@@ -6935,13 +6939,13 @@
         <v>282</v>
       </c>
       <c r="D287" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E287">
         <v>979</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>854759</v>
       </c>
@@ -6949,7 +6953,7 @@
         <v>283</v>
       </c>
       <c r="D288" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E288">
         <v>694</v>
@@ -6963,7 +6967,7 @@
         <v>284</v>
       </c>
       <c r="D289" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E289">
         <v>2016</v>
@@ -6977,7 +6981,7 @@
         <v>285</v>
       </c>
       <c r="D290" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E290">
         <v>851</v>
@@ -6991,13 +6995,13 @@
         <v>286</v>
       </c>
       <c r="D291" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E291">
         <v>979</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>853804</v>
       </c>
@@ -7005,7 +7009,7 @@
         <v>287</v>
       </c>
       <c r="D292" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E292">
         <v>29</v>
@@ -7019,7 +7023,7 @@
         <v>288</v>
       </c>
       <c r="D293" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E293">
         <v>2038</v>
@@ -7033,7 +7037,7 @@
         <v>289</v>
       </c>
       <c r="D294" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E294">
         <v>1807</v>
@@ -7047,7 +7051,7 @@
         <v>290</v>
       </c>
       <c r="D295" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E295">
         <v>1807</v>
@@ -7061,7 +7065,7 @@
         <v>291</v>
       </c>
       <c r="D296" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E296">
         <v>1807</v>
@@ -7075,7 +7079,7 @@
         <v>292</v>
       </c>
       <c r="D297" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E297">
         <v>694</v>
@@ -7089,13 +7093,13 @@
         <v>292</v>
       </c>
       <c r="D298" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E298">
         <v>694</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>853700</v>
       </c>
@@ -7103,13 +7107,13 @@
         <v>293</v>
       </c>
       <c r="D299" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E299">
         <v>293</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>854713</v>
       </c>
@@ -7117,7 +7121,7 @@
         <v>294</v>
       </c>
       <c r="D300" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E300">
         <v>639</v>
@@ -7131,7 +7135,7 @@
         <v>295</v>
       </c>
       <c r="D301" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E301">
         <v>996</v>
@@ -7145,13 +7149,13 @@
         <v>296</v>
       </c>
       <c r="D302" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E302">
         <v>1807</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>853703</v>
       </c>
@@ -7159,7 +7163,7 @@
         <v>297</v>
       </c>
       <c r="D303" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E303">
         <v>293</v>
@@ -7173,7 +7177,7 @@
         <v>298</v>
       </c>
       <c r="D304" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E304">
         <v>293</v>
@@ -7187,7 +7191,7 @@
         <v>299</v>
       </c>
       <c r="D305" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E305">
         <v>2073</v>
@@ -7201,7 +7205,7 @@
         <v>300</v>
       </c>
       <c r="D306" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E306">
         <v>979</v>
@@ -7215,7 +7219,7 @@
         <v>301</v>
       </c>
       <c r="D307" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E307">
         <v>60</v>
@@ -7229,7 +7233,7 @@
         <v>302</v>
       </c>
       <c r="D308" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E308">
         <v>851</v>
@@ -7243,7 +7247,7 @@
         <v>303</v>
       </c>
       <c r="D309" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E309">
         <v>851</v>
@@ -7257,7 +7261,7 @@
         <v>304</v>
       </c>
       <c r="D310" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E310">
         <v>851</v>
@@ -7271,7 +7275,7 @@
         <v>305</v>
       </c>
       <c r="D311" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E311">
         <v>851</v>
@@ -7285,7 +7289,7 @@
         <v>306</v>
       </c>
       <c r="D312" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E312">
         <v>979</v>
@@ -7299,7 +7303,7 @@
         <v>307</v>
       </c>
       <c r="D313" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E313">
         <v>1807</v>
@@ -7313,7 +7317,7 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E314">
         <v>293</v>
@@ -7327,7 +7331,7 @@
         <v>309</v>
       </c>
       <c r="D315" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E315">
         <v>293</v>
@@ -7341,7 +7345,7 @@
         <v>310</v>
       </c>
       <c r="D316" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E316">
         <v>293</v>
@@ -7355,7 +7359,7 @@
         <v>311</v>
       </c>
       <c r="D317" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E317">
         <v>996</v>
@@ -7369,7 +7373,7 @@
         <v>312</v>
       </c>
       <c r="D318" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E318">
         <v>257</v>
@@ -7383,7 +7387,7 @@
         <v>313</v>
       </c>
       <c r="D319" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E319">
         <v>2081</v>
@@ -7397,7 +7401,7 @@
         <v>314</v>
       </c>
       <c r="D320" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E320">
         <v>2081</v>
@@ -7411,13 +7415,14 @@
         <v>315</v>
       </c>
       <c r="D321" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E321">
         <v>2081</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E321" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EFCE48B-4A5C-47BC-B010-9070122237A3}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFE388A9-D8C4-4C2E-AC5C-336FECE73A54}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="246">
   <si>
     <t>Pedido</t>
   </si>
@@ -110,14 +110,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.417,91_x000D_
-• Valor em ruptura: R$ 1.639,98_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -241,22 +233,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.457,70_x000D_
-• Valor em ruptura: R$ 1.981,90_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.878,49_x000D_
-• Valor em ruptura: R$ 730,60_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.074,99_x000D_
 • Valor em ruptura: R$ 1.177,40_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
@@ -270,78 +246,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.722,55_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 554,31_x000D_
-• Valor em ruptura: R$ 1.431,84_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.163,04_x000D_
-• Valor em ruptura: R$ 433,75_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.787,55_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 28.580,84_x000D_
-• Valor em ruptura: R$ 975,93_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 518,35_x000D_
-• Valor em ruptura: R$ 4.672,87_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.697,92_x000D_
-• Valor em ruptura: R$ 2.148,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.643,05_x000D_
-• Valor em ruptura: R$ 4.122,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -350,14 +254,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.507,46_x000D_
-• Valor em ruptura: R$ 12.658,73_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -371,30 +267,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 897,13_x000D_
 • Valor em ruptura: R$ 1.673,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.637,72_x000D_
-• Valor em ruptura: R$ 1.240,40_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.944,58_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.927,62_x000D_
-• Valor em ruptura: R$ 2.053,78_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -406,30 +278,6 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.503,30_x000D_
-• Valor em ruptura: R$ 7.593,60_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.659,85_x000D_
-• Valor em ruptura: R$ 1.067,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.249,26_x000D_
-• Valor em ruptura: R$ 190,82_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -457,27 +305,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 333,50_x000D_
-• Valor em ruptura: R$ 4.298,61_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.601,68_x000D_
-• Valor em ruptura: R$ 725,53_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -486,22 +318,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.330,15_x000D_
-• Valor em ruptura: R$ 5.017,32_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 40.945,56_x000D_
-• Valor em ruptura: R$ 2.163,98_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -518,22 +334,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.498,92_x000D_
-• Valor em ruptura: R$ 529,10_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.789,86_x000D_
-• Valor em ruptura: R$ 12.543,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -542,46 +342,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.998,03_x000D_
-• Valor em ruptura: R$ 7.142,84_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.138,49_x000D_
-• Valor em ruptura: R$ 181,28_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.386,90_x000D_
-• Valor em ruptura: R$ 183,10_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.853,29_x000D_
-• Valor em ruptura: R$ 181,28_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.997,40_x000D_
-• Valor em ruptura: R$ 182,76_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -606,14 +366,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.795,32_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -622,14 +374,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.548,78_x000D_
-• Valor em ruptura: R$ 169,77_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -646,38 +390,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.343,14_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.003,60_x000D_
-• Valor em ruptura: R$ 1.362,03_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.524,82_x000D_
-• Valor em ruptura: R$ 3.178,47_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.686,07_x000D_
-• Valor em ruptura: R$ 612,91_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -724,70 +436,6 @@
 • Valor em estoque: R$ 13.311,22_x000D_
 • Valor em ruptura: R$ 480,96_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.223,37_x000D_
-• Valor em ruptura: R$ 181,28_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.413,43_x000D_
-• Valor em ruptura: R$ 181,28_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 953,52_x000D_
-• Valor em ruptura: R$ 366,20_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.580,46_x000D_
-• Valor em ruptura: R$ 183,10_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.707,19_x000D_
-• Valor em ruptura: R$ 366,20_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.317,76_x000D_
-• Valor em ruptura: R$ 181,38_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 15.138,01_x000D_
-• Valor em ruptura: R$ 513,45_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.004,69_x000D_
-• Valor em ruptura: R$ 1.414,82_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -809,38 +457,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.546,54_x000D_
-• Valor em ruptura: R$ 1.728,64_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.513,27_x000D_
-• Valor em ruptura: R$ 182,76_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.082,47_x000D_
-• Valor em ruptura: R$ 182,76_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.758,69_x000D_
-• Valor em ruptura: R$ 547,87_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.467,70_x000D_
 • Valor em ruptura: R$ 271,15_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -849,14 +465,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.994,45_x000D_
-• Valor em ruptura: R$ 1.362,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.919,41_x000D_
 • Valor em ruptura: R$ 2.700,94_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -916,14 +524,6 @@
 • Valor em estoque: R$ 1.014,62_x000D_
 • Valor em ruptura: R$ 2.376,06_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.630,03_x000D_
-• Valor em ruptura: R$ 4.413,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -942,30 +542,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.119,34_x000D_
-• Valor em ruptura: R$ 3.835,42_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.177,80_x000D_
-• Valor em ruptura: R$ 1.767,78_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.255,48_x000D_
-• Valor em ruptura: R$ 1.596,63_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -987,14 +563,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
@@ -1011,22 +579,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.828,78_x000D_
 • Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.506,19_x000D_
-• Valor em ruptura: R$ 346,29_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 188,90_x000D_
-• Valor em ruptura: R$ 7.525,98_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1038,30 +590,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.210,72_x000D_
-• Valor em ruptura: R$ 6.362,48_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.221,75_x000D_
-• Valor em ruptura: R$ 171,15_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.010,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1098,23 +626,7 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.593,16_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 20.730,54_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 15.909,49_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1179,22 +691,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 448,07_x000D_
 • Valor em ruptura: R$ 1.886,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 743,27_x000D_
-• Valor em ruptura: R$ 1.886,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.109,99_x000D_
-• Valor em ruptura: R$ 2.121,01_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1214,51 +710,11 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.573,35_x000D_
-• Valor em ruptura: R$ 4.894,85_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 357,25_x000D_
 • Valor em ruptura: R$ 2.224,93_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.739,48_x000D_
-• Valor em ruptura: R$ 15.211,27_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.816,67_x000D_
-• Valor em ruptura: R$ 4.540,68_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.243,37_x000D_
-• Valor em ruptura: R$ 1.325,06_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.712,26_x000D_
-• Valor em ruptura: R$ 1.507,86_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1270,14 +726,6 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.987,42_x000D_
-• Valor em ruptura: R$ 7.171,10_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1289,30 +737,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 17.322,79_x000D_
-• Valor em ruptura: R$ 291,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.181,60_x000D_
-• Valor em ruptura: R$ 1.711,48_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.653,23_x000D_
-• Valor em ruptura: R$ 855,74_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.394,44_x000D_
 • Valor em ruptura: R$ 529,10_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1326,30 +750,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.484,12_x000D_
-• Valor em ruptura: R$ 173,23_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 988,25_x000D_
-• Valor em ruptura: R$ 4.276,44_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.435,76_x000D_
-• Valor em ruptura: R$ 4.481,70_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1377,14 +777,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.125,16_x000D_
-• Valor em ruptura: R$ 3.010,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.514,89_x000D_
 • Valor em ruptura: R$ 977,09_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1393,14 +785,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.305,08_x000D_
-• Valor em ruptura: R$ 2.222,75_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.918,98_x000D_
 • Valor em ruptura: R$ 1.112,47_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1409,22 +793,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.641,47_x000D_
-• Valor em ruptura: R$ 1.587,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.748,77_x000D_
-• Valor em ruptura: R$ 865,72_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.016,76_x000D_
 • Valor em ruptura: R$ 2.347,13_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -1444,22 +812,6 @@
 • Valor em estoque: R$ 2.666,49_x000D_
 • Valor em ruptura: R$ 1.330,59_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.418,95_x000D_
-• Valor em ruptura: R$ 1.086,60_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.165,13_x000D_
-• Valor em ruptura: R$ 4.335,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -1473,38 +825,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.325,08_x000D_
-• Valor em ruptura: R$ 826,84_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 12.199,59_x000D_
-• Valor em ruptura: R$ 2.023,73_x000D_
-• Valor mínimo de frete: R$ 1.000,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 14.139,49_x000D_
-• Valor em ruptura: R$ 3.042,44_x000D_
-• Valor mínimo de frete: R$ 50,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 22.697,28_x000D_
-• Valor em ruptura: R$ 9.077,86_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 13.558,09_x000D_
 • Valor em ruptura: R$ 254,41_x000D_
 • Valor mínimo de frete: R$ 6.250,00</t>
@@ -1513,14 +833,6 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.320,12_x000D_
-• Valor em ruptura: R$ 6.577,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.683,49_x000D_
 • Valor em ruptura: R$ 92.386,96_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
@@ -1542,22 +854,6 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 11.395,89_x000D_
-• Valor em ruptura: R$ 4.527,09_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 38.652,70_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1569,49 +865,9 @@
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.538,31_x000D_
-• Valor em ruptura: R$ 11.897,95_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.337,69_x000D_
 • Valor em ruptura: R$ 36.831,92_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 33.786,80_x000D_
-• Valor em ruptura: R$ 27.342,87_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.001,53_x000D_
-• Valor em ruptura: R$ 3.102,97_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.931,73_x000D_
-• Valor em ruptura: R$ 2.909,52_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 127.001,27_x000D_
-• Valor em ruptura: R$ 16.021,32_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -1662,30 +918,6 @@
 • Valor mínimo de frete: R$ 50,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.423,30_x000D_
-• Valor em ruptura: R$ 211.828,13_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.095,84_x000D_
-• Valor em ruptura: R$ 43.851,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.214,94_x000D_
-• Valor em ruptura: R$ 4.425,49_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1702,70 +934,6 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 17.298,69_x000D_
-• Valor em ruptura: R$ 532,67_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.814,30_x000D_
-• Valor em ruptura: R$ 3.019,84_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.825,58_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 7.175,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.535,74_x000D_
-• Valor em ruptura: R$ 7.637,57_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.571,30_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.183,97_x000D_
-• Valor em ruptura: R$ 1.335,66_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.052,14_x000D_
-• Valor em ruptura: R$ 433,79_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.944,81_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1782,52 +950,12 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.660,86_x000D_
-• Valor em ruptura: R$ 264,55_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.229,66_x000D_
 • Valor em ruptura: R$ 1.267,97_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 18.797,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.353,51_x000D_
-• Valor em ruptura: R$ 5.540,62_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 836,12_x000D_
-• Valor em ruptura: R$ 1.920,93_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.629,44_x000D_
-• Valor em ruptura: R$ 2.397,11_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -1849,30 +977,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.610,66_x000D_
-• Valor em ruptura: R$ 1.058,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.708,65_x000D_
-• Valor em ruptura: R$ 1.793,35_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.099,21_x000D_
-• Valor em ruptura: R$ 264,55_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 2.645,50_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1883,22 +987,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.803,76_x000D_
 • Valor em ruptura: R$ 2.410,60_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.527,58_x000D_
-• Valor em ruptura: R$ 4.739,29_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 759,84_x000D_
-• Valor em ruptura: R$ 1.920,93_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1921,14 +1009,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.486,75_x000D_
-• Valor em ruptura: R$ 1.301,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.394,93_x000D_
 • Valor em ruptura: R$ 1.881,50_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1945,7 +1025,839 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.424,10_x000D_
+• Valor em estoque: R$ 588,41_x000D_
+• Valor em ruptura: R$ 2.645,50_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 662,67_x000D_
+• Valor em ruptura: R$ 2.508,66_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.508,66_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 295,26_x000D_
+• Valor em ruptura: R$ 4.509,50_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.736,04_x000D_
+• Valor em ruptura: R$ 2.765,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.039,56_x000D_
+• Valor em ruptura: R$ 5.006,80_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 541,90_x000D_
+• Valor em ruptura: R$ 3.333,02_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.790,28_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.140,94_x000D_
+• Valor em ruptura: R$ 1.587,30_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 28.950,21_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 31.786,92_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 63.573,84_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 59.303,96_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 44.204,67_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 63.851,18_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 73.674,44_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.249,80_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 153.277,92_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 162.401,60_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 9.123,69_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 6.741,46_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 31.523,73_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 21.256,77_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 16.603,72_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 8.610,08_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.882,35_x000D_
+• Valor em ruptura: R$ 53.346,92_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.654,58_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 38.762,66_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 38.772,48_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.733,80_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.327,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 11.722,62_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 57.852,90_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.299,24_x000D_
+• Valor em ruptura: R$ 257,60_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 275.948,41_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 11.148,58_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 33.802,88_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 44.044,57_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 142.341,65_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 12.872,38_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 19.255,88_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 103.262,47_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 23.378,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.188,31_x000D_
+• Valor em ruptura: R$ 182,50_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.729,14_x000D_
+• Valor em ruptura: R$ 328,75_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.450,87_x000D_
+• Valor em ruptura: R$ 71,37_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.842,47_x000D_
+• Valor em ruptura: R$ 1.597,13_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.070,87_x000D_
+• Valor em ruptura: R$ 538,22_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.250,78_x000D_
+• Valor em ruptura: R$ 55,78_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.270,03_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 17.096,86_x000D_
+• Valor em ruptura: R$ 206,22_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.675,68_x000D_
+• Valor em ruptura: R$ 515,54_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.110,86_x000D_
+• Valor em ruptura: R$ 2.654,58_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.484,62_x000D_
+• Valor em ruptura: R$ 393,50_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.255,31_x000D_
+• Valor em ruptura: R$ 1.800,63_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.978,59_x000D_
+• Valor em ruptura: R$ 7.118,31_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.931,41_x000D_
+• Valor em ruptura: R$ 10.726,02_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.186,15_x000D_
+• Valor em ruptura: R$ 3.742,73_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.994,42_x000D_
+• Valor em ruptura: R$ 1.003,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.545,48_x000D_
+• Valor em ruptura: R$ 5.296,53_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.093,04_x000D_
+• Valor em ruptura: R$ 278,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.436,64_x000D_
+• Valor em ruptura: R$ 1.491,64_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.650,02_x000D_
+• Valor em ruptura: R$ 1.693,12_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.091,89_x000D_
+• Valor em ruptura: R$ 273,74_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 923,18_x000D_
+• Valor em ruptura: R$ 766,12_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.381,80_x000D_
+• Valor em ruptura: R$ 3.600,62_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.430,80_x000D_
+• Valor em ruptura: R$ 844,38_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.485,77_x000D_
+• Valor em ruptura: R$ 3.557,76_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.296,18_x000D_
+• Valor em ruptura: R$ 3.658,58_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.691,25_x000D_
+• Valor em ruptura: R$ 1.254,33_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.597,78_x000D_
+• Valor em ruptura: R$ 1.254,33_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.493,26_x000D_
+• Valor em ruptura: R$ 278,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.265,63_x000D_
+• Valor em ruptura: R$ 2.699,16_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.040,04_x000D_
+• Valor em ruptura: R$ 5.533,16_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.603,96_x000D_
+• Valor em ruptura: R$ 1.003,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.109,99_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.815,83_x000D_
+• Valor em ruptura: R$ 752,60_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.985,97_x000D_
+• Valor em ruptura: R$ 3.167,76_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.557,64_x000D_
+• Valor em ruptura: R$ 1.429,94_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.493,35_x000D_
+• Valor em ruptura: R$ 6.665,17_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.501,70_x000D_
+• Valor em ruptura: R$ 3.762,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.949,21_x000D_
+• Valor em ruptura: R$ 3.968,25_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 13.172,91_x000D_
+• Valor em ruptura: R$ 6.028,58_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.200,42_x000D_
+• Valor em ruptura: R$ 2.190,29_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.050,63_x000D_
+• Valor em ruptura: R$ 5.340,53_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.586,66_x000D_
+• Valor em ruptura: R$ 1.941,17_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.584,81_x000D_
+• Valor em ruptura: R$ 920,74_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.315,74_x000D_
+• Valor em ruptura: R$ 4.185,05_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.145,70_x000D_
+• Valor em ruptura: R$ 3.620,54_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 15.720,18_x000D_
+• Valor em ruptura: R$ 1.461,75_x000D_
+• Valor mínimo de frete: R$ 50,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 13.223,82_x000D_
+• Valor em ruptura: R$ 2.699,16_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 12.289,77_x000D_
+• Valor em ruptura: R$ 8.146,49_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.807,69_x000D_
+• Valor em ruptura: R$ 296,81_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.444,00_x000D_
+• Valor em ruptura: R$ 10.653,20_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.824,78_x000D_
+• Valor em ruptura: R$ 1.009,36_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.038,86_x000D_
+• Valor em ruptura: R$ 240,48_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.979,59_x000D_
+• Valor em ruptura: R$ 5.879,40_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.836,90_x000D_
+• Valor em ruptura: R$ 8.893,74_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.021,40_x000D_
+• Valor em ruptura: R$ 1.202,39_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.585,36_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 24.017,55_x000D_
+• Valor em ruptura: R$ 933,28_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.640,74_x000D_
+• Valor em ruptura: R$ 861,26_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.897,42_x000D_
+• Valor em ruptura: R$ 4.369,45_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.679,13_x000D_
+• Valor em ruptura: R$ 1.108,81_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.293,41_x000D_
 • Valor em ruptura: R$ 275,83_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
@@ -1953,545 +1865,121 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 588,41_x000D_
-• Valor em ruptura: R$ 2.645,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 662,67_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.141,27_x000D_
-• Valor em ruptura: R$ 381,64_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 295,26_x000D_
-• Valor em ruptura: R$ 4.509,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.736,04_x000D_
-• Valor em ruptura: R$ 2.765,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.039,56_x000D_
-• Valor em ruptura: R$ 5.006,80_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.133,00_x000D_
-• Valor em ruptura: R$ 278,23_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.236,91_x000D_
-• Valor em ruptura: R$ 1.953,40_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.937,96_x000D_
-• Valor em ruptura: R$ 498,97_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.074,00_x000D_
-• Valor em ruptura: R$ 1.588,02_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.370,56_x000D_
-• Valor em ruptura: R$ 759,98_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 541,90_x000D_
-• Valor em ruptura: R$ 3.333,02_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.790,28_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.140,94_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.615,50_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.201,21_x000D_
+• Valor em ruptura: R$ 2.164,30_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.154,85_x000D_
+• Valor em ruptura: R$ 2.525,38_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.603,01_x000D_
 • Valor em ruptura: R$ 1.587,30_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 28.950,21_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 31.786,92_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 63.573,84_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 59.303,96_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 44.204,67_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 63.851,18_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 73.674,44_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.249,80_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 153.277,92_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 162.401,60_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 9.123,69_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 6.741,46_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 31.523,73_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 21.256,77_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 16.603,72_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 8.610,08_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.882,35_x000D_
-• Valor em ruptura: R$ 53.346,92_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 14.956,83_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.213,82_x000D_
-• Valor em ruptura: R$ 770,94_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.654,58_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.629,86_x000D_
-• Valor em ruptura: R$ 825,82_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.432,78_x000D_
+• Valor em ruptura: R$ 1.229,24_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.198,78_x000D_
+• Valor em ruptura: R$ 250,87_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.975,84_x000D_
-• Valor em ruptura: R$ 6.058,80_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 38.762,66_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 38.772,48_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.733,80_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.327,99_x000D_
+• Valor em estoque: R$ 4.785,18_x000D_
+• Valor em ruptura: R$ 6.640,08_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.571,79_x000D_
+• Valor em ruptura: R$ 558,75_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 10.522,24_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.744,10_x000D_
-• Valor em ruptura: R$ 3.489,15_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.024,47_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.092,69_x000D_
-• Valor em ruptura: R$ 206,05_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 11.722,62_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.696,88_x000D_
-• Valor em ruptura: R$ 804,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.104,61_x000D_
-• Valor em ruptura: R$ 1.787,66_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.174,30_x000D_
-• Valor em ruptura: R$ 15.186,65_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 57.852,90_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.954,42_x000D_
-• Valor em ruptura: R$ 3.808,78_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.039,53_x000D_
-• Valor em ruptura: R$ 811,51_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.537,27_x000D_
-• Valor em ruptura: R$ 398,76_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.299,24_x000D_
-• Valor em ruptura: R$ 257,60_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 275.948,41_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.931,08_x000D_
-• Valor em ruptura: R$ 6.113,91_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 11.148,58_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 6.315,48_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.713,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 33.802,88_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 44.044,57_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 142.341,65_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 12.872,38_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 19.255,88_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 103.262,47_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 23.378,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.748,58_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.101,86_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 1.554,84_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
+• Valor em estoque: R$ 8.743,94_x000D_
+• Valor em ruptura: R$ 8.743,94_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 18.487,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 96.400,69_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 13.976,84_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.599,75_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.057,80_x000D_
+• Valor em ruptura: R$ 4.102,09_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
 </sst>
 </file>
@@ -2867,7 +2355,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -2965,94 +2453,94 @@
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>853943</v>
+        <v>855347</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>773</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>855177</v>
+        <v>853943</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>2078</v>
+        <v>773</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>853849</v>
+        <v>855177</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>1021</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>853567</v>
+        <v>853849</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>3060</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>854781</v>
+        <v>853567</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>3093</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>848783</v>
+        <v>854781</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>3075</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>853426</v>
+        <v>848783</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -3063,16 +2551,16 @@
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>855023</v>
+        <v>853426</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>3057</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
@@ -3080,7 +2568,7 @@
         <v>854985</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -3094,7 +2582,7 @@
         <v>854061</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -3108,7 +2596,7 @@
         <v>849811</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -3119,136 +2607,136 @@
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>849918</v>
+        <v>855293</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>750</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>849917</v>
+        <v>849918</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>3089</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>850200</v>
+        <v>855268</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>1021</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>852593</v>
+        <v>849917</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>632</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>852631</v>
+        <v>850200</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>3085</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>853998</v>
+        <v>852593</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>722</v>
+        <v>632</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>853852</v>
+        <v>852631</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>773</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>854933</v>
+        <v>853998</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>983</v>
+        <v>722</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>854931</v>
+        <v>855341</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>983</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>854237</v>
+        <v>853852</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -3259,136 +2747,136 @@
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>854330</v>
+        <v>854933</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>854385</v>
+        <v>854931</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>2090</v>
+        <v>983</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>855005</v>
+        <v>854237</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>3055</v>
+        <v>773</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>855050</v>
+        <v>854585</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>979</v>
+        <v>933</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>854538</v>
+        <v>855295</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>853431</v>
+        <v>854330</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>2091</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>853694</v>
+        <v>855330</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>854374</v>
+        <v>854385</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>3069</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>854739</v>
+        <v>855232</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>2073</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>854225</v>
+        <v>854374</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
@@ -3402,7 +2890,7 @@
         <v>854940</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -3416,7 +2904,7 @@
         <v>855052</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -3425,152 +2913,152 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>853956</v>
+        <v>854415</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40">
-        <v>614</v>
+        <v>703</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>854415</v>
+        <v>854840</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>854840</v>
+        <v>855159</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>642</v>
+        <v>614</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>855159</v>
+        <v>855376</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>614</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>853934</v>
+        <v>855350</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44">
-        <v>380</v>
+        <v>614</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>854578</v>
+        <v>854934</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>948</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>854934</v>
+        <v>854891</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>2064</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>854891</v>
+        <v>854250</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>2051</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>854080</v>
+        <v>853913</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>580</v>
+        <v>614</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>854949</v>
+        <v>855357</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>750</v>
+        <v>699</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>854250</v>
+        <v>854234</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -3581,220 +3069,220 @@
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>853913</v>
+        <v>853816</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>614</v>
+        <v>880</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>854234</v>
+        <v>855348</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>90</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>855164</v>
+        <v>854375</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>855157</v>
+        <v>855266</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>855160</v>
+        <v>854535</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>377</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855156</v>
+        <v>855386</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>377</v>
+        <v>737</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>855169</v>
+        <v>854025</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>377</v>
+        <v>614</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>855171</v>
+        <v>855359</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>377</v>
+        <v>699</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>854678</v>
+        <v>854338</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>1097</v>
+        <v>281</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>853816</v>
+        <v>854345</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
-        <v>880</v>
+        <v>281</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>853990</v>
+        <v>853715</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>854747</v>
+        <v>854069</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
       </c>
       <c r="E62">
-        <v>388</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>854375</v>
+        <v>855069</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>854773</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64">
         <v>90</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>854535</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D64" t="s">
-        <v>5</v>
-      </c>
-      <c r="E64">
-        <v>3078</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>854534</v>
+        <v>854812</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>853813</v>
+        <v>855393</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
@@ -3805,836 +3293,836 @@
     </row>
     <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>854025</v>
+        <v>855203</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>614</v>
+        <v>703</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>853939</v>
+        <v>854800</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>874</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>854452</v>
+        <v>855289</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>134</v>
+        <v>580</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>854636</v>
+        <v>854285</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>134</v>
+        <v>737</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>854640</v>
+        <v>854290</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>134</v>
+        <v>737</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>854645</v>
+        <v>854273</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>854338</v>
+        <v>854639</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>281</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>854345</v>
+        <v>854945</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>281</v>
+        <v>737</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>853715</v>
+        <v>855090</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>3092</v>
+        <v>669</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>853992</v>
+        <v>855221</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>854069</v>
+        <v>853770</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>2032</v>
+        <v>294</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>854972</v>
+        <v>854693</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>2090</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>855069</v>
+        <v>855033</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>380</v>
+        <v>723</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>854691</v>
+        <v>855108</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>854773</v>
+        <v>854315</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>854812</v>
+        <v>854320</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>855203</v>
+        <v>854301</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>703</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>854800</v>
+        <v>854306</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>853958</v>
+        <v>854312</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>855163</v>
+        <v>854310</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>675</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>854285</v>
+        <v>854216</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>737</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>854290</v>
+        <v>854756</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>737</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>854273</v>
+        <v>855211</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>737</v>
+        <v>593</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>854639</v>
+        <v>854809</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>3092</v>
+        <v>951</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>854945</v>
+        <v>854519</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>855090</v>
+        <v>854367</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>854631</v>
+        <v>854979</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>134</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>854632</v>
+        <v>854944</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>134</v>
+        <v>703</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>854654</v>
+        <v>854701</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>134</v>
+        <v>703</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>854634</v>
+        <v>854881</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>134</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>854664</v>
+        <v>854357</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>134</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>855155</v>
+        <v>855242</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>854515</v>
+        <v>855030</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>593</v>
+        <v>723</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>854709</v>
+        <v>855111</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>281</v>
+        <v>593</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>853770</v>
+        <v>854683</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>294</v>
+        <v>951</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>854693</v>
+        <v>855338</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>669</v>
+        <v>614</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>855033</v>
+        <v>854193</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>723</v>
+        <v>614</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>854620</v>
+        <v>855077</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>100</v>
+        <v>199</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>134</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>854612</v>
+        <v>855017</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>134</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>854585</v>
+        <v>854543</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>933</v>
+        <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>855108</v>
+        <v>855075</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>853973</v>
+        <v>853459</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>854315</v>
+        <v>850430</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>281</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>854320</v>
+        <v>855274</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>281</v>
+        <v>951</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>854301</v>
+        <v>854518</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>854306</v>
+        <v>854834</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>281</v>
+        <v>951</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>854312</v>
+        <v>854228</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>854310</v>
+        <v>854224</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>854216</v>
+        <v>854221</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>854756</v>
+        <v>854980</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>281</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>855211</v>
+        <v>854212</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>854809</v>
+        <v>854209</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>951</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>854519</v>
+        <v>854977</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>854367</v>
+        <v>854692</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>854979</v>
+        <v>854754</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>3078</v>
+        <v>811</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>854944</v>
+        <v>853295</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>703</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>854701</v>
+        <v>854150</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>703</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>854881</v>
+        <v>854749</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>855234</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D125" t="s">
+        <v>5</v>
+      </c>
+      <c r="E125">
         <v>699</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>854357</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D125" t="s">
-        <v>5</v>
-      </c>
-      <c r="E125">
-        <v>281</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>854607</v>
+        <v>854784</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -4645,444 +4133,444 @@
     </row>
     <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>855030</v>
+        <v>855365</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>855111</v>
+        <v>855138</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>593</v>
+        <v>294</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>854683</v>
+        <v>854992</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>951</v>
+        <v>874</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>854428</v>
+        <v>854601</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>722</v>
+        <v>90</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>853995</v>
+        <v>854702</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>854193</v>
+        <v>854689</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>614</v>
+        <v>874</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>855077</v>
+        <v>854279</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>380</v>
+        <v>737</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>854748</v>
+        <v>854151</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>703</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>853997</v>
+        <v>855056</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>854118</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D136" t="s">
+        <v>5</v>
+      </c>
+      <c r="E136">
         <v>699</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>855017</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D136" t="s">
-        <v>5</v>
-      </c>
-      <c r="E136">
-        <v>3089</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>854543</v>
+        <v>855104</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>855075</v>
+        <v>855405</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>853459</v>
+        <v>853809</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>850425</v>
+        <v>854750</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>850430</v>
+        <v>854404</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>850476</v>
+        <v>854348</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>2081</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>854518</v>
+        <v>854354</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>854834</v>
+        <v>854361</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>951</v>
+        <v>281</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>854228</v>
+        <v>854771</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>3078</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>854224</v>
+        <v>854932</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>854221</v>
+        <v>855024</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>3078</v>
+        <v>614</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>854980</v>
+        <v>854935</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>3078</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>854212</v>
+        <v>855062</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>3078</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>854209</v>
+        <v>854302</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>854207</v>
+        <v>853206</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>3078</v>
+        <v>614</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>854977</v>
+        <v>854305</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>699</v>
+        <v>574</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>854692</v>
+        <v>854263</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>642</v>
+        <v>574</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>854754</v>
+        <v>855047</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>811</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>853295</v>
+        <v>855384</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>149</v>
+        <v>17</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>2027</v>
+        <v>90</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>854013</v>
+        <v>854606</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>90</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>854150</v>
+        <v>854356</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>90</v>
+        <v>867</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>853978</v>
+        <v>854114</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -5091,264 +4579,264 @@
         <v>90</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>853834</v>
+        <v>855173</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>854749</v>
+        <v>855284</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>90</v>
+        <v>811</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>854821</v>
+        <v>853929</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>853837</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D162" t="s">
+        <v>5</v>
+      </c>
+      <c r="E162">
         <v>699</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>854784</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D162" t="s">
-        <v>5</v>
-      </c>
-      <c r="E162">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>855138</v>
+        <v>854443</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>294</v>
+        <v>377</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>855175</v>
+        <v>854387</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>854861</v>
+        <v>854112</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>951</v>
+        <v>723</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>854926</v>
+        <v>854122</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>2032</v>
+        <v>723</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>854885</v>
+        <v>854148</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>2032</v>
+        <v>723</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>854992</v>
+        <v>854319</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>874</v>
+        <v>574</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>854601</v>
+        <v>854314</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>90</v>
+        <v>574</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>854775</v>
+        <v>854807</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>854702</v>
+        <v>855392</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>854689</v>
+        <v>855051</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>874</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>854279</v>
+        <v>854999</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>854151</v>
+        <v>854267</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>90</v>
+        <v>943</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>855056</v>
+        <v>854769</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>854118</v>
+        <v>855366</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>169</v>
+        <v>223</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
-        <v>699</v>
+        <v>639</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>854002</v>
+        <v>855219</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -5357,2262 +4845,1282 @@
         <v>699</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>855104</v>
+        <v>854577</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
       <c r="E178">
-        <v>593</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>853809</v>
+        <v>853773</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="E179">
-        <v>90</v>
+        <v>377</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>854352</v>
+        <v>855230</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>377</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>854750</v>
+        <v>855279</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181">
-        <v>811</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>854404</v>
+        <v>855136</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182">
-        <v>90</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>854021</v>
+        <v>854833</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183">
-        <v>951</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>855025</v>
+        <v>855172</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
       <c r="E184">
-        <v>2088</v>
+        <v>874</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>854348</v>
+        <v>854884</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185">
-        <v>281</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>854354</v>
+        <v>854820</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>854361</v>
+        <v>854392</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187">
-        <v>281</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>854771</v>
+        <v>855315</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>854932</v>
+        <v>855065</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>699</v>
+        <v>829</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>855024</v>
+        <v>853358</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>854935</v>
+        <v>854660</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191">
-        <v>2027</v>
+        <v>737</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>854433</v>
+        <v>855229</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192">
-        <v>742</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>854434</v>
+        <v>854734</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193">
-        <v>696</v>
+        <v>874</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>855062</v>
+        <v>854084</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
       </c>
       <c r="E194">
-        <v>3072</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>854436</v>
+        <v>854942</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
       </c>
       <c r="E195">
-        <v>742</v>
+        <v>699</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>854302</v>
+        <v>855352</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
       </c>
       <c r="E196">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>853730</v>
+        <v>855001</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="D197" t="s">
         <v>5</v>
       </c>
       <c r="E197">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>853206</v>
+        <v>854347</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
       </c>
       <c r="E198">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>854305</v>
+        <v>854984</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199">
-        <v>574</v>
+        <v>90</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>854263</v>
+        <v>854712</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>855047</v>
+        <v>855091</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
       </c>
       <c r="E201">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>853720</v>
+        <v>855312</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202">
-        <v>90</v>
+        <v>811</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>854606</v>
+        <v>855395</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203">
-        <v>2032</v>
+        <v>90</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>854356</v>
+        <v>855083</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204">
-        <v>867</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>854114</v>
+        <v>855237</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="D205" t="s">
         <v>5</v>
       </c>
       <c r="E205">
-        <v>90</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>853725</v>
+        <v>855248</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="D206" t="s">
         <v>5</v>
       </c>
       <c r="E206">
-        <v>614</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>855173</v>
+        <v>854697</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D207" t="s">
         <v>5</v>
       </c>
       <c r="E207">
-        <v>722</v>
+        <v>90</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>854733</v>
+        <v>854520</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="D208" t="s">
         <v>5</v>
       </c>
       <c r="E208">
-        <v>836</v>
+        <v>90</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>845451</v>
+        <v>855275</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="D209" t="s">
         <v>5</v>
       </c>
       <c r="E209">
-        <v>1162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>853929</v>
+        <v>855258</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="D210" t="s">
         <v>5</v>
       </c>
       <c r="E210">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>853837</v>
+        <v>855079</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="D211" t="s">
         <v>5</v>
       </c>
       <c r="E211">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>854443</v>
+        <v>854964</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="D212" t="s">
         <v>5</v>
       </c>
       <c r="E212">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>854387</v>
+        <v>854695</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="D213" t="s">
         <v>5</v>
       </c>
       <c r="E213">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>854112</v>
+        <v>855119</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="D214" t="s">
         <v>5</v>
       </c>
       <c r="E214">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>854122</v>
+        <v>851354</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="D215" t="s">
         <v>5</v>
       </c>
       <c r="E215">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>854148</v>
+        <v>851356</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="D216" t="s">
         <v>5</v>
       </c>
       <c r="E216">
-        <v>723</v>
+        <v>60</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>854143</v>
+        <v>851357</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="D217" t="s">
         <v>5</v>
       </c>
       <c r="E217">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>853783</v>
+        <v>854953</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="D218" t="s">
         <v>5</v>
       </c>
       <c r="E218">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>853784</v>
+        <v>854954</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="D219" t="s">
         <v>5</v>
       </c>
       <c r="E219">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>854319</v>
+        <v>851359</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="D220" t="s">
         <v>5</v>
       </c>
       <c r="E220">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>854314</v>
+        <v>854955</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="D221" t="s">
         <v>5</v>
       </c>
       <c r="E221">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>854805</v>
+        <v>854956</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="D222" t="s">
         <v>5</v>
       </c>
       <c r="E222">
-        <v>2083</v>
+        <v>60</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>854807</v>
+        <v>844931</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>212</v>
+        <v>142</v>
       </c>
       <c r="D223" t="s">
         <v>5</v>
       </c>
       <c r="E223">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>851031</v>
+        <v>851348</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="D224" t="s">
         <v>5</v>
       </c>
       <c r="E224">
-        <v>916</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>854886</v>
+        <v>851349</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>214</v>
+        <v>144</v>
       </c>
       <c r="D225" t="s">
         <v>5</v>
       </c>
       <c r="E225">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>854993</v>
+        <v>854602</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D226" t="s">
         <v>5</v>
       </c>
       <c r="E226">
-        <v>3089</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>854723</v>
+        <v>854603</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="D227" t="s">
         <v>5</v>
       </c>
       <c r="E227">
-        <v>3089</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>855166</v>
+        <v>854604</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="D228" t="s">
         <v>5</v>
       </c>
       <c r="E228">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>855051</v>
+        <v>855261</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>18</v>
+        <v>239</v>
       </c>
       <c r="D229" t="s">
         <v>5</v>
       </c>
       <c r="E229">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>853984</v>
+        <v>854899</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="D230" t="s">
         <v>5</v>
       </c>
       <c r="E230">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>854999</v>
+        <v>855254</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="D231" t="s">
         <v>5</v>
       </c>
       <c r="E231">
-        <v>2041</v>
+        <v>906</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>854267</v>
+        <v>855272</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>220</v>
+        <v>147</v>
       </c>
       <c r="D232" t="s">
         <v>5</v>
       </c>
       <c r="E232">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>855154</v>
+        <v>855255</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="D233" t="s">
         <v>5</v>
       </c>
       <c r="E233">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>854703</v>
+        <v>855264</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
       <c r="D234" t="s">
         <v>5</v>
       </c>
       <c r="E234">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>854769</v>
+        <v>855271</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>222</v>
+        <v>148</v>
       </c>
       <c r="D235" t="s">
         <v>5</v>
       </c>
       <c r="E235">
-        <v>593</v>
+        <v>906</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>855124</v>
+        <v>853930</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="D236" t="s">
         <v>5</v>
       </c>
       <c r="E236">
-        <v>3035</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>854924</v>
+        <v>854939</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="D237" t="s">
         <v>5</v>
       </c>
       <c r="E237">
-        <v>943</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="238" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>854786</v>
+        <v>855297</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D238" t="s">
         <v>5</v>
       </c>
       <c r="E238">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>853471</v>
+        <v>854777</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
       <c r="D239" t="s">
         <v>5</v>
       </c>
       <c r="E239">
-        <v>933</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>854577</v>
+        <v>853472</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="D240" t="s">
         <v>5</v>
       </c>
       <c r="E240">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>853773</v>
+        <v>855278</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D241" t="s">
         <v>5</v>
       </c>
       <c r="E241">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>854677</v>
+        <v>852719</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="D242" t="s">
         <v>5</v>
       </c>
       <c r="E242">
-        <v>3045</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>855136</v>
+        <v>852720</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>230</v>
+        <v>154</v>
       </c>
       <c r="D243" t="s">
         <v>5</v>
       </c>
       <c r="E243">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>854970</v>
+        <v>853734</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="D244" t="s">
         <v>5</v>
       </c>
       <c r="E244">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>854833</v>
+        <v>853738</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="D245" t="s">
         <v>5</v>
       </c>
       <c r="E245">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>855172</v>
+        <v>854686</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D246" t="s">
         <v>5</v>
       </c>
       <c r="E246">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>854884</v>
+        <v>852752</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="D247" t="s">
         <v>5</v>
       </c>
       <c r="E247">
-        <v>1097</v>
+        <v>979</v>
       </c>
     </row>
     <row r="248" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>854788</v>
+        <v>855374</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="D248" t="s">
         <v>5</v>
       </c>
       <c r="E248">
-        <v>3060</v>
+        <v>293</v>
       </c>
     </row>
     <row r="249" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>854820</v>
+        <v>854925</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>236</v>
+        <v>17</v>
       </c>
       <c r="D249" t="s">
         <v>5</v>
       </c>
       <c r="E249">
-        <v>967</v>
+        <v>904</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>854392</v>
+        <v>852562</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="D250" t="s">
         <v>5</v>
       </c>
       <c r="E250">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>854947</v>
+        <v>854724</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D251" t="s">
         <v>5</v>
       </c>
       <c r="E251">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>855065</v>
+        <v>855382</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D252" t="s">
         <v>5</v>
       </c>
       <c r="E252">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>853358</v>
+        <v>855400</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D253" t="s">
         <v>5</v>
       </c>
       <c r="E253">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>854660</v>
+        <v>855045</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="D254" t="s">
         <v>5</v>
       </c>
       <c r="E254">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>855107</v>
+        <v>848786</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D255" t="s">
         <v>5</v>
       </c>
       <c r="E255">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>854734</v>
+        <v>854889</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="D256" t="s">
         <v>5</v>
       </c>
       <c r="E256">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>854084</v>
+        <v>855355</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D257" t="s">
         <v>5</v>
       </c>
       <c r="E257">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>854942</v>
+        <v>854839</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c r="D258" t="s">
         <v>5</v>
       </c>
       <c r="E258">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>855092</v>
+        <v>854658</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>245</v>
+        <v>163</v>
       </c>
       <c r="D259" t="s">
         <v>5</v>
       </c>
       <c r="E259">
-        <v>3060</v>
+        <v>851</v>
       </c>
     </row>
     <row r="260" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>855073</v>
+        <v>854830</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D260" t="s">
         <v>5</v>
       </c>
       <c r="E260">
-        <v>966</v>
+        <v>851</v>
       </c>
     </row>
     <row r="261" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>855001</v>
+        <v>854832</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D261" t="s">
         <v>5</v>
       </c>
       <c r="E261">
-        <v>874</v>
+        <v>851</v>
       </c>
     </row>
     <row r="262" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>854347</v>
+        <v>854835</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D262" t="s">
         <v>5</v>
       </c>
       <c r="E262">
-        <v>967</v>
+        <v>851</v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>854984</v>
+        <v>854051</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>246</v>
+        <v>164</v>
       </c>
       <c r="D263" t="s">
         <v>5</v>
       </c>
       <c r="E263">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>854712</v>
+        <v>855137</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>247</v>
+        <v>165</v>
       </c>
       <c r="D264" t="s">
         <v>5</v>
       </c>
       <c r="E264">
-        <v>3034</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>854022</v>
+        <v>854629</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="D265" t="s">
         <v>5</v>
       </c>
       <c r="E265">
-        <v>3060</v>
+        <v>293</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>855091</v>
+        <v>855310</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D266" t="s">
         <v>5</v>
       </c>
       <c r="E266">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>854988</v>
+        <v>854579</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="D267" t="s">
         <v>5</v>
       </c>
       <c r="E267">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>855083</v>
+        <v>852886</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="D268" t="s">
         <v>5</v>
       </c>
       <c r="E268">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A269">
-        <v>854697</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D269" t="s">
-        <v>5</v>
-      </c>
-      <c r="E269">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A270">
-        <v>854675</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D270" t="s">
-        <v>5</v>
-      </c>
-      <c r="E270">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A271">
-        <v>854520</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D271" t="s">
-        <v>5</v>
-      </c>
-      <c r="E271">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A272">
-        <v>855079</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D272" t="s">
-        <v>5</v>
-      </c>
-      <c r="E272">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A273">
-        <v>854964</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D273" t="s">
-        <v>5</v>
-      </c>
-      <c r="E273">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A274">
-        <v>854695</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D274" t="s">
-        <v>5</v>
-      </c>
-      <c r="E274">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A275">
-        <v>855119</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D275" t="s">
-        <v>5</v>
-      </c>
-      <c r="E275">
-        <v>3055</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A276">
-        <v>855099</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D276" t="s">
-        <v>5</v>
-      </c>
-      <c r="E276">
-        <v>3055</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A277">
-        <v>851354</v>
-      </c>
-      <c r="B277" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D277" t="s">
-        <v>5</v>
-      </c>
-      <c r="E277">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A278">
-        <v>851356</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D278" t="s">
-        <v>5</v>
-      </c>
-      <c r="E278">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A279">
-        <v>851357</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D279" t="s">
-        <v>5</v>
-      </c>
-      <c r="E279">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A280">
-        <v>854953</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D280" t="s">
-        <v>5</v>
-      </c>
-      <c r="E280">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A281">
-        <v>854954</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D281" t="s">
-        <v>5</v>
-      </c>
-      <c r="E281">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A282">
-        <v>851359</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D282" t="s">
-        <v>5</v>
-      </c>
-      <c r="E282">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A283">
-        <v>854955</v>
-      </c>
-      <c r="B283" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D283" t="s">
-        <v>5</v>
-      </c>
-      <c r="E283">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A284">
-        <v>854956</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D284" t="s">
-        <v>5</v>
-      </c>
-      <c r="E284">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A285">
-        <v>844931</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D285" t="s">
-        <v>5</v>
-      </c>
-      <c r="E285">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A286">
-        <v>851348</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D286" t="s">
-        <v>5</v>
-      </c>
-      <c r="E286">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A287">
-        <v>851349</v>
-      </c>
-      <c r="B287" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D287" t="s">
-        <v>5</v>
-      </c>
-      <c r="E287">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A288">
-        <v>854602</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D288" t="s">
-        <v>5</v>
-      </c>
-      <c r="E288">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A289">
-        <v>854603</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D289" t="s">
-        <v>5</v>
-      </c>
-      <c r="E289">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A290">
-        <v>854604</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D290" t="s">
-        <v>5</v>
-      </c>
-      <c r="E290">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A291">
-        <v>854899</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D291" t="s">
-        <v>5</v>
-      </c>
-      <c r="E291">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A292">
-        <v>854901</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D292" t="s">
-        <v>5</v>
-      </c>
-      <c r="E292">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A293">
-        <v>853930</v>
-      </c>
-      <c r="B293" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D293" t="s">
-        <v>5</v>
-      </c>
-      <c r="E293">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A294">
-        <v>854939</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D294" t="s">
-        <v>5</v>
-      </c>
-      <c r="E294">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A295">
-        <v>854777</v>
-      </c>
-      <c r="B295" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D295" t="s">
-        <v>5</v>
-      </c>
-      <c r="E295">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A296">
-        <v>848533</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D296" t="s">
-        <v>5</v>
-      </c>
-      <c r="E296">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A297">
-        <v>854837</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D297" t="s">
-        <v>5</v>
-      </c>
-      <c r="E297">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A298">
-        <v>853472</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D298" t="s">
-        <v>5</v>
-      </c>
-      <c r="E298">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A299">
-        <v>854995</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D299" t="s">
-        <v>5</v>
-      </c>
-      <c r="E299">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A300">
-        <v>852605</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D300" t="s">
-        <v>5</v>
-      </c>
-      <c r="E300">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A301">
-        <v>852719</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D301" t="s">
-        <v>5</v>
-      </c>
-      <c r="E301">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A302">
-        <v>852720</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D302" t="s">
-        <v>5</v>
-      </c>
-      <c r="E302">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A303">
-        <v>853734</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D303" t="s">
-        <v>5</v>
-      </c>
-      <c r="E303">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A304">
-        <v>853738</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D304" t="s">
-        <v>5</v>
-      </c>
-      <c r="E304">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A305">
-        <v>854686</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D305" t="s">
-        <v>5</v>
-      </c>
-      <c r="E305">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A306">
-        <v>852752</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D306" t="s">
-        <v>5</v>
-      </c>
-      <c r="E306">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A307">
-        <v>855016</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D307" t="s">
-        <v>5</v>
-      </c>
-      <c r="E307">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A308">
-        <v>854175</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D308" t="s">
-        <v>5</v>
-      </c>
-      <c r="E308">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A309">
-        <v>854925</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D309" t="s">
-        <v>5</v>
-      </c>
-      <c r="E309">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A310">
-        <v>855020</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D310" t="s">
-        <v>5</v>
-      </c>
-      <c r="E310">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A311">
-        <v>852562</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D311" t="s">
-        <v>5</v>
-      </c>
-      <c r="E311">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A312">
-        <v>854960</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D312" t="s">
-        <v>5</v>
-      </c>
-      <c r="E312">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A313">
-        <v>855037</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D313" t="s">
-        <v>5</v>
-      </c>
-      <c r="E313">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A314">
-        <v>855058</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D314" t="s">
-        <v>5</v>
-      </c>
-      <c r="E314">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A315">
-        <v>853898</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D315" t="s">
-        <v>5</v>
-      </c>
-      <c r="E315">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A316">
-        <v>854724</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D316" t="s">
-        <v>5</v>
-      </c>
-      <c r="E316">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A317">
-        <v>854713</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D317" t="s">
-        <v>5</v>
-      </c>
-      <c r="E317">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A318">
-        <v>854727</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D318" t="s">
-        <v>5</v>
-      </c>
-      <c r="E318">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A319">
-        <v>855061</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D319" t="s">
-        <v>5</v>
-      </c>
-      <c r="E319">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A320">
-        <v>855045</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D320" t="s">
-        <v>5</v>
-      </c>
-      <c r="E320">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A321">
-        <v>848786</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D321" t="s">
-        <v>5</v>
-      </c>
-      <c r="E321">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A322">
-        <v>853703</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D322" t="s">
-        <v>5</v>
-      </c>
-      <c r="E322">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A323">
-        <v>854889</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D323" t="s">
-        <v>5</v>
-      </c>
-      <c r="E323">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A324">
-        <v>853599</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D324" t="s">
-        <v>5</v>
-      </c>
-      <c r="E324">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A325">
-        <v>854718</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D325" t="s">
-        <v>5</v>
-      </c>
-      <c r="E325">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A326">
-        <v>854839</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D326" t="s">
-        <v>5</v>
-      </c>
-      <c r="E326">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A327">
-        <v>854658</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D327" t="s">
-        <v>5</v>
-      </c>
-      <c r="E327">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A328">
-        <v>854830</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D328" t="s">
-        <v>5</v>
-      </c>
-      <c r="E328">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A329">
-        <v>854832</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D329" t="s">
-        <v>5</v>
-      </c>
-      <c r="E329">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A330">
-        <v>854835</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D330" t="s">
-        <v>5</v>
-      </c>
-      <c r="E330">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A331">
-        <v>854051</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D331" t="s">
-        <v>5</v>
-      </c>
-      <c r="E331">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A332">
-        <v>855137</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D332" t="s">
-        <v>5</v>
-      </c>
-      <c r="E332">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A333">
-        <v>854629</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D333" t="s">
-        <v>5</v>
-      </c>
-      <c r="E333">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A334">
-        <v>854579</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D334" t="s">
-        <v>5</v>
-      </c>
-      <c r="E334">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A335">
-        <v>852886</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D335" t="s">
-        <v>5</v>
-      </c>
-      <c r="E335">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A336">
-        <v>850426</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D336" t="s">
-        <v>5</v>
-      </c>
-      <c r="E336">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A337">
-        <v>850431</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D337" t="s">
-        <v>5</v>
-      </c>
-      <c r="E337">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A338">
-        <v>850436</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D338" t="s">
-        <v>5</v>
-      </c>
-      <c r="E338">
-        <v>2081</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E321" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}"/>
+  <autoFilter ref="A1:E268" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFE388A9-D8C4-4C2E-AC5C-336FECE73A54}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B8A4293-332F-4170-B3BB-D28530771A17}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$233</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="211">
   <si>
     <t>Pedido</t>
   </si>
@@ -281,14 +281,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.563,64_x000D_
-• Valor em ruptura: R$ 1.135,17_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.773,46_x000D_
 • Valor em ruptura: R$ 2.076,65_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
@@ -318,14 +310,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.576,07_x000D_
-• Valor em ruptura: R$ 2.669,92_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -337,14 +321,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.012,86_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.645,60_x000D_
 • Valor em ruptura: R$ 1.427,70_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -369,73 +345,9 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 119,55_x000D_
-• Valor em ruptura: R$ 31.755,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.427,37_x000D_
-• Valor em ruptura: R$ 4.144,07_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.072,61_x000D_
-• Valor em ruptura: R$ 2.247,55_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 13.143,06_x000D_
-• Valor em ruptura: R$ 6.492,90_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.794,25_x000D_
-• Valor em ruptura: R$ 2.164,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.567,33_x000D_
-• Valor em ruptura: R$ 2.645,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.106,86_x000D_
 • Valor em ruptura: R$ 22.560,96_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.683,45_x000D_
-• Valor em ruptura: R$ 1.666,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 13.311,22_x000D_
-• Valor em ruptura: R$ 480,96_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -446,14 +358,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.838,34_x000D_
-• Valor em ruptura: R$ 480,96_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -465,51 +369,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.919,41_x000D_
-• Valor em ruptura: R$ 2.700,94_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.963,01_x000D_
-• Valor em ruptura: R$ 2.327,99_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.017,86_x000D_
-• Valor em ruptura: R$ 824,56_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 717,96_x000D_
-• Valor em ruptura: R$ 921,43_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.528,03_x000D_
 • Valor em ruptura: R$ 339,44_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.393,34_x000D_
-• Valor em ruptura: R$ 242,56_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -524,14 +388,6 @@
 • Valor em estoque: R$ 1.014,62_x000D_
 • Valor em ruptura: R$ 2.376,06_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.765,94_x000D_
-• Valor em ruptura: R$ 2.028,76_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -582,14 +438,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 16.052,57_x000D_
-• Valor em ruptura: R$ 13.697,05_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -601,14 +449,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.896,84_x000D_
-• Valor em ruptura: R$ 1.190,37_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.383,60_x000D_
 • Valor em ruptura: R$ 207,02_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -630,14 +470,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.386,39_x000D_
-• Valor em ruptura: R$ 1.267,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -657,49 +489,9 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.937,64_x000D_
-• Valor em ruptura: R$ 9.432,57_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.672,35_x000D_
-• Valor em ruptura: R$ 7.074,42_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 6.554,12_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 557,45_x000D_
-• Valor em ruptura: R$ 1.886,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 448,07_x000D_
-• Valor em ruptura: R$ 1.886,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 937,74_x000D_
-• Valor em ruptura: R$ 5.580,87_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -713,22 +505,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 357,25_x000D_
-• Valor em ruptura: R$ 2.224,93_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.652,75_x000D_
-• Valor em ruptura: R$ 7.279,40_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
@@ -742,30 +518,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 610,63_x000D_
-• Valor em ruptura: R$ 1.756,06_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.259,60_x000D_
-• Valor em ruptura: R$ 2.645,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.353,31_x000D_
-• Valor em ruptura: R$ 2.243,83_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -779,14 +531,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.514,89_x000D_
 • Valor em ruptura: R$ 977,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.918,98_x000D_
-• Valor em ruptura: R$ 1.112,47_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -830,14 +574,6 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.683,49_x000D_
-• Valor em ruptura: R$ 92.386,96_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -854,36 +590,12 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.774,90_x000D_
-• Valor em ruptura: R$ 2.100,55_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.337,69_x000D_
-• Valor em ruptura: R$ 36.831,92_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 693,34_x000D_
 • Valor em ruptura: R$ 1.624,39_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 75.424,40_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -937,38 +649,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 979,40_x000D_
-• Valor em ruptura: R$ 3.491,80_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.851,21_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.229,66_x000D_
-• Valor em ruptura: R$ 1.267,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.154,05_x000D_
-• Valor em ruptura: R$ 7.896,53_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 221,48_x000D_
 • Valor em ruptura: R$ 519,16_x000D_
 • Valor mínimo de frete: R$ 5.150,00</t>
@@ -998,14 +678,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 6.133,16_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1017,14 +689,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.084,88_x000D_
-• Valor em ruptura: R$ 2.404,78_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 588,41_x000D_
 • Valor em ruptura: R$ 2.645,50_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1033,14 +697,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 662,67_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 2.508,66_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1057,38 +713,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.736,04_x000D_
-• Valor em ruptura: R$ 2.765,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.039,56_x000D_
-• Valor em ruptura: R$ 5.006,80_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 541,90_x000D_
-• Valor em ruptura: R$ 3.333,02_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.790,28_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.140,94_x000D_
 • Valor em ruptura: R$ 1.587,30_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1234,14 +858,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.654,58_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 38.762,66_x000D_
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
@@ -1286,14 +902,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.299,24_x000D_
-• Valor em ruptura: R$ 257,60_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1322,14 +930,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 44.044,57_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 142.341,65_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -1339,14 +939,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 12.872,38_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 19.255,88_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
@@ -1478,14 +1070,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.186,15_x000D_
-• Valor em ruptura: R$ 3.742,73_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1507,14 +1091,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.093,04_x000D_
 • Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.436,64_x000D_
-• Valor em ruptura: R$ 1.491,64_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1638,14 +1214,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.985,97_x000D_
-• Valor em ruptura: R$ 3.167,76_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1686,30 +1254,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.200,42_x000D_
-• Valor em ruptura: R$ 2.190,29_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.050,63_x000D_
-• Valor em ruptura: R$ 5.340,53_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.586,66_x000D_
-• Valor em ruptura: R$ 1.941,17_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1766,14 +1310,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.444,00_x000D_
-• Valor em ruptura: R$ 10.653,20_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1782,14 +1318,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.038,86_x000D_
-• Valor em ruptura: R$ 240,48_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1804,22 +1332,6 @@
 • Valor em estoque: R$ 6.836,90_x000D_
 • Valor em ruptura: R$ 8.893,74_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.021,40_x000D_
-• Valor em ruptura: R$ 1.202,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.585,36_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -1862,22 +1374,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.615,50_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.201,21_x000D_
-• Valor em ruptura: R$ 2.164,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1897,14 +1393,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.432,78_x000D_
-• Valor em ruptura: R$ 1.229,24_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.198,78_x000D_
 • Valor em ruptura: R$ 250,87_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1980,6 +1468,238 @@
 • Valor em estoque: R$ 3.057,80_x000D_
 • Valor em ruptura: R$ 4.102,09_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.849,52_x000D_
+• Valor em ruptura: R$ 3.877,52_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.920,57_x000D_
+• Valor em ruptura: R$ 3.106,20_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.590,93_x000D_
+• Valor em ruptura: R$ 1.337,95_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.667,85_x000D_
+• Valor em ruptura: R$ 3.903,59_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.034,52_x000D_
+• Valor em ruptura: R$ 1.285,64_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.891,37_x000D_
+• Valor em ruptura: R$ 1.036,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.404,53_x000D_
+• Valor em ruptura: R$ 2.215,82_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.933,25_x000D_
+• Valor em ruptura: R$ 1.357,75_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.502,98_x000D_
+• Valor em ruptura: R$ 339,44_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 960,52_x000D_
+• Valor em ruptura: R$ 678,87_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.398,03_x000D_
+• Valor em ruptura: R$ 813,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.555,67_x000D_
+• Valor em ruptura: R$ 296,81_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 28.711,30_x000D_
+• Valor em ruptura: R$ 1.038,32_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.315,20_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.150,27_x000D_
+• Valor em ruptura: R$ 1.003,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.848,40_x000D_
+• Valor em ruptura: R$ 542,31_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 296,81_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 94.126,89_x000D_
+• Valor em ruptura: R$ 943,56_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.015,38_x000D_
+• Valor em ruptura: R$ 1.860,07_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.870,32_x000D_
+• Valor em ruptura: R$ 9.226,88_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.192,63_x000D_
+• Valor em ruptura: R$ 2.278,57_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.353,51_x000D_
+• Valor em ruptura: R$ 5.540,62_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.170,95_x000D_
+• Valor em ruptura: R$ 1.605,54_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.395,85_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.920,53_x000D_
+• Valor em ruptura: R$ 1.125,83_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.535,95_x000D_
+• Valor em ruptura: R$ 1.254,33_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 367,70_x000D_
+• Valor em ruptura: R$ 3.668,92_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 644,47_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 927,80_x000D_
+• Valor em ruptura: R$ 2.400,30_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
 </sst>
 </file>
@@ -2355,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -2383,94 +2103,94 @@
     </row>
     <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>853850</v>
+        <v>854080</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>773</v>
+        <v>580</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>853854</v>
+        <v>855293</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>773</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>853926</v>
+        <v>855426</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>773</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>853853</v>
+        <v>855374</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>773</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>850631</v>
+        <v>853850</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>147</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>855347</v>
+        <v>853854</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>134</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>853943</v>
+        <v>853926</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -2481,416 +2201,416 @@
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>855177</v>
+        <v>853853</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>2078</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>853849</v>
+        <v>850631</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>1021</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>853567</v>
+        <v>855347</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>3060</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>854781</v>
+        <v>853943</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>3093</v>
+        <v>773</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>848783</v>
+        <v>855177</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>3075</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>853426</v>
+        <v>853849</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>3075</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>854985</v>
+        <v>853567</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>2090</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>854061</v>
+        <v>854781</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>589</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>849811</v>
+        <v>848783</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>3058</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>855293</v>
+        <v>853426</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>2072</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>849918</v>
+        <v>854985</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>750</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>855268</v>
+        <v>854061</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>2083</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>849917</v>
+        <v>855423</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>3089</v>
+        <v>951</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>850200</v>
+        <v>849811</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>1021</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>852593</v>
+        <v>855295</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>632</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>852631</v>
+        <v>849918</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>3085</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>853998</v>
+        <v>855268</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>722</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>855341</v>
+        <v>849917</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>3029</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>853852</v>
+        <v>850200</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>773</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>854933</v>
+        <v>852593</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>983</v>
+        <v>632</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>854931</v>
+        <v>852631</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>983</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>854237</v>
+        <v>853998</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>773</v>
+        <v>722</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>854585</v>
+        <v>855341</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>933</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>855295</v>
+        <v>853852</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>377</v>
+        <v>773</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>854330</v>
+        <v>854933</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>281</v>
+        <v>983</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>855330</v>
+        <v>854931</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>854385</v>
+        <v>854237</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>2090</v>
+        <v>773</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>855232</v>
+        <v>854585</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>2084</v>
+        <v>933</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>854374</v>
+        <v>854330</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>3069</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>854940</v>
+        <v>855330</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2899,138 +2619,138 @@
         <v>703</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>855052</v>
+        <v>854385</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
-        <v>380</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>854415</v>
+        <v>855232</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40">
-        <v>703</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>854840</v>
+        <v>854374</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>642</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>855159</v>
+        <v>854940</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>614</v>
+        <v>703</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>855376</v>
+        <v>855052</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>1021</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>855350</v>
+        <v>854415</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44">
-        <v>614</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>854934</v>
+        <v>854840</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>2064</v>
+        <v>642</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>854891</v>
+        <v>855159</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>2051</v>
+        <v>614</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>854250</v>
+        <v>855376</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>90</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>853913</v>
+        <v>855350</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -3041,66 +2761,66 @@
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>855357</v>
+        <v>854934</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>182</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>699</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>854234</v>
+        <v>854891</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50">
-        <v>90</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>853816</v>
+        <v>853913</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>880</v>
+        <v>614</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>855348</v>
+        <v>855357</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>134</v>
+        <v>699</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>854375</v>
+        <v>854234</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -3109,37 +2829,37 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>855266</v>
+        <v>853816</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>380</v>
+        <v>880</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>854535</v>
+        <v>855348</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>3078</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855386</v>
+        <v>855266</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>184</v>
@@ -3148,57 +2868,57 @@
         <v>5</v>
       </c>
       <c r="E56">
-        <v>737</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>854025</v>
+        <v>854535</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>614</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>855359</v>
+        <v>855386</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>699</v>
+        <v>737</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>854338</v>
+        <v>855359</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>281</v>
+        <v>699</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>854345</v>
+        <v>854338</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -3209,30 +2929,30 @@
     </row>
     <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A61">
+        <v>854345</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>853715</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61">
+      <c r="B62" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62">
         <v>3092</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>854069</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62">
-        <v>2032</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
@@ -3240,7 +2960,7 @@
         <v>855069</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
@@ -3254,7 +2974,7 @@
         <v>854773</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
@@ -3268,7 +2988,7 @@
         <v>854812</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
@@ -3296,7 +3016,7 @@
         <v>855203</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -3310,7 +3030,7 @@
         <v>854800</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
@@ -3324,7 +3044,7 @@
         <v>855289</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
@@ -3333,166 +3053,166 @@
         <v>580</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>854285</v>
+        <v>854639</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>737</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>854290</v>
+        <v>855221</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>737</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>854273</v>
+        <v>853770</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>854639</v>
+        <v>855033</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>3092</v>
+        <v>723</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>854945</v>
+        <v>855108</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>737</v>
+        <v>593</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>855090</v>
+        <v>854315</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>669</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>855221</v>
+        <v>854320</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>1027</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>853770</v>
+        <v>854301</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>854693</v>
+        <v>854306</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>669</v>
+        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>855033</v>
+        <v>854312</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>723</v>
+        <v>281</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>855108</v>
+        <v>854216</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>593</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>854315</v>
+        <v>854756</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
@@ -3503,612 +3223,612 @@
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>854320</v>
+        <v>855211</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>854301</v>
+        <v>854809</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>854306</v>
+        <v>854367</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>854312</v>
+        <v>854979</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>281</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>854310</v>
+        <v>854944</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>854216</v>
+        <v>854701</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>1027</v>
+        <v>703</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>854756</v>
+        <v>854881</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>281</v>
+        <v>699</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>855211</v>
+        <v>854357</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>854809</v>
+        <v>855242</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>951</v>
+        <v>380</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>854519</v>
+        <v>855030</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>855111</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D92" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92">
         <v>593</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>854367</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D92" t="s">
-        <v>5</v>
-      </c>
-      <c r="E92">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>854979</v>
+        <v>854683</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>194</v>
+        <v>52</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>3078</v>
+        <v>951</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>854944</v>
+        <v>855338</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>703</v>
+        <v>614</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>854701</v>
+        <v>854428</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>703</v>
+        <v>722</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>854881</v>
+        <v>854193</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>699</v>
+        <v>614</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>854357</v>
+        <v>855077</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>855242</v>
+        <v>855421</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>380</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>855030</v>
+        <v>855017</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>723</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>855111</v>
+        <v>855075</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>854683</v>
+        <v>853459</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>855338</v>
+        <v>850430</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>614</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>854193</v>
+        <v>855274</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>855077</v>
+        <v>854834</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>380</v>
+        <v>951</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>855017</v>
+        <v>854228</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>3089</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>854543</v>
+        <v>854980</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>380</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>855075</v>
+        <v>854977</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>853459</v>
+        <v>854692</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>850430</v>
+        <v>853295</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>2081</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>855274</v>
+        <v>854749</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>951</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>854518</v>
+        <v>855234</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>854834</v>
+        <v>855365</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>854228</v>
+        <v>855138</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>854224</v>
+        <v>854992</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>3078</v>
+        <v>874</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>854221</v>
+        <v>854702</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>854980</v>
+        <v>854689</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>3078</v>
+        <v>874</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>854212</v>
+        <v>855056</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>854209</v>
+        <v>854118</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>3078</v>
+        <v>699</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>854977</v>
+        <v>855104</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>699</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>854692</v>
+        <v>853809</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>201</v>
+        <v>64</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>854754</v>
+        <v>854348</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>811</v>
+        <v>281</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>853295</v>
+        <v>854354</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>2027</v>
+        <v>281</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>854150</v>
+        <v>854361</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>854749</v>
+        <v>854771</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>90</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>855234</v>
+        <v>854932</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -4119,1396 +3839,1396 @@
     </row>
     <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>854784</v>
+        <v>855024</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>855365</v>
+        <v>854935</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>855138</v>
+        <v>855062</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>294</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>854992</v>
+        <v>854028</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>874</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>854601</v>
+        <v>854302</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>854702</v>
+        <v>853206</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>703</v>
+        <v>614</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>854689</v>
+        <v>854305</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>874</v>
+        <v>574</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>854279</v>
+        <v>854263</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>737</v>
+        <v>574</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>854151</v>
+        <v>855047</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>90</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>855056</v>
+        <v>855384</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>854118</v>
+        <v>854606</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>699</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>855104</v>
+        <v>854356</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>855405</v>
+        <v>855173</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>853809</v>
+        <v>855284</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>90</v>
+        <v>811</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>854750</v>
+        <v>853929</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>211</v>
+        <v>72</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>811</v>
+        <v>722</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>854404</v>
+        <v>854443</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>90</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>854348</v>
+        <v>854387</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>854354</v>
+        <v>854112</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>281</v>
+        <v>723</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>854361</v>
+        <v>854122</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>281</v>
+        <v>723</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>854771</v>
+        <v>854148</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>854932</v>
+        <v>854319</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>699</v>
+        <v>574</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>855024</v>
+        <v>854314</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>854935</v>
+        <v>854807</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>855062</v>
+        <v>855051</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>3072</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>854302</v>
+        <v>854999</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>853206</v>
+        <v>854924</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>614</v>
+        <v>943</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>854305</v>
+        <v>855366</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>574</v>
+        <v>639</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>854263</v>
+        <v>853773</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>574</v>
+        <v>377</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>855047</v>
+        <v>855428</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>1021</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>855384</v>
+        <v>855279</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>90</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>854606</v>
+        <v>855136</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>2032</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>854356</v>
+        <v>854833</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>867</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>854114</v>
+        <v>855172</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>90</v>
+        <v>874</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>855173</v>
+        <v>855437</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>855284</v>
+        <v>854884</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>811</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>853929</v>
+        <v>854820</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>853837</v>
+        <v>855315</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>699</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>854443</v>
+        <v>855065</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>377</v>
+        <v>829</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>854387</v>
+        <v>853358</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>854112</v>
+        <v>855229</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>723</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>854122</v>
+        <v>854734</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>723</v>
+        <v>874</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>854148</v>
+        <v>854942</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>723</v>
+        <v>699</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>854319</v>
+        <v>855352</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>574</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>854314</v>
+        <v>855001</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>574</v>
+        <v>874</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>854807</v>
+        <v>854347</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>220</v>
+        <v>17</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>855392</v>
+        <v>854984</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>221</v>
+        <v>86</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>855051</v>
+        <v>855091</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>3078</v>
+        <v>281</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>854999</v>
+        <v>855083</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>854267</v>
+        <v>854697</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>943</v>
+        <v>90</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>854769</v>
+        <v>855275</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>593</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>855366</v>
+        <v>855258</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
-        <v>639</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>855219</v>
+        <v>855079</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
       <c r="E177">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>854577</v>
+        <v>854695</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>118</v>
+        <v>207</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
       <c r="E178">
-        <v>3037</v>
+        <v>380</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>853773</v>
+        <v>855119</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="E179">
-        <v>377</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>855230</v>
+        <v>855186</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>3034</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>855279</v>
+        <v>851354</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>855136</v>
+        <v>851356</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>854833</v>
+        <v>851357</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>855172</v>
+        <v>854953</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
       <c r="E184">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>854884</v>
+        <v>854954</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>854820</v>
+        <v>851359</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186">
-        <v>967</v>
+        <v>60</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>854392</v>
+        <v>854955</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>855315</v>
+        <v>854956</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188">
-        <v>3034</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>855065</v>
+        <v>844931</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>229</v>
+        <v>95</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>853358</v>
+        <v>851348</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>854660</v>
+        <v>851349</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>855229</v>
+        <v>854602</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>854734</v>
+        <v>854603</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>854084</v>
+        <v>854604</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
       </c>
       <c r="E194">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>854942</v>
+        <v>855261</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
       </c>
       <c r="E195">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>855352</v>
+        <v>854899</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
       </c>
       <c r="E196">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>855001</v>
+        <v>855254</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="D197" t="s">
         <v>5</v>
       </c>
       <c r="E197">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>854347</v>
+        <v>855272</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
       </c>
       <c r="E198">
-        <v>967</v>
+        <v>906</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>854984</v>
+        <v>855255</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>854712</v>
+        <v>855264</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200">
-        <v>3034</v>
+        <v>906</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>855091</v>
+        <v>855271</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
       </c>
       <c r="E201">
-        <v>281</v>
+        <v>906</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>855312</v>
+        <v>855436</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202">
-        <v>811</v>
+        <v>906</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>855395</v>
+        <v>855438</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>855083</v>
+        <v>853930</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>233</v>
+        <v>102</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>855237</v>
+        <v>854939</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="D205" t="s">
         <v>5</v>
       </c>
       <c r="E205">
-        <v>3060</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>855248</v>
+        <v>855297</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="D206" t="s">
         <v>5</v>
       </c>
       <c r="E206">
-        <v>3060</v>
+        <v>381</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>854697</v>
+        <v>855345</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>234</v>
+        <v>17</v>
       </c>
       <c r="D207" t="s">
         <v>5</v>
       </c>
       <c r="E207">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>854520</v>
+        <v>854777</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="D208" t="s">
         <v>5</v>
       </c>
       <c r="E208">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>855275</v>
+        <v>855278</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="D209" t="s">
         <v>5</v>
       </c>
       <c r="E209">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>855258</v>
+        <v>852719</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="D210" t="s">
         <v>5</v>
       </c>
       <c r="E210">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>855079</v>
+        <v>852720</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>238</v>
+        <v>106</v>
       </c>
       <c r="D211" t="s">
         <v>5</v>
       </c>
       <c r="E211">
-        <v>703</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>854964</v>
+        <v>853734</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D212" t="s">
         <v>5</v>
       </c>
       <c r="E212">
-        <v>737</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>854695</v>
+        <v>853738</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="D213" t="s">
         <v>5</v>
       </c>
       <c r="E213">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>855119</v>
+        <v>854686</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="D214" t="s">
         <v>5</v>
       </c>
       <c r="E214">
-        <v>3055</v>
+        <v>118</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>851354</v>
+        <v>852752</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="D215" t="s">
         <v>5</v>
       </c>
       <c r="E215">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>851356</v>
+        <v>854925</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="D216" t="s">
         <v>5</v>
       </c>
       <c r="E216">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>851357</v>
+        <v>855424</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="D217" t="s">
         <v>5</v>
       </c>
       <c r="E217">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>854953</v>
+        <v>852562</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="D218" t="s">
         <v>5</v>
       </c>
       <c r="E218">
-        <v>60</v>
+        <v>979</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>854954</v>
+        <v>854724</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D219" t="s">
         <v>5</v>
       </c>
       <c r="E219">
-        <v>60</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="220" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>851359</v>
+        <v>855382</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="D220" t="s">
         <v>5</v>
       </c>
       <c r="E220">
-        <v>60</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>854955</v>
+        <v>855400</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
         <v>5</v>
       </c>
       <c r="E221">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>854956</v>
+        <v>848786</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="D222" t="s">
         <v>5</v>
       </c>
       <c r="E222">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>844931</v>
+        <v>854889</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="D223" t="s">
         <v>5</v>
       </c>
       <c r="E223">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>851348</v>
+        <v>855355</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="D224" t="s">
         <v>5</v>
       </c>
       <c r="E224">
-        <v>60</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>851349</v>
+        <v>854839</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="D225" t="s">
         <v>5</v>
@@ -5517,610 +5237,120 @@
         <v>60</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>854602</v>
+        <v>854830</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="D226" t="s">
         <v>5</v>
       </c>
       <c r="E226">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>854603</v>
+        <v>854832</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="D227" t="s">
         <v>5</v>
       </c>
       <c r="E227">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>854604</v>
+        <v>854835</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="D228" t="s">
         <v>5</v>
       </c>
       <c r="E228">
-        <v>60</v>
+        <v>851</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>855261</v>
+        <v>854051</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>239</v>
+        <v>114</v>
       </c>
       <c r="D229" t="s">
         <v>5</v>
       </c>
       <c r="E229">
-        <v>906</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>854899</v>
+        <v>855137</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="D230" t="s">
         <v>5</v>
       </c>
       <c r="E230">
-        <v>906</v>
+        <v>375</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>855254</v>
+        <v>855310</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="D231" t="s">
         <v>5</v>
       </c>
       <c r="E231">
-        <v>906</v>
+        <v>293</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>855272</v>
+        <v>854579</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="D232" t="s">
         <v>5</v>
       </c>
       <c r="E232">
-        <v>906</v>
+        <v>996</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>855255</v>
+        <v>852886</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="D233" t="s">
         <v>5</v>
       </c>
       <c r="E233">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A234">
-        <v>855264</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D234" t="s">
-        <v>5</v>
-      </c>
-      <c r="E234">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A235">
-        <v>855271</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D235" t="s">
-        <v>5</v>
-      </c>
-      <c r="E235">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A236">
-        <v>853930</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D236" t="s">
-        <v>5</v>
-      </c>
-      <c r="E236">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A237">
-        <v>854939</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D237" t="s">
-        <v>5</v>
-      </c>
-      <c r="E237">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A238">
-        <v>855297</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D238" t="s">
-        <v>5</v>
-      </c>
-      <c r="E238">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A239">
-        <v>854777</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D239" t="s">
-        <v>5</v>
-      </c>
-      <c r="E239">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A240">
-        <v>853472</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D240" t="s">
-        <v>5</v>
-      </c>
-      <c r="E240">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A241">
-        <v>855278</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D241" t="s">
-        <v>5</v>
-      </c>
-      <c r="E241">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A242">
-        <v>852719</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D242" t="s">
-        <v>5</v>
-      </c>
-      <c r="E242">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A243">
-        <v>852720</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D243" t="s">
-        <v>5</v>
-      </c>
-      <c r="E243">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A244">
-        <v>853734</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D244" t="s">
-        <v>5</v>
-      </c>
-      <c r="E244">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A245">
-        <v>853738</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D245" t="s">
-        <v>5</v>
-      </c>
-      <c r="E245">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A246">
-        <v>854686</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D246" t="s">
-        <v>5</v>
-      </c>
-      <c r="E246">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A247">
-        <v>852752</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D247" t="s">
-        <v>5</v>
-      </c>
-      <c r="E247">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A248">
-        <v>855374</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D248" t="s">
-        <v>5</v>
-      </c>
-      <c r="E248">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A249">
-        <v>854925</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D249" t="s">
-        <v>5</v>
-      </c>
-      <c r="E249">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A250">
-        <v>852562</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D250" t="s">
-        <v>5</v>
-      </c>
-      <c r="E250">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A251">
-        <v>854724</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D251" t="s">
-        <v>5</v>
-      </c>
-      <c r="E251">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A252">
-        <v>855382</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D252" t="s">
-        <v>5</v>
-      </c>
-      <c r="E252">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A253">
-        <v>855400</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D253" t="s">
-        <v>5</v>
-      </c>
-      <c r="E253">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A254">
-        <v>855045</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D254" t="s">
-        <v>5</v>
-      </c>
-      <c r="E254">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A255">
-        <v>848786</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D255" t="s">
-        <v>5</v>
-      </c>
-      <c r="E255">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A256">
-        <v>854889</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D256" t="s">
-        <v>5</v>
-      </c>
-      <c r="E256">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A257">
-        <v>855355</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D257" t="s">
-        <v>5</v>
-      </c>
-      <c r="E257">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A258">
-        <v>854839</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D258" t="s">
-        <v>5</v>
-      </c>
-      <c r="E258">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A259">
-        <v>854658</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D259" t="s">
-        <v>5</v>
-      </c>
-      <c r="E259">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A260">
-        <v>854830</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D260" t="s">
-        <v>5</v>
-      </c>
-      <c r="E260">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A261">
-        <v>854832</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D261" t="s">
-        <v>5</v>
-      </c>
-      <c r="E261">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A262">
-        <v>854835</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D262" t="s">
-        <v>5</v>
-      </c>
-      <c r="E262">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A263">
-        <v>854051</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D263" t="s">
-        <v>5</v>
-      </c>
-      <c r="E263">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A264">
-        <v>855137</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D264" t="s">
-        <v>5</v>
-      </c>
-      <c r="E264">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A265">
-        <v>854629</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D265" t="s">
-        <v>5</v>
-      </c>
-      <c r="E265">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A266">
-        <v>855310</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D266" t="s">
-        <v>5</v>
-      </c>
-      <c r="E266">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A267">
-        <v>854579</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D267" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A268">
-        <v>852886</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D268" t="s">
-        <v>5</v>
-      </c>
-      <c r="E268">
         <v>257</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E268" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}"/>
+  <autoFilter ref="A1:E233" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B8A4293-332F-4170-B3BB-D28530771A17}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{682434B5-8622-4901-9CC6-AF945A4D8225}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="218">
   <si>
     <t>Pedido</t>
   </si>
@@ -113,14 +113,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 575,69_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.583,84_x000D_
 • Valor em ruptura: R$ 136,32_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -161,14 +153,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.362,83_x000D_
-• Valor em ruptura: R$ 165,31_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 180,45_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -238,14 +222,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.412,08_x000D_
-• Valor em ruptura: R$ 3.311,45_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -281,22 +257,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.773,46_x000D_
-• Valor em ruptura: R$ 2.076,65_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.146,67_x000D_
-• Valor em ruptura: R$ 6.222,92_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 5.150,00</t>
@@ -313,62 +273,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.651,89_x000D_
-• Valor em ruptura: R$ 2.380,95_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.645,60_x000D_
-• Valor em ruptura: R$ 1.427,70_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.169,78_x000D_
-• Valor em ruptura: R$ 919,43_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.211,50_x000D_
-• Valor em ruptura: R$ 287,61_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.106,86_x000D_
-• Valor em ruptura: R$ 22.560,96_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 21.653,18_x000D_
-• Valor em ruptura: R$ 494,24_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.467,70_x000D_
-• Valor em ruptura: R$ 271,15_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.528,03_x000D_
 • Valor em ruptura: R$ 339,44_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -409,14 +313,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.221,22_x000D_
-• Valor em ruptura: R$ 1.876,39_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -425,35 +321,11 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.596,02_x000D_
-• Valor em ruptura: R$ 542,31_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.828,78_x000D_
 • Valor em ruptura: R$ 2.508,66_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.340,23_x000D_
-• Valor em ruptura: R$ 273,47_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.383,60_x000D_
-• Valor em ruptura: R$ 207,02_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -475,22 +347,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 4.136,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.439,71_x000D_
-• Valor em ruptura: R$ 11.790,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 6.554,12_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -510,46 +366,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.394,44_x000D_
-• Valor em ruptura: R$ 529,10_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 860,07_x000D_
-• Valor em ruptura: R$ 5.142,57_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.514,89_x000D_
-• Valor em ruptura: R$ 977,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.016,76_x000D_
-• Valor em ruptura: R$ 2.347,13_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.211,97_x000D_
-• Valor em ruptura: R$ 1.838,86_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -558,22 +374,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.233,28_x000D_
-• Valor em ruptura: R$ 7.312,26_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 13.558,09_x000D_
-• Valor em ruptura: R$ 254,41_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -590,54 +390,6 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 693,34_x000D_
-• Valor em ruptura: R$ 1.624,39_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.360,71_x000D_
-• Valor em ruptura: R$ 259,58_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.181,84_x000D_
-• Valor em ruptura: R$ 29.279,18_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 655,73_x000D_
-• Valor em ruptura: R$ 5.269,97_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.116,43_x000D_
-• Valor em ruptura: R$ 418,06_x000D_
-• Valor mínimo de frete: R$ 50,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 24.941,97_x000D_
-• Valor em ruptura: R$ 56.331,26_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -649,33 +401,9 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 221,48_x000D_
-• Valor em ruptura: R$ 519,16_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 2.645,50_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.803,76_x000D_
-• Valor em ruptura: R$ 2.410,60_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.663,71_x000D_
-• Valor em ruptura: R$ 716,44_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -702,14 +430,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 295,26_x000D_
-• Valor em ruptura: R$ 4.509,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -858,14 +578,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 38.762,66_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 38.772,48_x000D_
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
@@ -908,22 +620,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 275.948,41_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 11.148,58_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 33.802,88_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -1038,14 +734,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.484,62_x000D_
-• Valor em ruptura: R$ 393,50_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1062,14 +750,6 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.931,41_x000D_
-• Valor em ruptura: R$ 10.726,02_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1100,14 +780,6 @@
 • Valor em estoque: R$ 1.650,02_x000D_
 • Valor em ruptura: R$ 1.693,12_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.091,89_x000D_
-• Valor em ruptura: R$ 273,74_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -1118,14 +790,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.381,80_x000D_
-• Valor em ruptura: R$ 3.600,62_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1142,14 +806,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.296,18_x000D_
-• Valor em ruptura: R$ 3.658,58_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1198,14 +854,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.109,99_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1225,40 +873,8 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.493,35_x000D_
-• Valor em ruptura: R$ 6.665,17_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.501,70_x000D_
 • Valor em ruptura: R$ 3.762,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.949,21_x000D_
-• Valor em ruptura: R$ 3.968,25_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 13.172,91_x000D_
-• Valor em ruptura: R$ 6.028,58_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.584,81_x000D_
-• Valor em ruptura: R$ 920,74_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1278,14 +894,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 15.720,18_x000D_
-• Valor em ruptura: R$ 1.461,75_x000D_
-• Valor mínimo de frete: R$ 50,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1305,14 +913,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.807,69_x000D_
-• Valor em ruptura: R$ 296,81_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.824,78_x000D_
 • Valor em ruptura: R$ 1.009,36_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1332,14 +932,6 @@
 • Valor em estoque: R$ 6.836,90_x000D_
 • Valor em ruptura: R$ 8.893,74_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 24.017,55_x000D_
-• Valor em ruptura: R$ 933,28_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -1361,14 +953,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.679,13_x000D_
-• Valor em ruptura: R$ 1.108,81_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.293,41_x000D_
 • Valor em ruptura: R$ 275,83_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
@@ -1470,22 +1054,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.849,52_x000D_
-• Valor em ruptura: R$ 3.877,52_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.920,57_x000D_
-• Valor em ruptura: R$ 3.106,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1502,28 +1070,12 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.034,52_x000D_
-• Valor em ruptura: R$ 1.285,64_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.891,37_x000D_
 • Valor em ruptura: R$ 1.036,91_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.404,53_x000D_
-• Valor em ruptura: R$ 2.215,82_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -1550,30 +1102,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.398,03_x000D_
-• Valor em ruptura: R$ 813,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.555,67_x000D_
-• Valor em ruptura: R$ 296,81_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 28.711,30_x000D_
-• Valor em ruptura: R$ 1.038,32_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1588,22 +1116,6 @@
 • Valor em estoque: R$ 4.150,27_x000D_
 • Valor em ruptura: R$ 1.003,46_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.848,40_x000D_
-• Valor em ruptura: R$ 542,31_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 296,81_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -1614,14 +1126,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.015,38_x000D_
-• Valor em ruptura: R$ 1.860,07_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1638,28 +1142,12 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.353,51_x000D_
-• Valor em ruptura: R$ 5.540,62_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.170,95_x000D_
 • Valor em ruptura: R$ 1.605,54_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.395,85_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -1681,25 +1169,588 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 367,70_x000D_
-• Valor em ruptura: R$ 3.668,92_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 644,47_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.362,83_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 644,47_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 927,80_x000D_
-• Valor em ruptura: R$ 2.400,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
+• Valor em estoque: R$ 3.174,99_x000D_
+• Valor em ruptura: R$ 252,48_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 625,14_x000D_
+• Valor em ruptura: R$ 75,07_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.570,80_x000D_
+• Valor em ruptura: R$ 356,25_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.005,29_x000D_
+• Valor em ruptura: R$ 718,24_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.388,31_x000D_
+• Valor em ruptura: R$ 55,78_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.007,75_x000D_
+• Valor em ruptura: R$ 546,58_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.747,62_x000D_
+• Valor em ruptura: R$ 647,30_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.695,08_x000D_
+• Valor em ruptura: R$ 9.962,35_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.771,06_x000D_
+• Valor em ruptura: R$ 1.168,57_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.281,94_x000D_
+• Valor em ruptura: R$ 3.568,36_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.408,00_x000D_
+• Valor em ruptura: R$ 665,30_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.423,91_x000D_
+• Valor em ruptura: R$ 665,30_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.978,94_x000D_
+• Valor em ruptura: R$ 177,61_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.702,48_x000D_
+• Valor em ruptura: R$ 1.517,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.306,51_x000D_
+• Valor em ruptura: R$ 2.675,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.967,87_x000D_
+• Valor em ruptura: R$ 4.791,54_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.303,97_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.923,17_x000D_
+• Valor em ruptura: R$ 1.697,18_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.700,43_x000D_
+• Valor em ruptura: R$ 1.254,33_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.739,86_x000D_
+• Valor em ruptura: R$ 1.357,75_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 19.209,59_x000D_
+• Valor em ruptura: R$ 2.815,84_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.645,82_x000D_
+• Valor em ruptura: R$ 2.380,95_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 240,48_x000D_
+• Valor em ruptura: R$ 3.094,75_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 781,52_x000D_
+• Valor em ruptura: R$ 3.233,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.756,95_x000D_
+• Valor em ruptura: R$ 4.797,17_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 988,25_x000D_
+• Valor em ruptura: R$ 2.508,66_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.995,19_x000D_
+• Valor em ruptura: R$ 1.410,93_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.457,99_x000D_
+• Valor em ruptura: R$ 2.700,53_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 50,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 14.652,45_x000D_
+• Valor em ruptura: R$ 4.549,04_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 599,47_x000D_
+• Valor em ruptura: R$ 2.531,75_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.270,47_x000D_
+• Valor em ruptura: R$ 598,55_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.867,55_x000D_
+• Valor em ruptura: R$ 1.688,75_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.033,30_x000D_
+• Valor em ruptura: R$ 1.330,59_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.720,24_x000D_
+• Valor em ruptura: R$ 1.330,59_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.839,37_x000D_
+• Valor em ruptura: R$ 666,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.752,44_x000D_
+• Valor em ruptura: R$ 6.793,10_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.309,75_x000D_
+• Valor em ruptura: R$ 15.232,59_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 16.421,62_x000D_
+• Valor em ruptura: R$ 760,31_x000D_
+• Valor mínimo de frete: R$ 50,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.966,37_x000D_
+• Valor em ruptura: R$ 4.277,95_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.529,64_x000D_
+• Valor em ruptura: R$ 1.345,81_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 16.335,03_x000D_
+• Valor em ruptura: R$ 1.545,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.111,25_x000D_
+• Valor em ruptura: R$ 28.349,77_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 32.671,96_x000D_
+• Valor em ruptura: R$ 48.601,27_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 10.038,29_x000D_
+• Valor em ruptura: R$ 3.143,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.256,53_x000D_
+• Valor em ruptura: R$ 293,29_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.097,96_x000D_
+• Valor em ruptura: R$ 2.116,40_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.438,97_x000D_
+• Valor em ruptura: R$ 296,94_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.249,18_x000D_
+• Valor em ruptura: R$ 250,87_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.224,71_x000D_
+• Valor em ruptura: R$ 1.368,29_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.314,87_x000D_
+• Valor em ruptura: R$ 4.806,93_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.254,35_x000D_
+• Valor em ruptura: R$ 533,59_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 344,34_x000D_
+• Valor em ruptura: R$ 299,36_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.738,13_x000D_
+• Valor em ruptura: R$ 3.066,63_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.029,69_x000D_
+• Valor em ruptura: R$ 4.466,00_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.151,19_x000D_
+• Valor em ruptura: R$ 836,96_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 485,29_x000D_
+• Valor em ruptura: R$ 5.063,49_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.698,31_x000D_
+• Valor em ruptura: R$ 278,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.165,01_x000D_
+• Valor em ruptura: R$ 825,56_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.650,34_x000D_
+• Valor em ruptura: R$ 880,57_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 22.974,12_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.550,81_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 28.867,37_x000D_
+• Valor em ruptura: R$ 9.895,29_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 13.999,51_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 23.808,26_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.357,03_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.793,84_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 71.847,56_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.373,30_x000D_
+• Valor em ruptura: R$ 30.429,58_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>O valor do pedido encontra-se abaixo do mínimo estabelecido para a região, ficamos no aguarde de pedido complementar ou cancelamento do mesmo.</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2126,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -2103,94 +2154,94 @@
     </row>
     <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>854080</v>
+        <v>853850</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>182</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>580</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>855293</v>
+        <v>853854</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>2072</v>
+        <v>773</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>855426</v>
+        <v>853926</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>429</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>855374</v>
+        <v>853853</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>293</v>
+        <v>773</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>853850</v>
+        <v>850631</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>773</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>853854</v>
+        <v>855347</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>773</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>853926</v>
+        <v>853943</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -2201,416 +2252,416 @@
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>853853</v>
+        <v>855177</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>773</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>850631</v>
+        <v>853567</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>147</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>855347</v>
+        <v>854781</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>134</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>853943</v>
+        <v>848783</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>773</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>855177</v>
+        <v>853426</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>2078</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>853849</v>
+        <v>854985</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>1021</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>853567</v>
+        <v>854061</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>3060</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>854781</v>
+        <v>849811</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>3093</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>848783</v>
+        <v>855293</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>3075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>853426</v>
+        <v>849918</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>3075</v>
+        <v>750</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>854985</v>
+        <v>849917</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>2090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>854061</v>
+        <v>850200</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>589</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>855423</v>
+        <v>852593</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>951</v>
+        <v>632</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>849811</v>
+        <v>852631</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>3058</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>855295</v>
+        <v>853998</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>377</v>
+        <v>722</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>849918</v>
+        <v>855341</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>750</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>855268</v>
+        <v>853852</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>2083</v>
+        <v>773</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>849917</v>
+        <v>854933</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>3089</v>
+        <v>983</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>850200</v>
+        <v>854931</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>1021</v>
+        <v>983</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>852593</v>
+        <v>854237</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>632</v>
+        <v>773</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>852631</v>
+        <v>854585</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>3085</v>
+        <v>933</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>853998</v>
+        <v>855295</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>722</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>855341</v>
+        <v>854330</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>3029</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>853852</v>
+        <v>855330</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>854933</v>
+        <v>854385</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>983</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>854931</v>
+        <v>855232</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>983</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>854237</v>
+        <v>855480</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>773</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>854585</v>
+        <v>854374</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>933</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>854330</v>
+        <v>854940</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>855330</v>
+        <v>855501</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2619,163 +2670,163 @@
         <v>703</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>854385</v>
+        <v>855052</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
-        <v>2090</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>855232</v>
+        <v>855598</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40">
-        <v>2084</v>
+        <v>642</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>854374</v>
+        <v>854415</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>3069</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>854940</v>
+        <v>854840</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>855052</v>
+        <v>855376</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>380</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>854415</v>
+        <v>855350</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44">
-        <v>703</v>
+        <v>614</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>854840</v>
+        <v>854934</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>642</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>855159</v>
+        <v>854891</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>614</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>855376</v>
+        <v>855357</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>1021</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>855350</v>
+        <v>853816</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>614</v>
+        <v>880</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>854934</v>
+        <v>855348</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>2064</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>854891</v>
+        <v>855266</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>130</v>
@@ -2784,29 +2835,29 @@
         <v>5</v>
       </c>
       <c r="E50">
-        <v>2051</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>853913</v>
+        <v>855386</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>614</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>855357</v>
+        <v>855484</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -2817,570 +2868,570 @@
     </row>
     <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>854234</v>
+        <v>855359</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>90</v>
+        <v>699</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>853816</v>
+        <v>854338</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>880</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>855348</v>
+        <v>854345</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>134</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855266</v>
+        <v>855512</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>380</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>854535</v>
+        <v>855069</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>855386</v>
+        <v>854773</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>737</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>855359</v>
+        <v>855393</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>699</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>854338</v>
+        <v>855203</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>854345</v>
+        <v>855289</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61">
-        <v>281</v>
+        <v>580</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>853715</v>
+        <v>855596</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
       </c>
       <c r="E62">
-        <v>3092</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>855069</v>
+        <v>855221</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
-        <v>380</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>854773</v>
+        <v>855553</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64">
-        <v>90</v>
+        <v>951</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>854812</v>
+        <v>855033</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>855393</v>
+        <v>855483</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>90</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>855203</v>
+        <v>854315</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>703</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>854800</v>
+        <v>854320</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>377</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>855289</v>
+        <v>854301</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>854639</v>
+        <v>854306</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>3092</v>
+        <v>281</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>855221</v>
+        <v>854312</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>1027</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>853770</v>
+        <v>854216</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>294</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>855033</v>
+        <v>854756</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>855108</v>
+        <v>854809</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>854315</v>
+        <v>854367</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>188</v>
+        <v>35</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>281</v>
+        <v>614</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>854320</v>
+        <v>854979</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>281</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>854301</v>
+        <v>854944</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>854306</v>
+        <v>854701</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>854312</v>
+        <v>854881</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>281</v>
+        <v>699</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>854216</v>
+        <v>854357</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>1027</v>
+        <v>281</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>854756</v>
+        <v>855242</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>281</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>855211</v>
+        <v>855030</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>854809</v>
+        <v>855475</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>854683</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" t="s">
+        <v>5</v>
+      </c>
+      <c r="E84">
         <v>951</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>854367</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D84" t="s">
-        <v>5</v>
-      </c>
-      <c r="E84">
+    <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>855338</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85">
         <v>614</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>854979</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
-      </c>
-      <c r="E85">
-        <v>3078</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>854944</v>
+        <v>855077</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>703</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>854701</v>
+        <v>855423</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>703</v>
+        <v>951</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>854881</v>
+        <v>855466</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>854357</v>
+        <v>855421</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>855242</v>
+        <v>853459</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>855030</v>
+        <v>850430</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>855111</v>
+        <v>855274</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>854683</v>
+        <v>854834</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
@@ -3389,908 +3440,908 @@
         <v>951</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>855338</v>
+        <v>854980</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>614</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>854428</v>
+        <v>855548</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>722</v>
+        <v>699</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>854193</v>
+        <v>854977</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>614</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>855077</v>
+        <v>853295</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>855421</v>
+        <v>854749</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>2088</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>855017</v>
+        <v>855234</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>3089</v>
+        <v>699</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>855075</v>
+        <v>855365</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>853459</v>
+        <v>855449</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>55</v>
+        <v>172</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>850430</v>
+        <v>855138</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>855274</v>
+        <v>854702</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>854834</v>
+        <v>855549</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>951</v>
+        <v>700</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>854228</v>
+        <v>855580</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>854980</v>
+        <v>855056</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>3078</v>
+        <v>625</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>854977</v>
+        <v>855554</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>699</v>
+        <v>614</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>854692</v>
+        <v>855514</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>642</v>
+        <v>951</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>853295</v>
+        <v>855440</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>2027</v>
+        <v>922</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>854749</v>
+        <v>854348</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>855234</v>
+        <v>854354</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>699</v>
+        <v>281</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>855365</v>
+        <v>854361</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>854771</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D113" t="s">
+        <v>5</v>
+      </c>
+      <c r="E113">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>854932</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D114" t="s">
+        <v>5</v>
+      </c>
+      <c r="E114">
         <v>699</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>855138</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D113" t="s">
-        <v>5</v>
-      </c>
-      <c r="E113">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>854992</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D114" t="s">
-        <v>5</v>
-      </c>
-      <c r="E114">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>854702</v>
+        <v>855024</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>854689</v>
+        <v>854935</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>874</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>855056</v>
+        <v>855476</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>854118</v>
+        <v>855062</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>699</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>855104</v>
+        <v>853206</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>593</v>
+        <v>614</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>853809</v>
+        <v>854305</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>90</v>
+        <v>574</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>854348</v>
+        <v>854263</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>281</v>
+        <v>574</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>854354</v>
+        <v>855047</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>281</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>854361</v>
+        <v>855384</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>281</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>854771</v>
+        <v>854606</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>854932</v>
+        <v>854356</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855024</v>
+        <v>855284</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>854935</v>
+        <v>855560</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>2027</v>
+        <v>722</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>855062</v>
+        <v>854387</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>3072</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>854028</v>
+        <v>854112</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>1021</v>
+        <v>723</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>854302</v>
+        <v>854319</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>706</v>
+        <v>574</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>853206</v>
+        <v>854314</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>614</v>
+        <v>574</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>854305</v>
+        <v>854807</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>574</v>
+        <v>836</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>854263</v>
+        <v>855426</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>574</v>
+        <v>429</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>855047</v>
+        <v>855513</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>855384</v>
+        <v>855051</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>90</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>854606</v>
+        <v>854999</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>2032</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>854356</v>
+        <v>855500</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>867</v>
+        <v>829</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>855173</v>
+        <v>855366</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>855284</v>
+        <v>855498</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>811</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>853929</v>
+        <v>855428</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>722</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>854443</v>
+        <v>855136</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>377</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>854387</v>
+        <v>854833</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>854112</v>
+        <v>855496</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>723</v>
+        <v>811</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>854122</v>
+        <v>855172</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>723</v>
+        <v>874</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>854148</v>
+        <v>854884</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>723</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>854319</v>
+        <v>855566</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>574</v>
+        <v>614</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>854314</v>
+        <v>855595</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>574</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>854807</v>
+        <v>855556</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>855051</v>
+        <v>855315</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>3078</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>854999</v>
+        <v>855065</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>2041</v>
+        <v>829</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>854924</v>
+        <v>853358</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>203</v>
+        <v>49</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>943</v>
+        <v>90</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>855366</v>
+        <v>855468</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>639</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>853773</v>
+        <v>855229</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>377</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>855428</v>
+        <v>854734</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>3035</v>
+        <v>874</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>855279</v>
+        <v>854942</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>2088</v>
+        <v>699</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>855136</v>
+        <v>855352</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>3037</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>854833</v>
+        <v>855538</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>3060</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>855172</v>
+        <v>855001</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -4301,318 +4352,318 @@
     </row>
     <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>855437</v>
+        <v>854347</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>205</v>
+        <v>16</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>281</v>
+        <v>967</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>854884</v>
+        <v>854984</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>1097</v>
+        <v>90</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>854820</v>
+        <v>855091</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>967</v>
+        <v>281</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>855315</v>
+        <v>855453</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>3034</v>
+        <v>614</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>855065</v>
+        <v>855563</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>829</v>
+        <v>664</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>853358</v>
+        <v>855451</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>90</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>855229</v>
+        <v>855083</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>3049</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>854734</v>
+        <v>855237</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>874</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>854942</v>
+        <v>855248</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>699</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>855352</v>
+        <v>854697</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>3060</v>
+        <v>90</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>855001</v>
+        <v>855461</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>874</v>
+        <v>811</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>854347</v>
+        <v>855275</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>854984</v>
+        <v>855258</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>90</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>855091</v>
+        <v>855079</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>855083</v>
+        <v>854695</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>3060</v>
+        <v>380</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>854697</v>
+        <v>855119</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>855275</v>
+        <v>851354</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>855258</v>
+        <v>851356</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>855079</v>
+        <v>851357</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
       <c r="E177">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>854695</v>
+        <v>854953</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
       <c r="E178">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>855119</v>
+        <v>854954</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="E179">
-        <v>3055</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>855186</v>
+        <v>851359</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>208</v>
+        <v>57</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>851354</v>
+        <v>854955</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -4623,10 +4674,10 @@
     </row>
     <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>851356</v>
+        <v>854956</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -4635,12 +4686,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>851357</v>
+        <v>844931</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -4651,10 +4702,10 @@
     </row>
     <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>854953</v>
+        <v>851348</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -4665,10 +4716,10 @@
     </row>
     <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>854954</v>
+        <v>851349</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -4679,10 +4730,10 @@
     </row>
     <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>851359</v>
+        <v>854602</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -4693,10 +4744,10 @@
     </row>
     <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>854955</v>
+        <v>854603</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -4707,10 +4758,10 @@
     </row>
     <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>854956</v>
+        <v>854604</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -4719,96 +4770,96 @@
         <v>60</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>844931</v>
+        <v>855576</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>60</v>
+        <v>407</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>851348</v>
+        <v>855261</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>851349</v>
+        <v>854899</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>854602</v>
+        <v>855254</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>854603</v>
+        <v>855272</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>854604</v>
+        <v>855255</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
       </c>
       <c r="E194">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>855261</v>
+        <v>855264</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
@@ -4819,10 +4870,10 @@
     </row>
     <row r="196" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>854899</v>
+        <v>855271</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
@@ -4831,12 +4882,12 @@
         <v>906</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>855254</v>
+        <v>855436</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="D197" t="s">
         <v>5</v>
@@ -4845,12 +4896,12 @@
         <v>906</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>855272</v>
+        <v>855438</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
@@ -4861,234 +4912,234 @@
     </row>
     <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>855255</v>
+        <v>853930</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199">
-        <v>906</v>
+        <v>979</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>855264</v>
+        <v>855494</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200">
-        <v>906</v>
+        <v>979</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>855271</v>
+        <v>854939</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
       </c>
       <c r="E201">
-        <v>906</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>855436</v>
+        <v>855297</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>855438</v>
+        <v>854777</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203">
-        <v>906</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>853930</v>
+        <v>855278</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>854939</v>
+        <v>852719</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="D205" t="s">
         <v>5</v>
       </c>
       <c r="E205">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>855297</v>
+        <v>852720</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="D206" t="s">
         <v>5</v>
       </c>
       <c r="E206">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>855345</v>
+        <v>853734</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="D207" t="s">
         <v>5</v>
       </c>
       <c r="E207">
-        <v>979</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>854777</v>
+        <v>853738</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D208" t="s">
         <v>5</v>
       </c>
       <c r="E208">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>855278</v>
+        <v>855583</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="D209" t="s">
         <v>5</v>
       </c>
       <c r="E209">
-        <v>293</v>
+        <v>778</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>852719</v>
+        <v>854686</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D210" t="s">
         <v>5</v>
       </c>
       <c r="E210">
-        <v>1019</v>
+        <v>118</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>852720</v>
+        <v>852752</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="D211" t="s">
         <v>5</v>
       </c>
       <c r="E211">
-        <v>1019</v>
+        <v>979</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>853734</v>
+        <v>855582</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="D212" t="s">
         <v>5</v>
       </c>
       <c r="E212">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>853738</v>
+        <v>855374</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="D213" t="s">
         <v>5</v>
       </c>
       <c r="E213">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>854686</v>
+        <v>854925</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="D214" t="s">
         <v>5</v>
       </c>
       <c r="E214">
-        <v>118</v>
+        <v>904</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>852752</v>
+        <v>852562</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D215" t="s">
         <v>5</v>
@@ -5097,46 +5148,46 @@
         <v>979</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>854925</v>
+        <v>855543</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="D216" t="s">
         <v>5</v>
       </c>
       <c r="E216">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>855424</v>
+        <v>855547</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D217" t="s">
         <v>5</v>
       </c>
       <c r="E217">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>852562</v>
+        <v>855492</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="D218" t="s">
         <v>5</v>
       </c>
       <c r="E218">
-        <v>979</v>
+        <v>60</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="90" x14ac:dyDescent="0.25">
@@ -5144,7 +5195,7 @@
         <v>854724</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D219" t="s">
         <v>5</v>
@@ -5158,7 +5209,7 @@
         <v>855382</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D220" t="s">
         <v>5</v>
@@ -5169,10 +5220,10 @@
     </row>
     <row r="221" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>855400</v>
+        <v>855578</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="D221" t="s">
         <v>5</v>
@@ -5183,30 +5234,30 @@
     </row>
     <row r="222" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>848786</v>
+        <v>855400</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D222" t="s">
         <v>5</v>
       </c>
       <c r="E222">
-        <v>1807</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>854889</v>
+        <v>848786</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D223" t="s">
         <v>5</v>
       </c>
       <c r="E223">
-        <v>293</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="90" x14ac:dyDescent="0.25">
@@ -5214,7 +5265,7 @@
         <v>855355</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D224" t="s">
         <v>5</v>
@@ -5223,12 +5274,12 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>854839</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>113</v>
+        <v>215</v>
       </c>
       <c r="D225" t="s">
         <v>5</v>
@@ -5239,24 +5290,24 @@
     </row>
     <row r="226" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>854830</v>
+        <v>854225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="D226" t="s">
         <v>5</v>
       </c>
       <c r="E226">
-        <v>851</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>854832</v>
+        <v>854830</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D227" t="s">
         <v>5</v>
@@ -5267,10 +5318,10 @@
     </row>
     <row r="228" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>854835</v>
+        <v>854832</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D228" t="s">
         <v>5</v>
@@ -5279,74 +5330,952 @@
         <v>851</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>854051</v>
+        <v>854835</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="D229" t="s">
         <v>5</v>
       </c>
       <c r="E229">
-        <v>1807</v>
+        <v>851</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>855137</v>
+        <v>854051</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="D230" t="s">
         <v>5</v>
       </c>
       <c r="E230">
-        <v>375</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>855310</v>
+        <v>855137</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="D231" t="s">
         <v>5</v>
       </c>
       <c r="E231">
-        <v>293</v>
+        <v>375</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>854579</v>
+        <v>855310</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D232" t="s">
         <v>5</v>
       </c>
       <c r="E232">
-        <v>996</v>
+        <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A233">
+        <v>854579</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D233" t="s">
+        <v>5</v>
+      </c>
+      <c r="E233">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234">
         <v>852886</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D233" t="s">
-        <v>5</v>
-      </c>
-      <c r="E233">
+      <c r="B234" t="s">
+        <v>79</v>
+      </c>
+      <c r="D234" t="s">
+        <v>5</v>
+      </c>
+      <c r="E234">
         <v>257</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>843776</v>
+      </c>
+      <c r="B235" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>843780</v>
+      </c>
+      <c r="B236" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>843785</v>
+      </c>
+      <c r="B237" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>844518</v>
+      </c>
+      <c r="B238" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>844527</v>
+      </c>
+      <c r="B239" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>846411</v>
+      </c>
+      <c r="B240" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>846414</v>
+      </c>
+      <c r="B241" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>847008</v>
+      </c>
+      <c r="B242" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>851106</v>
+      </c>
+      <c r="B243" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>851109</v>
+      </c>
+      <c r="B244" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>851875</v>
+      </c>
+      <c r="B245" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>851876</v>
+      </c>
+      <c r="B246" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>851881</v>
+      </c>
+      <c r="B247" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>852454</v>
+      </c>
+      <c r="B248" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>846997</v>
+      </c>
+      <c r="B249" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>847009</v>
+      </c>
+      <c r="B250" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>848642</v>
+      </c>
+      <c r="B251" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>851100</v>
+      </c>
+      <c r="B252" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>851115</v>
+      </c>
+      <c r="B253" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>852345</v>
+      </c>
+      <c r="B254" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>852346</v>
+      </c>
+      <c r="B255" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>852352</v>
+      </c>
+      <c r="B256" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>852452</v>
+      </c>
+      <c r="B257" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>854969</v>
+      </c>
+      <c r="B258" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>855562</v>
+      </c>
+      <c r="B259" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>852386</v>
+      </c>
+      <c r="B260" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>855246</v>
+      </c>
+      <c r="B261" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>849283</v>
+      </c>
+      <c r="B262" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>849405</v>
+      </c>
+      <c r="B263" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>849445</v>
+      </c>
+      <c r="B264" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>849452</v>
+      </c>
+      <c r="B265" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>849464</v>
+      </c>
+      <c r="B266" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>849499</v>
+      </c>
+      <c r="B267" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>849478</v>
+      </c>
+      <c r="B268" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>849969</v>
+      </c>
+      <c r="B269" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>850323</v>
+      </c>
+      <c r="B270" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>854479</v>
+      </c>
+      <c r="B271" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>854482</v>
+      </c>
+      <c r="B272" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>849444</v>
+      </c>
+      <c r="B273" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>854894</v>
+      </c>
+      <c r="B274" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>851751</v>
+      </c>
+      <c r="B275" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>849662</v>
+      </c>
+      <c r="B276" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>853691</v>
+      </c>
+      <c r="B277" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>849622</v>
+      </c>
+      <c r="B278" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>849563</v>
+      </c>
+      <c r="B279" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>854288</v>
+      </c>
+      <c r="B280" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>854260</v>
+      </c>
+      <c r="B281" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>854255</v>
+      </c>
+      <c r="B282" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>854272</v>
+      </c>
+      <c r="B283" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>849613</v>
+      </c>
+      <c r="B284" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>849183</v>
+      </c>
+      <c r="B285" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>849750</v>
+      </c>
+      <c r="B286" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>849603</v>
+      </c>
+      <c r="B287" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>852382</v>
+      </c>
+      <c r="B288" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>849376</v>
+      </c>
+      <c r="B289" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>849832</v>
+      </c>
+      <c r="B290" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>849559</v>
+      </c>
+      <c r="B291" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>849659</v>
+      </c>
+      <c r="B292" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>849663</v>
+      </c>
+      <c r="B293" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>849847</v>
+      </c>
+      <c r="B294" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>849636</v>
+      </c>
+      <c r="B295" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>849652</v>
+      </c>
+      <c r="B296" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>849913</v>
+      </c>
+      <c r="B297" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>855273</v>
+      </c>
+      <c r="B298" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>849940</v>
+      </c>
+      <c r="B299" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>849567</v>
+      </c>
+      <c r="B300" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>849780</v>
+      </c>
+      <c r="B301" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>849773</v>
+      </c>
+      <c r="B302" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>849792</v>
+      </c>
+      <c r="B303" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>849812</v>
+      </c>
+      <c r="B304" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>849639</v>
+      </c>
+      <c r="B305" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>849796</v>
+      </c>
+      <c r="B306" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>849821</v>
+      </c>
+      <c r="B307" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>848706</v>
+      </c>
+      <c r="B308" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>849882</v>
+      </c>
+      <c r="B309" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>850013</v>
+      </c>
+      <c r="B310" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>852307</v>
+      </c>
+      <c r="B311" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>854060</v>
+      </c>
+      <c r="B312" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>855485</v>
+      </c>
+      <c r="B313" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>853428</v>
+      </c>
+      <c r="B314" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>855455</v>
+      </c>
+      <c r="B315" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>855521</v>
+      </c>
+      <c r="B316" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>855588</v>
+      </c>
+      <c r="B317" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>855568</v>
+      </c>
+      <c r="B318" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>855413</v>
+      </c>
+      <c r="B319" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>855429</v>
+      </c>
+      <c r="B320" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>855574</v>
+      </c>
+      <c r="B321" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>855579</v>
+      </c>
+      <c r="B322" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>855257</v>
+      </c>
+      <c r="B323" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>855442</v>
+      </c>
+      <c r="B324" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>855349</v>
+      </c>
+      <c r="B325" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>855473</v>
+      </c>
+      <c r="B326" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>855534</v>
+      </c>
+      <c r="B327" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>855587</v>
+      </c>
+      <c r="B328" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>855518</v>
+      </c>
+      <c r="B329" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>855540</v>
+      </c>
+      <c r="B330" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>855524</v>
+      </c>
+      <c r="B331" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>855593</v>
+      </c>
+      <c r="B332" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>855488</v>
+      </c>
+      <c r="B333" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>855559</v>
+      </c>
+      <c r="B334" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>854186</v>
+      </c>
+      <c r="B335" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>855590</v>
+      </c>
+      <c r="B336" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>855517</v>
+      </c>
+      <c r="B337" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>855070</v>
+      </c>
+      <c r="B338" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>855497</v>
+      </c>
+      <c r="B339" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>855333</v>
+      </c>
+      <c r="B340" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>855427</v>
+      </c>
+      <c r="B341" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>855493</v>
+      </c>
+      <c r="B342" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{682434B5-8622-4901-9CC6-AF945A4D8225}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20989C11-7AAA-4474-BA4D-30EA0923E1A6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="187">
   <si>
     <t>Pedido</t>
   </si>
@@ -75,14 +75,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 595,04_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.767,51_x000D_
-• Valor em ruptura: R$ 405,90_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
@@ -102,14 +94,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 29.335,43_x000D_
-• Valor em ruptura: R$ 1.882,09_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -214,86 +198,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.074,99_x000D_
-• Valor em ruptura: R$ 1.177,40_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.729,99_x000D_
-• Valor em ruptura: R$ 2.675,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.507,64_x000D_
-• Valor em ruptura: R$ 1.682,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 897,13_x000D_
-• Valor em ruptura: R$ 1.673,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.415,99_x000D_
-• Valor em ruptura: R$ 2.157,94_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.001,00_x000D_
-• Valor em ruptura: R$ 853,76_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.528,03_x000D_
-• Valor em ruptura: R$ 339,44_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.176,55_x000D_
-• Valor em ruptura: R$ 2.018,72_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.014,62_x000D_
-• Valor em ruptura: R$ 2.376,06_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -305,27 +209,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.185,90_x000D_
-• Valor em ruptura: R$ 1.756,06_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.828,78_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -342,44 +230,12 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.136,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.384,28_x000D_
-• Valor em ruptura: R$ 679,31_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.666,49_x000D_
-• Valor em ruptura: R$ 1.330,59_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 36.260,95_x000D_
-• Valor em ruptura: R$ 58.321,52_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
@@ -401,14 +257,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.645,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.394,93_x000D_
 • Valor em ruptura: R$ 1.881,50_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -417,24 +265,8 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 588,41_x000D_
-• Valor em ruptura: R$ 2.645,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.140,94_x000D_
-• Valor em ruptura: R$ 1.587,30_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -587,22 +419,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 7.733,80_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.327,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 11.722,62_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -665,14 +481,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.729,14_x000D_
-• Valor em ruptura: R$ 328,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.450,87_x000D_
 • Valor em ruptura: R$ 71,37_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -726,68 +534,12 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.110,86_x000D_
-• Valor em ruptura: R$ 2.654,58_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.255,31_x000D_
-• Valor em ruptura: R$ 1.800,63_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.978,59_x000D_
-• Valor em ruptura: R$ 7.118,31_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.994,42_x000D_
-• Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.545,48_x000D_
-• Valor em ruptura: R$ 5.296,53_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.093,04_x000D_
 • Valor em ruptura: R$ 278,99_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.650,02_x000D_
-• Valor em ruptura: R$ 1.693,12_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 923,18_x000D_
-• Valor em ruptura: R$ 766,12_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -798,139 +550,11 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.485,77_x000D_
-• Valor em ruptura: R$ 3.557,76_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.691,25_x000D_
-• Valor em ruptura: R$ 1.254,33_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.597,78_x000D_
-• Valor em ruptura: R$ 1.254,33_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.493,26_x000D_
 • Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.265,63_x000D_
-• Valor em ruptura: R$ 2.699,16_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.040,04_x000D_
-• Valor em ruptura: R$ 5.533,16_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.603,96_x000D_
-• Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.815,83_x000D_
-• Valor em ruptura: R$ 752,60_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.557,64_x000D_
-• Valor em ruptura: R$ 1.429,94_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.501,70_x000D_
-• Valor em ruptura: R$ 3.762,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.315,74_x000D_
-• Valor em ruptura: R$ 4.185,05_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.145,70_x000D_
-• Valor em ruptura: R$ 3.620,54_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 13.223,82_x000D_
-• Valor em ruptura: R$ 2.699,16_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 12.289,77_x000D_
-• Valor em ruptura: R$ 8.146,49_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.824,78_x000D_
-• Valor em ruptura: R$ 1.009,36_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.979,59_x000D_
-• Valor em ruptura: R$ 5.879,40_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.836,90_x000D_
-• Valor em ruptura: R$ 8.893,74_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -945,59 +569,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.897,42_x000D_
-• Valor em ruptura: R$ 4.369,45_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.293,41_x000D_
 • Valor em ruptura: R$ 275,83_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.154,85_x000D_
-• Valor em ruptura: R$ 2.525,38_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.603,01_x000D_
-• Valor em ruptura: R$ 1.587,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.198,78_x000D_
-• Valor em ruptura: R$ 250,87_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.785,18_x000D_
-• Valor em ruptura: R$ 6.640,08_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.571,79_x000D_
-• Valor em ruptura: R$ 558,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1034,14 +610,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 13.976,84_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.599,75_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -1054,99 +622,11 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.590,93_x000D_
-• Valor em ruptura: R$ 1.337,95_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.667,85_x000D_
 • Valor em ruptura: R$ 3.903,59_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.891,37_x000D_
-• Valor em ruptura: R$ 1.036,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.933,25_x000D_
-• Valor em ruptura: R$ 1.357,75_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.502,98_x000D_
-• Valor em ruptura: R$ 339,44_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 960,52_x000D_
-• Valor em ruptura: R$ 678,87_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.315,20_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.150,27_x000D_
-• Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 94.126,89_x000D_
-• Valor em ruptura: R$ 943,56_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.870,32_x000D_
-• Valor em ruptura: R$ 9.226,88_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.192,63_x000D_
-• Valor em ruptura: R$ 2.278,57_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.170,95_x000D_
-• Valor em ruptura: R$ 1.605,54_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1161,25 +641,9 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.535,95_x000D_
-• Valor em ruptura: R$ 1.254,33_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 644,47_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.362,83_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -1193,99 +657,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 625,14_x000D_
-• Valor em ruptura: R$ 75,07_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.570,80_x000D_
-• Valor em ruptura: R$ 356,25_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.005,29_x000D_
-• Valor em ruptura: R$ 718,24_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.388,31_x000D_
 • Valor em ruptura: R$ 55,78_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.007,75_x000D_
-• Valor em ruptura: R$ 546,58_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.747,62_x000D_
-• Valor em ruptura: R$ 647,30_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.695,08_x000D_
-• Valor em ruptura: R$ 9.962,35_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.771,06_x000D_
-• Valor em ruptura: R$ 1.168,57_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.281,94_x000D_
-• Valor em ruptura: R$ 3.568,36_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.408,00_x000D_
-• Valor em ruptura: R$ 665,30_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.423,91_x000D_
-• Valor em ruptura: R$ 665,30_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.978,94_x000D_
-• Valor em ruptura: R$ 177,61_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1294,52 +670,12 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.306,51_x000D_
-• Valor em ruptura: R$ 2.675,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.967,87_x000D_
 • Valor em ruptura: R$ 4.791,54_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.303,97_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.923,17_x000D_
-• Valor em ruptura: R$ 1.697,18_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.700,43_x000D_
-• Valor em ruptura: R$ 1.254,33_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.739,86_x000D_
-• Valor em ruptura: R$ 1.357,75_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -1350,78 +686,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.645,82_x000D_
-• Valor em ruptura: R$ 2.380,95_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 240,48_x000D_
-• Valor em ruptura: R$ 3.094,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 781,52_x000D_
-• Valor em ruptura: R$ 3.233,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.756,95_x000D_
-• Valor em ruptura: R$ 4.797,17_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 988,25_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.995,19_x000D_
-• Valor em ruptura: R$ 1.410,93_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.457,99_x000D_
-• Valor em ruptura: R$ 2.700,53_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 50,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 14.652,45_x000D_
-• Valor em ruptura: R$ 4.549,04_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1446,38 +710,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.033,30_x000D_
-• Valor em ruptura: R$ 1.330,59_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.720,24_x000D_
-• Valor em ruptura: R$ 1.330,59_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.839,37_x000D_
-• Valor em ruptura: R$ 666,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.752,44_x000D_
-• Valor em ruptura: R$ 6.793,10_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1497,51 +729,11 @@
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.966,37_x000D_
-• Valor em ruptura: R$ 4.277,95_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.529,64_x000D_
-• Valor em ruptura: R$ 1.345,81_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 16.335,03_x000D_
-• Valor em ruptura: R$ 1.545,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.111,25_x000D_
-• Valor em ruptura: R$ 28.349,77_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 32.671,96_x000D_
 • Valor em ruptura: R$ 48.601,27_x000D_
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 10.038,29_x000D_
-• Valor em ruptura: R$ 3.143,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1556,14 +748,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.097,96_x000D_
-• Valor em ruptura: R$ 2.116,40_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -1590,30 +774,6 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.314,87_x000D_
-• Valor em ruptura: R$ 4.806,93_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.254,35_x000D_
-• Valor em ruptura: R$ 533,59_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 344,34_x000D_
-• Valor em ruptura: R$ 299,36_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1625,27 +785,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.029,69_x000D_
-• Valor em ruptura: R$ 4.466,00_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.151,19_x000D_
 • Valor em ruptura: R$ 836,96_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 485,29_x000D_
-• Valor em ruptura: R$ 5.063,49_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1654,22 +798,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.165,01_x000D_
-• Valor em ruptura: R$ 825,56_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.650,34_x000D_
-• Valor em ruptura: R$ 880,57_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1686,14 +814,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 28.867,37_x000D_
-• Valor em ruptura: R$ 9.895,29_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1707,14 +827,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 23.808,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.357,03_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1751,6 +863,646 @@
   </si>
   <si>
     <t>O valor do pedido encontra-se abaixo do mínimo estabelecido para a região, ficamos no aguarde de pedido complementar ou cancelamento do mesmo.</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.857,89_x000D_
+• Valor em ruptura: R$ 316,51_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.876,49_x000D_
+• Valor em ruptura: R$ 50,56_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.684,16_x000D_
+• Valor em ruptura: R$ 39,37_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 1.115,94_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.275,34_x000D_
+• Valor em ruptura: R$ 278,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.783,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.409,86_x000D_
+• Valor em ruptura: R$ 2.231,89_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.614,85_x000D_
+• Valor em ruptura: R$ 2.111,07_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.774,36_x000D_
+• Valor em ruptura: R$ 281,58_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.990,28_x000D_
+• Valor em ruptura: R$ 583,65_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.307,31_x000D_
+• Valor em ruptura: R$ 168,42_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 19.132,66_x000D_
+• Valor em ruptura: R$ 524,77_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 64.407,33_x000D_
+• Valor em ruptura: R$ 2.163,98_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.776,04_x000D_
+• Valor em ruptura: R$ 4.808,51_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.292,33_x000D_
+• Valor em ruptura: R$ 557,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.220,47_x000D_
+• Valor em ruptura: R$ 1.094,41_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.519,73_x000D_
+• Valor em ruptura: R$ 2.053,80_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.311,94_x000D_
+• Valor em ruptura: R$ 530,07_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.731,80_x000D_
+• Valor em ruptura: R$ 424,75_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 10.775,54_x000D_
+• Valor em ruptura: R$ 1.394,93_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.091,33_x000D_
+• Valor em ruptura: R$ 6.329,37_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.341,23_x000D_
+• Valor em ruptura: R$ 376,99_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.272,64_x000D_
+• Valor em ruptura: R$ 321,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.417,47_x000D_
+• Valor em ruptura: R$ 321,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.676,55_x000D_
+• Valor em ruptura: R$ 5.177,12_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 10.020,81_x000D_
+• Valor em ruptura: R$ 552,39_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.498,27_x000D_
+• Valor em ruptura: R$ 836,96_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.048,73_x000D_
+• Valor em ruptura: R$ 3.266,47_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.199,01_x000D_
+• Valor em ruptura: R$ 278,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 14.621,53_x000D_
+• Valor em ruptura: R$ 5.059,93_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.427,02_x000D_
+• Valor em ruptura: R$ 588,41_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.828,67_x000D_
+• Valor em ruptura: R$ 321,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 984,68_x000D_
+• Valor em ruptura: R$ 6.924,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.079,08_x000D_
+• Valor em ruptura: R$ 12.053,17_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.471,65_x000D_
+• Valor em ruptura: R$ 1.071,25_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.032,71_x000D_
+• Valor em ruptura: R$ 7.269,85_x000D_
+• Valor mínimo de frete: R$ 50,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.218,80_x000D_
+• Valor em ruptura: R$ 1.081,21_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 19.672,77_x000D_
+• Valor em ruptura: R$ 5.811,10_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 23.032,99_x000D_
+• Valor em ruptura: R$ 1.405,81_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.370,95_x000D_
+• Valor em ruptura: R$ 2.917,89_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.614,17_x000D_
+• Valor em ruptura: R$ 3.782,93_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.175,61_x000D_
+• Valor em ruptura: R$ 1.325,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 10.465,95_x000D_
+• Valor em ruptura: R$ 778,37_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.178,85_x000D_
+• Valor em ruptura: R$ 188,35_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 16.692,98_x000D_
+• Valor em ruptura: R$ 1.187,24_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.898,78_x000D_
+• Valor em ruptura: R$ 169,82_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.098,78_x000D_
+• Valor em ruptura: R$ 249,32_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.270,58_x000D_
+• Valor em ruptura: R$ 588,41_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.572,85_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.491,89_x000D_
+• Valor em ruptura: R$ 529,10_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 248,52_x000D_
+• Valor em ruptura: R$ 518,52_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.785,39_x000D_
+• Valor em ruptura: R$ 863,11_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.898,96_x000D_
+• Valor em ruptura: R$ 1.229,24_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 999,64_x000D_
+• Valor em ruptura: R$ 2.063,17_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 540,43_x000D_
+• Valor em ruptura: R$ 6.653,79_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 485,21_x000D_
+• Valor em ruptura: R$ 5.296,31_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.070,36_x000D_
+• Valor em ruptura: R$ 2.311,78_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.703,70_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 965,31_x000D_
+• Valor em ruptura: R$ 13.017,23_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.432,60_x000D_
+• Valor em ruptura: R$ 557,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.042,03_x000D_
+• Valor em ruptura: R$ 863,98_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.964,61_x000D_
+• Valor em ruptura: R$ 2.460,65_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.836,34_x000D_
+• Valor em ruptura: R$ 294,20_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 9.225,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 525,68_x000D_
+• Valor em ruptura: R$ 289,13_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.895,29_x000D_
+• Valor em ruptura: R$ 28.877,19_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.603,21_x000D_
+• Valor em ruptura: R$ 6.271,65_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.275,41_x000D_
+• Valor em ruptura: R$ 200.672,97_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.381,30_x000D_
+• Valor em ruptura: R$ 3.936,50_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 55.154,85_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.167,67_x000D_
+• Valor em ruptura: R$ 2.017,56_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 19.328,40_x000D_
+• Valor em ruptura: R$ 409,41_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.788,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 887,67_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 10.167,26_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 33.033,43_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.676,72_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 19.255,88_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.235,69_x000D_
+• Valor em ruptura: R$ 1.129,19_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
 </sst>
 </file>
@@ -2126,7 +1878,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E342"/>
+  <dimension ref="A1:E331"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -2182,7 +1934,7 @@
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>853926</v>
+        <v>853853</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -2196,7 +1948,7 @@
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>853853</v>
+        <v>850631</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
@@ -2205,68 +1957,68 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>773</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>850631</v>
+        <v>855347</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>855347</v>
+        <v>855752</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>134</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>853943</v>
+        <v>853567</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>773</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>855177</v>
+        <v>854781</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>2078</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>853567</v>
+        <v>848783</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
@@ -2275,12 +2027,12 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>3060</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>854781</v>
+        <v>853426</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
@@ -2289,26 +2041,26 @@
         <v>5</v>
       </c>
       <c r="E11">
-        <v>3093</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>848783</v>
+        <v>854985</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>3075</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>853426</v>
+        <v>849811</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
@@ -2317,40 +2069,40 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>3075</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>854985</v>
+        <v>855293</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>2090</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>854061</v>
+        <v>849918</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>589</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>849811</v>
+        <v>849917</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>17</v>
@@ -2359,337 +2111,337 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>3058</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>855293</v>
+        <v>850200</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>2072</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>849918</v>
+        <v>852593</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>750</v>
+        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>849917</v>
+        <v>852631</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>3089</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>850200</v>
+        <v>853998</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>1021</v>
+        <v>722</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>852593</v>
+        <v>853852</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>632</v>
+        <v>773</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>852631</v>
+        <v>854933</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>3085</v>
+        <v>983</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>853998</v>
+        <v>854931</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>722</v>
+        <v>983</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>855341</v>
+        <v>854585</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>3029</v>
+        <v>933</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>853852</v>
+        <v>855295</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>773</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>854933</v>
+        <v>854330</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>983</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>854931</v>
+        <v>855330</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>983</v>
+        <v>703</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>854237</v>
+        <v>855731</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>854585</v>
+        <v>854385</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>933</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>855295</v>
+        <v>855232</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>377</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>854330</v>
+        <v>855480</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>281</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>855330</v>
+        <v>854374</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>854940</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33">
         <v>703</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>854385</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33">
-        <v>2090</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>855232</v>
+        <v>855501</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>855480</v>
+        <v>855764</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>3037</v>
+        <v>642</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>854374</v>
+        <v>855761</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>3069</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>854940</v>
+        <v>855759</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>855501</v>
+        <v>855758</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>855052</v>
+        <v>855756</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
-        <v>380</v>
+        <v>642</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>855598</v>
+        <v>855753</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
@@ -2700,24 +2452,24 @@
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>854415</v>
+        <v>855749</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>854840</v>
+        <v>855748</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -2728,268 +2480,268 @@
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>855376</v>
+        <v>855683</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>1021</v>
+        <v>642</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>855350</v>
+        <v>855746</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44">
-        <v>614</v>
+        <v>642</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>854934</v>
+        <v>855686</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>2064</v>
+        <v>699</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>854891</v>
+        <v>855376</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>2051</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>855357</v>
+        <v>855350</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>699</v>
+        <v>614</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>853816</v>
+        <v>854934</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>880</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>855348</v>
+        <v>855823</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>134</v>
+        <v>614</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>855266</v>
+        <v>855783</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50">
-        <v>380</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>855386</v>
+        <v>855357</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>737</v>
+        <v>699</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>855484</v>
+        <v>855666</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>699</v>
+        <v>388</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>855359</v>
+        <v>855872</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>699</v>
+        <v>625</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>854338</v>
+        <v>855484</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>281</v>
+        <v>699</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>854345</v>
+        <v>855896</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>281</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855512</v>
+        <v>855834</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>3057</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>855069</v>
+        <v>855359</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>854773</v>
+        <v>855512</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>90</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>855393</v>
+        <v>855659</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>90</v>
+        <v>669</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>855203</v>
+        <v>855069</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>855289</v>
+        <v>854773</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61">
-        <v>580</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
@@ -2997,7 +2749,7 @@
         <v>855596</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
@@ -3006,418 +2758,418 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>855221</v>
+        <v>855742</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A64">
+        <v>855690</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>855553</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D64" t="s">
-        <v>5</v>
-      </c>
-      <c r="E64">
+      <c r="B65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65">
         <v>951</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>855033</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D65" t="s">
-        <v>5</v>
-      </c>
-      <c r="E65">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>855483</v>
+        <v>855909</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>2051</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>854315</v>
+        <v>855905</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>281</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>854320</v>
+        <v>855033</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>723</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>854301</v>
+        <v>855766</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>854306</v>
+        <v>854367</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>281</v>
+        <v>614</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>854312</v>
+        <v>855737</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>281</v>
+        <v>614</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>854216</v>
+        <v>855242</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>1027</v>
+        <v>380</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>854756</v>
+        <v>855338</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>854809</v>
+        <v>855077</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>854367</v>
+        <v>855466</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>614</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>854979</v>
+        <v>855421</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>3078</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>854944</v>
+        <v>855635</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>703</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>854701</v>
+        <v>855615</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>854881</v>
+        <v>853459</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>854357</v>
+        <v>850430</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>281</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>855242</v>
+        <v>855274</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>380</v>
+        <v>951</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>855030</v>
+        <v>855894</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>723</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>855475</v>
+        <v>855807</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>854683</v>
+        <v>855797</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>951</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>855338</v>
+        <v>855687</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>614</v>
+        <v>699</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>855077</v>
+        <v>855812</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>380</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>855423</v>
+        <v>855616</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>951</v>
+        <v>614</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>855466</v>
+        <v>855549</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>855421</v>
+        <v>855580</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>853459</v>
+        <v>855554</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>850430</v>
+        <v>855718</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>855274</v>
+        <v>855514</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
@@ -3426,432 +3178,432 @@
         <v>951</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>854834</v>
+        <v>855440</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>854980</v>
+        <v>855649</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>3078</v>
+        <v>916</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>855548</v>
+        <v>855648</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>699</v>
+        <v>916</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>854977</v>
+        <v>855651</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>699</v>
+        <v>916</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>853295</v>
+        <v>854932</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>2027</v>
+        <v>699</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>854749</v>
+        <v>855476</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>90</v>
+        <v>699</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>855234</v>
+        <v>855062</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>699</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>855365</v>
+        <v>854263</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>699</v>
+        <v>574</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>855449</v>
+        <v>855384</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>593</v>
+        <v>90</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>855138</v>
+        <v>855787</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>854702</v>
+        <v>855699</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>703</v>
+        <v>429</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>855549</v>
+        <v>855560</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>700</v>
+        <v>722</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>855580</v>
+        <v>854319</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>2027</v>
+        <v>574</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>855056</v>
+        <v>854314</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>625</v>
+        <v>574</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>855554</v>
+        <v>855426</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>614</v>
+        <v>429</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>855514</v>
+        <v>855506</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>951</v>
+        <v>569</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>855440</v>
+        <v>855051</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>922</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>854348</v>
+        <v>855790</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>281</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>854354</v>
+        <v>855794</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>281</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>854361</v>
+        <v>855697</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>281</v>
+        <v>703</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>854771</v>
+        <v>855890</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>854932</v>
+        <v>855603</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>699</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>855024</v>
+        <v>855498</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>854935</v>
+        <v>855136</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>2027</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>855476</v>
+        <v>855496</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>699</v>
+        <v>811</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>855062</v>
+        <v>855566</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>184</v>
+        <v>92</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>3072</v>
+        <v>614</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>853206</v>
+        <v>855595</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>614</v>
+        <v>90</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>854305</v>
+        <v>855556</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>574</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>854263</v>
+        <v>855627</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>574</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>855047</v>
+        <v>855730</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>1021</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>855384</v>
+        <v>853358</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
@@ -3862,850 +3614,850 @@
     </row>
     <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>854606</v>
+        <v>855796</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>854356</v>
+        <v>855468</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855284</v>
+        <v>855229</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>855560</v>
+        <v>855660</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>722</v>
+        <v>703</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>854387</v>
+        <v>855352</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>854112</v>
+        <v>855001</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>188</v>
+        <v>14</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>723</v>
+        <v>874</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>854319</v>
+        <v>854984</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>854314</v>
+        <v>855601</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>854807</v>
+        <v>855887</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>836</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>855426</v>
+        <v>855091</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>429</v>
+        <v>281</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>855513</v>
+        <v>855563</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>855051</v>
+        <v>855692</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>3078</v>
+        <v>574</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>854999</v>
+        <v>855237</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>2041</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>855500</v>
+        <v>855248</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>829</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>855366</v>
+        <v>855678</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>639</v>
+        <v>281</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>855498</v>
+        <v>855258</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>3097</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>855428</v>
+        <v>855079</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>3035</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>855136</v>
+        <v>851354</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>854833</v>
+        <v>851356</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>855496</v>
+        <v>851357</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>855172</v>
+        <v>854953</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>854884</v>
+        <v>854954</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>855566</v>
+        <v>851359</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>855595</v>
+        <v>854955</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>855556</v>
+        <v>854956</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>2041</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>855315</v>
+        <v>844931</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>3034</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>855065</v>
+        <v>851348</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>853358</v>
+        <v>851349</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>855468</v>
+        <v>854602</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D152" t="s">
+        <v>5</v>
+      </c>
+      <c r="E152">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>854603</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D152" t="s">
-        <v>5</v>
-      </c>
-      <c r="E152">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A153">
-        <v>855229</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>854734</v>
+        <v>854604</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>854942</v>
+        <v>855576</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>855352</v>
+        <v>855261</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>855538</v>
+        <v>855254</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>855001</v>
+        <v>855272</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>854347</v>
+        <v>855255</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>854984</v>
+        <v>855264</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>855091</v>
+        <v>855271</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>281</v>
+        <v>906</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>855453</v>
+        <v>855436</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>614</v>
+        <v>906</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>855563</v>
+        <v>855438</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>855451</v>
+        <v>853930</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>203</v>
+        <v>46</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>855083</v>
+        <v>855494</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>855237</v>
+        <v>854939</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>3060</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>855248</v>
+        <v>855297</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>205</v>
+        <v>71</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>854697</v>
+        <v>854777</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>855461</v>
+        <v>855773</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>855275</v>
+        <v>855278</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>90</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>855258</v>
+        <v>855781</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>855079</v>
+        <v>853734</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>854695</v>
+        <v>853738</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>380</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>855119</v>
+        <v>852720</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>3055</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>851354</v>
+        <v>855884</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>851356</v>
+        <v>855583</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
-        <v>60</v>
+        <v>778</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>851357</v>
+        <v>854686</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
       <c r="E177">
-        <v>60</v>
+        <v>118</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>854953</v>
+        <v>855582</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
       <c r="E178">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>854954</v>
+        <v>855374</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="E179">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>851359</v>
+        <v>855636</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>854955</v>
+        <v>854925</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>854956</v>
+        <v>855610</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182">
-        <v>60</v>
+        <v>979</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>844931</v>
+        <v>855727</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183">
-        <v>60</v>
+        <v>257</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>851348</v>
+        <v>855543</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -4716,10 +4468,10 @@
     </row>
     <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>851349</v>
+        <v>855765</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -4730,10 +4482,10 @@
     </row>
     <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>854602</v>
+        <v>855492</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -4742,1540 +4494,1272 @@
         <v>60</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>854603</v>
+        <v>855858</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>854604</v>
+        <v>854724</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188">
-        <v>60</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>855576</v>
+        <v>855382</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>407</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>855261</v>
+        <v>855578</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190">
-        <v>906</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>854899</v>
+        <v>848786</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191">
-        <v>906</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>855254</v>
+        <v>855355</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192">
-        <v>906</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>855272</v>
+        <v>855815</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>855255</v>
+        <v>854839</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
       </c>
       <c r="E194">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>855264</v>
+        <v>855782</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
       </c>
       <c r="E195">
-        <v>906</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>855271</v>
+        <v>854830</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
       </c>
       <c r="E196">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>855436</v>
+        <v>854835</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="D197" t="s">
         <v>5</v>
       </c>
       <c r="E197">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>855438</v>
+        <v>854051</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
       </c>
       <c r="E198">
-        <v>906</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>853930</v>
+        <v>855137</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199">
-        <v>979</v>
+        <v>375</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>855494</v>
+        <v>855906</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200">
-        <v>979</v>
+        <v>293</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>854939</v>
+        <v>855310</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
       </c>
       <c r="E201">
-        <v>1807</v>
+        <v>293</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>855297</v>
+        <v>855847</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202">
-        <v>381</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>854777</v>
+        <v>854579</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203">
-        <v>3</v>
+        <v>996</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>855278</v>
+        <v>852886</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>852719</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D205" t="s">
-        <v>5</v>
-      </c>
-      <c r="E205">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855072</v>
+      </c>
+      <c r="B205" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>852720</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D206" t="s">
-        <v>5</v>
-      </c>
-      <c r="E206">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854895</v>
+      </c>
+      <c r="B206" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>853734</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D207" t="s">
-        <v>5</v>
-      </c>
-      <c r="E207">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854917</v>
+      </c>
+      <c r="B207" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>853738</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D208" t="s">
-        <v>5</v>
-      </c>
-      <c r="E208">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>854503</v>
+      </c>
+      <c r="B208" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>855583</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D209" t="s">
-        <v>5</v>
-      </c>
-      <c r="E209">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854903</v>
+      </c>
+      <c r="B209" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>854686</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D210" t="s">
-        <v>5</v>
-      </c>
-      <c r="E210">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854494</v>
+      </c>
+      <c r="B210" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>852752</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D211" t="s">
-        <v>5</v>
-      </c>
-      <c r="E211">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854911</v>
+      </c>
+      <c r="B211" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>855582</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D212" t="s">
-        <v>5</v>
-      </c>
-      <c r="E212">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>854499</v>
+      </c>
+      <c r="B212" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>855374</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D213" t="s">
-        <v>5</v>
-      </c>
-      <c r="E213">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>854504</v>
+      </c>
+      <c r="B213" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>854925</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D214" t="s">
-        <v>5</v>
-      </c>
-      <c r="E214">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854908</v>
+      </c>
+      <c r="B214" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>852562</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D215" t="s">
-        <v>5</v>
-      </c>
-      <c r="E215">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854910</v>
+      </c>
+      <c r="B215" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>855543</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D216" t="s">
-        <v>5</v>
-      </c>
-      <c r="E216">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854507</v>
+      </c>
+      <c r="B216" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>855547</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D217" t="s">
-        <v>5</v>
-      </c>
-      <c r="E217">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854906</v>
+      </c>
+      <c r="B217" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>855492</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D218" t="s">
-        <v>5</v>
-      </c>
-      <c r="E218">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>854907</v>
+      </c>
+      <c r="B218" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>854724</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D219" t="s">
-        <v>5</v>
-      </c>
-      <c r="E219">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>850108</v>
+      </c>
+      <c r="B219" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>855382</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D220" t="s">
-        <v>5</v>
-      </c>
-      <c r="E220">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>850002</v>
+      </c>
+      <c r="B220" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>855578</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D221" t="s">
-        <v>5</v>
-      </c>
-      <c r="E221">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855820</v>
+      </c>
+      <c r="B221" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>855400</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D222" t="s">
-        <v>5</v>
-      </c>
-      <c r="E222">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855830</v>
+      </c>
+      <c r="B222" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>848786</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D223" t="s">
-        <v>5</v>
-      </c>
-      <c r="E223">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>848673</v>
+      </c>
+      <c r="B223" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>855355</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D224" t="s">
-        <v>5</v>
-      </c>
-      <c r="E224">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>855246</v>
+      </c>
+      <c r="B224" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>854839</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D225" t="s">
-        <v>5</v>
-      </c>
-      <c r="E225">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>855662</v>
+      </c>
+      <c r="B225" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>854225</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D226" t="s">
-        <v>5</v>
-      </c>
-      <c r="E226">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>849969</v>
+      </c>
+      <c r="B226" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>854830</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D227" t="s">
-        <v>5</v>
-      </c>
-      <c r="E227">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>849444</v>
+      </c>
+      <c r="B227" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>854832</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D228" t="s">
-        <v>5</v>
-      </c>
-      <c r="E228">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>855178</v>
+      </c>
+      <c r="B228" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>854835</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D229" t="s">
-        <v>5</v>
-      </c>
-      <c r="E229">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855180</v>
+      </c>
+      <c r="B229" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>854051</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D230" t="s">
-        <v>5</v>
-      </c>
-      <c r="E230">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855181</v>
+      </c>
+      <c r="B230" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>855137</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D231" t="s">
-        <v>5</v>
-      </c>
-      <c r="E231">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855182</v>
+      </c>
+      <c r="B231" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>855310</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D232" t="s">
-        <v>5</v>
-      </c>
-      <c r="E232">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>855185</v>
+      </c>
+      <c r="B232" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>854579</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D233" t="s">
-        <v>5</v>
-      </c>
-      <c r="E233">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+        <v>855189</v>
+      </c>
+      <c r="B233" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>852886</v>
+        <v>855191</v>
       </c>
       <c r="B234" t="s">
-        <v>79</v>
-      </c>
-      <c r="D234" t="s">
-        <v>5</v>
-      </c>
-      <c r="E234">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>843776</v>
+        <v>855192</v>
       </c>
       <c r="B235" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>843780</v>
+        <v>855193</v>
       </c>
       <c r="B236" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>843785</v>
+        <v>855194</v>
       </c>
       <c r="B237" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>844518</v>
+        <v>855195</v>
       </c>
       <c r="B238" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>844527</v>
+        <v>855196</v>
       </c>
       <c r="B239" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>846411</v>
+        <v>855197</v>
       </c>
       <c r="B240" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>846414</v>
+        <v>855198</v>
       </c>
       <c r="B241" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>847008</v>
+        <v>855199</v>
       </c>
       <c r="B242" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>851106</v>
+        <v>855200</v>
       </c>
       <c r="B243" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>851109</v>
+        <v>855201</v>
       </c>
       <c r="B244" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>851875</v>
+        <v>855202</v>
       </c>
       <c r="B245" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>851876</v>
+        <v>855204</v>
       </c>
       <c r="B246" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>851881</v>
+        <v>855205</v>
       </c>
       <c r="B247" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>852454</v>
+        <v>855206</v>
       </c>
       <c r="B248" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>846997</v>
+        <v>855207</v>
       </c>
       <c r="B249" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>847009</v>
+        <v>855208</v>
       </c>
       <c r="B250" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>848642</v>
+        <v>855209</v>
       </c>
       <c r="B251" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>851100</v>
+        <v>854887</v>
       </c>
       <c r="B252" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>851115</v>
+        <v>854890</v>
       </c>
       <c r="B253" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>852345</v>
+        <v>854493</v>
       </c>
       <c r="B254" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>852346</v>
+        <v>854498</v>
       </c>
       <c r="B255" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>852352</v>
+        <v>854896</v>
       </c>
       <c r="B256" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>852452</v>
+        <v>854894</v>
       </c>
       <c r="B257" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>854969</v>
+        <v>851751</v>
       </c>
       <c r="B258" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>855562</v>
+        <v>849662</v>
       </c>
       <c r="B259" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>852386</v>
+        <v>853691</v>
       </c>
       <c r="B260" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>855246</v>
+        <v>849622</v>
       </c>
       <c r="B261" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>849283</v>
+        <v>849563</v>
       </c>
       <c r="B262" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>849405</v>
+        <v>855289</v>
       </c>
       <c r="B263" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>849445</v>
+        <v>854257</v>
       </c>
       <c r="B264" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>849452</v>
+        <v>854288</v>
       </c>
       <c r="B265" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>849464</v>
+        <v>854260</v>
       </c>
       <c r="B266" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>849499</v>
+        <v>854255</v>
       </c>
       <c r="B267" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>849478</v>
+        <v>854272</v>
       </c>
       <c r="B268" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>849969</v>
+        <v>849613</v>
       </c>
       <c r="B269" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>850323</v>
+        <v>854308</v>
       </c>
       <c r="B270" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>854479</v>
+        <v>854301</v>
       </c>
       <c r="B271" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>854482</v>
+        <v>854306</v>
       </c>
       <c r="B272" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>849444</v>
+        <v>854311</v>
       </c>
       <c r="B273" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>854894</v>
+        <v>854312</v>
       </c>
       <c r="B274" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>851751</v>
+        <v>854310</v>
       </c>
       <c r="B275" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>849662</v>
+        <v>849183</v>
       </c>
       <c r="B276" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>853691</v>
+        <v>849750</v>
       </c>
       <c r="B277" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>849622</v>
+        <v>849603</v>
       </c>
       <c r="B278" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>849563</v>
+        <v>852382</v>
       </c>
       <c r="B279" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>854288</v>
+        <v>849376</v>
       </c>
       <c r="B280" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>854260</v>
+        <v>849832</v>
       </c>
       <c r="B281" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>854255</v>
+        <v>849559</v>
       </c>
       <c r="B282" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>854272</v>
+        <v>849847</v>
       </c>
       <c r="B283" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>849613</v>
+        <v>853295</v>
       </c>
       <c r="B284" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>849183</v>
+        <v>849636</v>
       </c>
       <c r="B285" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>849750</v>
+        <v>849652</v>
       </c>
       <c r="B286" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>849603</v>
+        <v>849913</v>
       </c>
       <c r="B287" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>852382</v>
+        <v>855273</v>
       </c>
       <c r="B288" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>849376</v>
+        <v>855644</v>
       </c>
       <c r="B289" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>849832</v>
+        <v>855654</v>
       </c>
       <c r="B290" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>849559</v>
+        <v>849940</v>
       </c>
       <c r="B291" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>849659</v>
+        <v>849567</v>
       </c>
       <c r="B292" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>849663</v>
+        <v>849780</v>
       </c>
       <c r="B293" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>849847</v>
+        <v>849773</v>
       </c>
       <c r="B294" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>849636</v>
+        <v>849792</v>
       </c>
       <c r="B295" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>849652</v>
+        <v>849812</v>
       </c>
       <c r="B296" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>849913</v>
+        <v>849639</v>
       </c>
       <c r="B297" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>855273</v>
+        <v>853427</v>
       </c>
       <c r="B298" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>849940</v>
+        <v>853538</v>
       </c>
       <c r="B299" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>849567</v>
+        <v>849821</v>
       </c>
       <c r="B300" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>849780</v>
+        <v>848706</v>
       </c>
       <c r="B301" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>849773</v>
+        <v>849882</v>
       </c>
       <c r="B302" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>849792</v>
+        <v>852307</v>
       </c>
       <c r="B303" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>849812</v>
+        <v>854060</v>
       </c>
       <c r="B304" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>849639</v>
+        <v>855485</v>
       </c>
       <c r="B305" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>849796</v>
+        <v>853428</v>
       </c>
       <c r="B306" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>849821</v>
+        <v>853773</v>
       </c>
       <c r="B307" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>848706</v>
+        <v>855806</v>
       </c>
       <c r="B308" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>849882</v>
+        <v>855735</v>
       </c>
       <c r="B309" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>850013</v>
+        <v>855774</v>
       </c>
       <c r="B310" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>852307</v>
+        <v>855538</v>
       </c>
       <c r="B311" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>854060</v>
+        <v>855901</v>
       </c>
       <c r="B312" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>855485</v>
+        <v>855895</v>
       </c>
       <c r="B313" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>853428</v>
+        <v>855461</v>
       </c>
       <c r="B314" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>855455</v>
+        <v>855574</v>
       </c>
       <c r="B315" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>855521</v>
+        <v>855579</v>
       </c>
       <c r="B316" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>855588</v>
+        <v>855640</v>
       </c>
       <c r="B317" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>855568</v>
+        <v>855642</v>
       </c>
       <c r="B318" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>855413</v>
+        <v>855809</v>
       </c>
       <c r="B319" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>855429</v>
+        <v>855257</v>
       </c>
       <c r="B320" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>855574</v>
+        <v>855802</v>
       </c>
       <c r="B321" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>855579</v>
+        <v>855822</v>
       </c>
       <c r="B322" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>855257</v>
+        <v>855703</v>
       </c>
       <c r="B323" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>855442</v>
+        <v>855518</v>
       </c>
       <c r="B324" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>855349</v>
+        <v>855524</v>
       </c>
       <c r="B325" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>855473</v>
+        <v>855843</v>
       </c>
       <c r="B326" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>855534</v>
+        <v>855811</v>
       </c>
       <c r="B327" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>855587</v>
+        <v>855893</v>
       </c>
       <c r="B328" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>855518</v>
+        <v>855819</v>
       </c>
       <c r="B329" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>855540</v>
+        <v>855517</v>
       </c>
       <c r="B330" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>855524</v>
+        <v>855708</v>
       </c>
       <c r="B331" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332">
-        <v>855593</v>
-      </c>
-      <c r="B332" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333">
-        <v>855488</v>
-      </c>
-      <c r="B333" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334">
-        <v>855559</v>
-      </c>
-      <c r="B334" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335">
-        <v>854186</v>
-      </c>
-      <c r="B335" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336">
-        <v>855590</v>
-      </c>
-      <c r="B336" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337">
-        <v>855517</v>
-      </c>
-      <c r="B337" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338">
-        <v>855070</v>
-      </c>
-      <c r="B338" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339">
-        <v>855497</v>
-      </c>
-      <c r="B339" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340">
-        <v>855333</v>
-      </c>
-      <c r="B340" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341">
-        <v>855427</v>
-      </c>
-      <c r="B341" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342">
-        <v>855493</v>
-      </c>
-      <c r="B342" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20989C11-7AAA-4474-BA4D-30EA0923E1A6}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E52829F-B9C6-4A10-A782-D5164B8CC837}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="208">
   <si>
     <t>Pedido</t>
   </si>
@@ -198,14 +198,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 757,35_x000D_
-• Valor em ruptura: R$ 7.595,24_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -228,14 +220,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 20.730,54_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
@@ -246,14 +230,6 @@
 • Valor mínimo de frete: R$ 6.250,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 32.188,83_x000D_
-• Valor em ruptura: R$ 48.601,27_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -362,14 +338,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 6.741,46_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 31.523,73_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -418,48 +386,8 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.733,80_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 57.852,90_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 275.948,41_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 142.341,65_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 12.872,38_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 103.262,47_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -481,14 +409,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.450,87_x000D_
-• Valor em ruptura: R$ 71,37_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.842,47_x000D_
 • Valor em ruptura: R$ 1.597,13_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -622,14 +542,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.667,85_x000D_
-• Valor em ruptura: R$ 3.903,59_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -641,14 +553,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 644,47_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.174,99_x000D_
 • Valor em ruptura: R$ 252,48_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -662,22 +566,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.702,48_x000D_
-• Valor em ruptura: R$ 1.517,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.967,87_x000D_
-• Valor em ruptura: R$ 4.791,54_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -713,14 +601,6 @@
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.309,75_x000D_
-• Valor em ruptura: R$ 15.232,59_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 16.421,62_x000D_
 • Valor em ruptura: R$ 760,31_x000D_
 • Valor mínimo de frete: R$ 50,00</t>
@@ -761,30 +641,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.249,18_x000D_
-• Valor em ruptura: R$ 250,87_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.224,71_x000D_
-• Valor em ruptura: R$ 1.368,29_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.738,13_x000D_
-• Valor em ruptura: R$ 3.066,63_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.151,19_x000D_
 • Valor em ruptura: R$ 836,96_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -811,22 +667,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 2.550,81_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 13.999,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 23.808,26_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -956,14 +796,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 19.132,66_x000D_
-• Valor em ruptura: R$ 524,77_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 64.407,33_x000D_
 • Valor em ruptura: R$ 2.163,98_x000D_
 • Valor mínimo de frete: R$ 7.325,00</t>
@@ -985,14 +817,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.220,47_x000D_
-• Valor em ruptura: R$ 1.094,41_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1004,14 +828,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.311,94_x000D_
-• Valor em ruptura: R$ 530,07_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.731,80_x000D_
 • Valor em ruptura: R$ 424,75_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1041,22 +857,6 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.272,64_x000D_
-• Valor em ruptura: R$ 321,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.417,47_x000D_
-• Valor em ruptura: R$ 321,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1097,27 +897,11 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 14.621,53_x000D_
-• Valor em ruptura: R$ 5.059,93_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.427,02_x000D_
 • Valor em ruptura: R$ 588,41_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.828,67_x000D_
-• Valor em ruptura: R$ 321,97_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1169,14 +953,6 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 23.032,99_x000D_
-• Valor em ruptura: R$ 1.405,81_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1260,32 +1036,8 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.491,89_x000D_
-• Valor em ruptura: R$ 529,10_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 248,52_x000D_
 • Valor em ruptura: R$ 518,52_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.785,39_x000D_
-• Valor em ruptura: R$ 863,11_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.898,96_x000D_
-• Valor em ruptura: R$ 1.229,24_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1324,14 +1076,6 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.703,70_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 965,31_x000D_
 • Valor em ruptura: R$ 13.017,23_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1380,14 +1124,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 9.225,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 525,68_x000D_
 • Valor em ruptura: R$ 289,13_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1441,14 +1177,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 19.328,40_x000D_
-• Valor em ruptura: R$ 409,41_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1477,14 +1205,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 33.033,43_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.676,72_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -1502,6 +1222,454 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 8.235,69_x000D_
 • Valor em ruptura: R$ 1.129,19_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.282,45_x000D_
+• Valor em ruptura: R$ 239,79_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 993,44_x000D_
+• Valor em ruptura: R$ 1.631,01_x000D_
+• Valor mínimo de frete: R$ 7.175,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.388,00_x000D_
+• Valor em ruptura: R$ 130,31_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.812,61_x000D_
+• Valor em ruptura: R$ 394,53_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.175,20_x000D_
+• Valor em ruptura: R$ 488,86_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.540,79_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.027,19_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.802,12_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 10.090,64_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.774,93_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.315,71_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 83.752,29_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.232,78_x000D_
+• Valor em ruptura: R$ 339,91_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.306,64_x000D_
+• Valor em ruptura: R$ 2.795,44_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.246,17_x000D_
+• Valor em ruptura: R$ 186,57_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 19.132,66_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.717,46_x000D_
+• Valor em ruptura: R$ 1.295,81_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.144,93_x000D_
+• Valor em ruptura: R$ 169,95_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 9.311,94_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.176,51_x000D_
+• Valor em ruptura: R$ 1.394,93_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.944,27_x000D_
+• Valor em ruptura: R$ 276,20_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.465,21_x000D_
+• Valor em ruptura: R$ 294,20_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 11.563,71_x000D_
+• Valor em ruptura: R$ 281,46_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.223,85_x000D_
+• Valor em ruptura: R$ 1.012,70_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.927,11_x000D_
+• Valor em ruptura: R$ 4.164,43_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 526,59_x000D_
+• Valor em ruptura: R$ 12.658,73_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.476,60_x000D_
+• Valor em ruptura: R$ 3.010,39_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.017,32_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.243,95_x000D_
+• Valor em ruptura: R$ 584,69_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 10.743,59_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.411,83_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 6.577,71_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 15.012,05_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 23.312,97_x000D_
+• Valor em ruptura: R$ 1.125,83_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 8.548,75_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.783,52_x000D_
+• Valor em ruptura: R$ 1.533,32_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.972,20_x000D_
+• Valor em ruptura: R$ 289,11_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.712,70_x000D_
+• Valor em ruptura: R$ 308,29_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.663,09_x000D_
+• Valor em ruptura: R$ 4.712,07_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.497,17_x000D_
+• Valor em ruptura: R$ 4.269,02_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.768,09_x000D_
+• Valor em ruptura: R$ 169,95_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.924,67_x000D_
+• Valor em ruptura: R$ 2.668,16_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 12.428,70_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.064,07_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.246,79_x000D_
+• Valor em ruptura: R$ 557,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.888,43_x000D_
+• Valor em ruptura: R$ 288,32_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.631,59_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.143,86_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 10.733,18_x000D_
+• Valor em ruptura: R$ 3.587,88_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.934,09_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.460,95_x000D_
+• Valor em ruptura: R$ 18.467,01_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.144,28_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.086,03_x000D_
+• Valor em ruptura: R$ 4.624,99_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.327,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 11.030,97_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.660,61_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
 </sst>
@@ -1878,7 +2046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E331"/>
+  <dimension ref="A1:E409"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -1965,7 +2133,7 @@
         <v>855347</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1979,7 +2147,7 @@
         <v>855752</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -2049,7 +2217,7 @@
         <v>854985</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -2077,7 +2245,7 @@
         <v>855293</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -2186,24 +2354,24 @@
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>854933</v>
+        <v>856033</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>983</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>854931</v>
+        <v>854933</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -2214,192 +2382,192 @@
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>854585</v>
+        <v>854931</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>933</v>
+        <v>983</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>855295</v>
+        <v>854585</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>377</v>
+        <v>933</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>854330</v>
+        <v>855295</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>281</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>855330</v>
+        <v>854330</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>703</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
+        <v>855330</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>855731</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28">
+      <c r="B29" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29">
         <v>1021</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A29">
+    <row r="30" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>854385</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29">
+      <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30">
         <v>2090</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>855232</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30">
-        <v>2084</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>855480</v>
+        <v>855232</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>3037</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>854374</v>
+        <v>855480</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>3069</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>854940</v>
+        <v>855445</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>703</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>855501</v>
+        <v>854374</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>854940</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35">
         <v>703</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>855764</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35">
-        <v>642</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>855761</v>
+        <v>855501</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>855759</v>
+        <v>855764</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
@@ -2408,12 +2576,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>855758</v>
+        <v>855761</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2424,10 +2592,10 @@
     </row>
     <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>855756</v>
+        <v>855759</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -2438,10 +2606,10 @@
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>855753</v>
+        <v>855758</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
@@ -2450,12 +2618,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>855749</v>
+        <v>855756</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2464,12 +2632,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>855748</v>
+        <v>855753</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -2480,10 +2648,10 @@
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>855683</v>
+        <v>855749</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2492,12 +2660,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>855746</v>
+        <v>855748</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
@@ -2508,402 +2676,402 @@
     </row>
     <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>855686</v>
+        <v>855683</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>855376</v>
+        <v>855746</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>1021</v>
+        <v>642</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>855350</v>
+        <v>856005</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>614</v>
+        <v>773</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>854934</v>
+        <v>855686</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>2064</v>
+        <v>699</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>855823</v>
+        <v>856027</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>614</v>
+        <v>704</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>855783</v>
+        <v>855376</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50">
-        <v>748</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>855357</v>
+        <v>855350</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>699</v>
+        <v>614</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>855666</v>
+        <v>854934</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>388</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>855872</v>
+        <v>855823</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>625</v>
+        <v>614</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>855484</v>
+        <v>855783</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>699</v>
+        <v>748</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>855896</v>
+        <v>855357</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>2084</v>
+        <v>699</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855834</v>
+        <v>855666</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>2051</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>855359</v>
+        <v>855872</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>699</v>
+        <v>625</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>855512</v>
+        <v>856043</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>3057</v>
+        <v>737</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>855659</v>
+        <v>855484</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>669</v>
+        <v>699</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>855069</v>
+        <v>855896</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>854773</v>
+        <v>855834</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61">
-        <v>90</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>855596</v>
+        <v>855359</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
       </c>
       <c r="E62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>855742</v>
+        <v>855512</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
-        <v>614</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>855690</v>
+        <v>855659</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>855553</v>
+        <v>855069</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65">
-        <v>951</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>855909</v>
+        <v>854773</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>380</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>855905</v>
+        <v>855596</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>855033</v>
+        <v>855742</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>723</v>
+        <v>614</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>855766</v>
+        <v>855690</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>854367</v>
+        <v>855553</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>614</v>
+        <v>951</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>855737</v>
+        <v>855949</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>614</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>855242</v>
+        <v>855033</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>380</v>
+        <v>723</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>855338</v>
+        <v>855766</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
@@ -2912,334 +3080,334 @@
         <v>614</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>855077</v>
+        <v>856008</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>855466</v>
+        <v>855934</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>90</v>
+        <v>614</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>855421</v>
+        <v>856026</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>2088</v>
+        <v>699</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>855635</v>
+        <v>855737</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>380</v>
+        <v>614</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>855615</v>
+        <v>855242</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>853459</v>
+        <v>855338</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>2081</v>
+        <v>614</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>850430</v>
+        <v>855931</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>2081</v>
+        <v>699</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>855274</v>
+        <v>855077</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>951</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>855894</v>
+        <v>855466</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>593</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>855807</v>
+        <v>855421</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>855797</v>
+        <v>855635</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>855687</v>
+        <v>853459</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>855812</v>
+        <v>850430</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>2032</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>855616</v>
+        <v>855274</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>614</v>
+        <v>951</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>855549</v>
+        <v>856051</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>855580</v>
+        <v>855797</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>2027</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>855554</v>
+        <v>855687</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>614</v>
+        <v>699</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>855718</v>
+        <v>855812</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>811</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>855514</v>
+        <v>855616</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>951</v>
+        <v>614</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>855440</v>
+        <v>855549</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>922</v>
+        <v>700</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>855649</v>
+        <v>855580</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>916</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>855648</v>
+        <v>855718</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>855651</v>
+        <v>856000</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>916</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>854932</v>
+        <v>855997</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
@@ -3250,10 +3418,10 @@
     </row>
     <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>855476</v>
+        <v>855999</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
@@ -3262,1440 +3430,1440 @@
         <v>699</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>855062</v>
+        <v>855996</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>88</v>
+        <v>183</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>3072</v>
+        <v>699</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>854263</v>
+        <v>855998</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>574</v>
+        <v>699</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>855384</v>
+        <v>855994</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>855787</v>
+        <v>855995</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>90</v>
+        <v>699</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>855699</v>
+        <v>855514</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>429</v>
+        <v>951</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>855560</v>
+        <v>855440</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>722</v>
+        <v>922</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>854319</v>
+        <v>855649</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>574</v>
+        <v>916</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>854314</v>
+        <v>855648</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>574</v>
+        <v>916</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>855426</v>
+        <v>855651</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>429</v>
+        <v>916</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>855506</v>
+        <v>854932</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>569</v>
+        <v>699</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>855051</v>
+        <v>855062</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>855790</v>
+        <v>856034</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>2097</v>
+        <v>642</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>855794</v>
+        <v>854263</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>2097</v>
+        <v>574</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>855697</v>
+        <v>855384</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>703</v>
+        <v>90</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>855890</v>
+        <v>855787</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>703</v>
+        <v>90</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>855603</v>
+        <v>855699</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>2055</v>
+        <v>429</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>855498</v>
+        <v>855560</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>3097</v>
+        <v>722</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>855136</v>
+        <v>855876</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>3037</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>855496</v>
+        <v>854319</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>811</v>
+        <v>574</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>855566</v>
+        <v>855426</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>614</v>
+        <v>429</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>855595</v>
+        <v>855506</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>90</v>
+        <v>569</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>855556</v>
+        <v>855051</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>2041</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>855627</v>
+        <v>855790</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>3060</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>855730</v>
+        <v>855794</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>3060</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>853358</v>
+        <v>855697</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>30</v>
+        <v>189</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>90</v>
+        <v>703</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>855796</v>
+        <v>855890</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>90</v>
+        <v>703</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>855468</v>
+        <v>856003</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>294</v>
+        <v>90</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855229</v>
+        <v>855498</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>3049</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>855660</v>
+        <v>855985</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>855352</v>
+        <v>856011</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>3060</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>855001</v>
+        <v>855136</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>874</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>854984</v>
+        <v>855496</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>855601</v>
+        <v>855566</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>855887</v>
+        <v>855717</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>3060</v>
+        <v>281</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>855091</v>
+        <v>853358</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>281</v>
+        <v>90</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>855563</v>
+        <v>855796</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>855692</v>
+        <v>855468</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>855237</v>
+        <v>856024</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>3060</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>855248</v>
+        <v>855929</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>3060</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>855678</v>
+        <v>855229</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>855258</v>
+        <v>855660</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>3060</v>
+        <v>703</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>855079</v>
+        <v>855352</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>851354</v>
+        <v>855001</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>851356</v>
+        <v>854984</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>851357</v>
+        <v>855887</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>854953</v>
+        <v>855091</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>854954</v>
+        <v>855563</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>851359</v>
+        <v>855692</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>854955</v>
+        <v>856023</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>854956</v>
+        <v>855237</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>60</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>844931</v>
+        <v>855248</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>851348</v>
+        <v>855978</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>851349</v>
+        <v>855678</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>854602</v>
+        <v>855258</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>854603</v>
+        <v>855079</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>854604</v>
+        <v>855914</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>60</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>855576</v>
+        <v>855816</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>855261</v>
+        <v>851354</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>906</v>
+        <v>60</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>855254</v>
+        <v>851356</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>906</v>
+        <v>60</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>855272</v>
+        <v>851357</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>906</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>855255</v>
+        <v>854953</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>906</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>855264</v>
+        <v>854954</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>906</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>855271</v>
+        <v>851359</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>855436</v>
+        <v>854955</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>855438</v>
+        <v>854956</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>853930</v>
+        <v>844931</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>979</v>
+        <v>60</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>855494</v>
+        <v>851348</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>979</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>854939</v>
+        <v>851349</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>855297</v>
+        <v>854602</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>381</v>
+        <v>60</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>854777</v>
+        <v>855576</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>855773</v>
+        <v>855261</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>3081</v>
+        <v>906</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>855278</v>
+        <v>855254</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>855781</v>
+        <v>855272</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>694</v>
+        <v>906</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>853734</v>
+        <v>855271</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>853738</v>
+        <v>855438</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>852720</v>
+        <v>853930</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>1019</v>
+        <v>979</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>855884</v>
+        <v>855494</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>174</v>
+        <v>42</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>855583</v>
+        <v>854939</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>854686</v>
+        <v>855297</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
       <c r="E177">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>855582</v>
+        <v>855345</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
       <c r="E178">
-        <v>639</v>
+        <v>979</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>855374</v>
+        <v>855671</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="E179">
-        <v>293</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>855636</v>
+        <v>854777</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>854925</v>
+        <v>856010</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>855610</v>
+        <v>856018</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>855727</v>
+        <v>855278</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183">
-        <v>257</v>
+        <v>293</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>855543</v>
+        <v>855935</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
       <c r="E184">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>855765</v>
+        <v>855781</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185">
-        <v>60</v>
+        <v>694</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>855492</v>
+        <v>853734</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>855858</v>
+        <v>853738</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>854724</v>
+        <v>852720</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188">
-        <v>1807</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>855382</v>
+        <v>855884</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>855578</v>
+        <v>856059</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>848786</v>
+        <v>855583</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191">
-        <v>1807</v>
+        <v>778</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>855355</v>
+        <v>855990</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>855815</v>
+        <v>855374</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>854839</v>
+        <v>855636</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
       </c>
       <c r="E194">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>855782</v>
+        <v>855987</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
       </c>
       <c r="E195">
-        <v>3069</v>
+        <v>851</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>854830</v>
+        <v>856021</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
       </c>
       <c r="E196">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>854835</v>
+        <v>854925</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>184</v>
+        <v>14</v>
       </c>
       <c r="D197" t="s">
         <v>5</v>
       </c>
       <c r="E197">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>854051</v>
+        <v>855610</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
       </c>
       <c r="E198">
-        <v>1807</v>
+        <v>979</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>855137</v>
+        <v>855765</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199">
-        <v>375</v>
+        <v>60</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>855906</v>
+        <v>855492</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>855310</v>
+        <v>855858</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
@@ -4704,1062 +4872,1746 @@
         <v>293</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>855847</v>
+        <v>855382</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202">
-        <v>2024</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>854579</v>
+        <v>855578</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203">
-        <v>996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>852886</v>
+        <v>848786</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204">
-        <v>257</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>855072</v>
+        <v>855355</v>
       </c>
       <c r="B205" t="s">
-        <v>106</v>
+        <v>64</v>
+      </c>
+      <c r="D205" t="s">
+        <v>5</v>
+      </c>
+      <c r="E205">
+        <v>2024</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>854895</v>
+        <v>855815</v>
       </c>
       <c r="B206" t="s">
-        <v>106</v>
+        <v>148</v>
+      </c>
+      <c r="D206" t="s">
+        <v>5</v>
+      </c>
+      <c r="E206">
+        <v>1807</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>854917</v>
+        <v>856057</v>
       </c>
       <c r="B207" t="s">
-        <v>106</v>
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>5</v>
+      </c>
+      <c r="E207">
+        <v>979</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
+        <v>854839</v>
+      </c>
+      <c r="B208" t="s">
+        <v>84</v>
+      </c>
+      <c r="D208" t="s">
+        <v>5</v>
+      </c>
+      <c r="E208">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>855782</v>
+      </c>
+      <c r="B209" t="s">
+        <v>85</v>
+      </c>
+      <c r="D209" t="s">
+        <v>5</v>
+      </c>
+      <c r="E209">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>854835</v>
+      </c>
+      <c r="B210" t="s">
+        <v>149</v>
+      </c>
+      <c r="D210" t="s">
+        <v>5</v>
+      </c>
+      <c r="E210">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>855906</v>
+      </c>
+      <c r="B211" t="s">
+        <v>150</v>
+      </c>
+      <c r="D211" t="s">
+        <v>5</v>
+      </c>
+      <c r="E211">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>855310</v>
+      </c>
+      <c r="B212" t="s">
+        <v>65</v>
+      </c>
+      <c r="D212" t="s">
+        <v>5</v>
+      </c>
+      <c r="E212">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>855847</v>
+      </c>
+      <c r="B213" t="s">
+        <v>151</v>
+      </c>
+      <c r="D213" t="s">
+        <v>5</v>
+      </c>
+      <c r="E213">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>852886</v>
+      </c>
+      <c r="B214" t="s">
+        <v>47</v>
+      </c>
+      <c r="D214" t="s">
+        <v>5</v>
+      </c>
+      <c r="E214">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>855072</v>
+      </c>
+      <c r="B215" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>854500</v>
+      </c>
+      <c r="B216" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>854895</v>
+      </c>
+      <c r="B217" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>854917</v>
+      </c>
+      <c r="B218" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219">
         <v>854503</v>
       </c>
-      <c r="B208" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209">
+      <c r="B219" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>854506</v>
+      </c>
+      <c r="B220" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221">
         <v>854903</v>
       </c>
-      <c r="B209" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210">
+      <c r="B221" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222">
         <v>854494</v>
       </c>
-      <c r="B210" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211">
+      <c r="B222" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223">
         <v>854911</v>
       </c>
-      <c r="B211" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212">
+      <c r="B223" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224">
         <v>854499</v>
       </c>
-      <c r="B212" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213">
-        <v>854504</v>
-      </c>
-      <c r="B213" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214">
-        <v>854908</v>
-      </c>
-      <c r="B214" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215">
-        <v>854910</v>
-      </c>
-      <c r="B215" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216">
-        <v>854507</v>
-      </c>
-      <c r="B216" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217">
-        <v>854906</v>
-      </c>
-      <c r="B217" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218">
-        <v>854907</v>
-      </c>
-      <c r="B218" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219">
-        <v>850108</v>
-      </c>
-      <c r="B219" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220">
-        <v>850002</v>
-      </c>
-      <c r="B220" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221">
-        <v>855820</v>
-      </c>
-      <c r="B221" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222">
-        <v>855830</v>
-      </c>
-      <c r="B222" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223">
-        <v>848673</v>
-      </c>
-      <c r="B223" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224">
-        <v>855246</v>
-      </c>
       <c r="B224" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>855662</v>
+        <v>854504</v>
       </c>
       <c r="B225" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>849969</v>
+        <v>854908</v>
       </c>
       <c r="B226" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>849444</v>
+        <v>854910</v>
       </c>
       <c r="B227" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>855178</v>
+        <v>854496</v>
       </c>
       <c r="B228" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>855180</v>
+        <v>854507</v>
       </c>
       <c r="B229" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>855181</v>
+        <v>854900</v>
       </c>
       <c r="B230" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>855182</v>
+        <v>854906</v>
       </c>
       <c r="B231" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>855185</v>
+        <v>854907</v>
       </c>
       <c r="B232" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>855189</v>
+        <v>855903</v>
       </c>
       <c r="B233" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>855191</v>
+        <v>850108</v>
       </c>
       <c r="B234" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>855192</v>
+        <v>850002</v>
       </c>
       <c r="B235" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>855193</v>
+        <v>851031</v>
       </c>
       <c r="B236" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>855194</v>
+        <v>843776</v>
       </c>
       <c r="B237" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>855195</v>
+        <v>843780</v>
       </c>
       <c r="B238" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>855196</v>
+        <v>843785</v>
       </c>
       <c r="B239" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>855197</v>
+        <v>844518</v>
       </c>
       <c r="B240" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>855198</v>
+        <v>844527</v>
       </c>
       <c r="B241" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>855199</v>
+        <v>846411</v>
       </c>
       <c r="B242" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>855200</v>
+        <v>846414</v>
       </c>
       <c r="B243" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>855201</v>
+        <v>847008</v>
       </c>
       <c r="B244" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>855202</v>
+        <v>851106</v>
       </c>
       <c r="B245" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>855204</v>
+        <v>851109</v>
       </c>
       <c r="B246" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>855205</v>
+        <v>851875</v>
       </c>
       <c r="B247" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>855206</v>
+        <v>851876</v>
       </c>
       <c r="B248" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>855207</v>
+        <v>851881</v>
       </c>
       <c r="B249" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>855208</v>
+        <v>852454</v>
       </c>
       <c r="B250" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>855209</v>
+        <v>846997</v>
       </c>
       <c r="B251" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>854887</v>
+        <v>847009</v>
       </c>
       <c r="B252" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>854890</v>
+        <v>848642</v>
       </c>
       <c r="B253" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>854493</v>
+        <v>851100</v>
       </c>
       <c r="B254" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>854498</v>
+        <v>851115</v>
       </c>
       <c r="B255" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>854896</v>
+        <v>852345</v>
       </c>
       <c r="B256" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>854894</v>
+        <v>852346</v>
       </c>
       <c r="B257" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>851751</v>
+        <v>852352</v>
       </c>
       <c r="B258" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>849662</v>
+        <v>852452</v>
       </c>
       <c r="B259" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>853691</v>
+        <v>854898</v>
       </c>
       <c r="B260" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>849622</v>
+        <v>855882</v>
       </c>
       <c r="B261" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>849563</v>
+        <v>855880</v>
       </c>
       <c r="B262" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>855289</v>
+        <v>855877</v>
       </c>
       <c r="B263" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>854257</v>
+        <v>855831</v>
       </c>
       <c r="B264" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>854288</v>
+        <v>855874</v>
       </c>
       <c r="B265" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>854260</v>
+        <v>855871</v>
       </c>
       <c r="B266" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>854255</v>
+        <v>855868</v>
       </c>
       <c r="B267" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>854272</v>
+        <v>855865</v>
       </c>
       <c r="B268" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>849613</v>
+        <v>855861</v>
       </c>
       <c r="B269" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>854308</v>
+        <v>855827</v>
       </c>
       <c r="B270" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>854301</v>
+        <v>855824</v>
       </c>
       <c r="B271" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>854306</v>
+        <v>855820</v>
       </c>
       <c r="B272" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>854311</v>
+        <v>855857</v>
       </c>
       <c r="B273" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>854312</v>
+        <v>855855</v>
       </c>
       <c r="B274" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>854310</v>
+        <v>855891</v>
       </c>
       <c r="B275" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>849183</v>
+        <v>855885</v>
       </c>
       <c r="B276" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>849750</v>
+        <v>855835</v>
       </c>
       <c r="B277" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>849603</v>
+        <v>855888</v>
       </c>
       <c r="B278" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>852382</v>
+        <v>855853</v>
       </c>
       <c r="B279" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>849376</v>
+        <v>855838</v>
       </c>
       <c r="B280" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>849832</v>
+        <v>855785</v>
       </c>
       <c r="B281" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>849559</v>
+        <v>855830</v>
       </c>
       <c r="B282" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>849847</v>
+        <v>855957</v>
       </c>
       <c r="B283" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>853295</v>
+        <v>855983</v>
       </c>
       <c r="B284" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>849636</v>
+        <v>855972</v>
       </c>
       <c r="B285" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>849652</v>
+        <v>848673</v>
       </c>
       <c r="B286" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>849913</v>
+        <v>855246</v>
       </c>
       <c r="B287" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>855273</v>
+        <v>855662</v>
       </c>
       <c r="B288" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>855644</v>
+        <v>849969</v>
       </c>
       <c r="B289" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>855654</v>
+        <v>849444</v>
       </c>
       <c r="B290" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>849940</v>
+        <v>855178</v>
       </c>
       <c r="B291" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>849567</v>
+        <v>855180</v>
       </c>
       <c r="B292" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>849780</v>
+        <v>855181</v>
       </c>
       <c r="B293" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>849773</v>
+        <v>855182</v>
       </c>
       <c r="B294" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>849792</v>
+        <v>855185</v>
       </c>
       <c r="B295" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>849812</v>
+        <v>855189</v>
       </c>
       <c r="B296" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>849639</v>
+        <v>855191</v>
       </c>
       <c r="B297" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>853427</v>
+        <v>855192</v>
       </c>
       <c r="B298" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>853538</v>
+        <v>855193</v>
       </c>
       <c r="B299" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>849821</v>
+        <v>855194</v>
       </c>
       <c r="B300" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>848706</v>
+        <v>855195</v>
       </c>
       <c r="B301" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>849882</v>
+        <v>855196</v>
       </c>
       <c r="B302" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>852307</v>
+        <v>855197</v>
       </c>
       <c r="B303" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>854060</v>
+        <v>855198</v>
       </c>
       <c r="B304" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>855485</v>
+        <v>855199</v>
       </c>
       <c r="B305" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>853428</v>
+        <v>855200</v>
       </c>
       <c r="B306" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>853773</v>
+        <v>855201</v>
       </c>
       <c r="B307" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>855806</v>
+        <v>855202</v>
       </c>
       <c r="B308" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>855735</v>
+        <v>855204</v>
       </c>
       <c r="B309" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>855774</v>
+        <v>855205</v>
       </c>
       <c r="B310" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>855538</v>
+        <v>855206</v>
       </c>
       <c r="B311" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>855901</v>
+        <v>855207</v>
       </c>
       <c r="B312" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>855895</v>
+        <v>855208</v>
       </c>
       <c r="B313" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>855461</v>
+        <v>855209</v>
       </c>
       <c r="B314" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>855574</v>
+        <v>854887</v>
       </c>
       <c r="B315" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>855579</v>
+        <v>854890</v>
       </c>
       <c r="B316" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>855640</v>
+        <v>854493</v>
       </c>
       <c r="B317" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>855642</v>
+        <v>854498</v>
       </c>
       <c r="B318" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>855809</v>
+        <v>854896</v>
       </c>
       <c r="B319" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>855257</v>
+        <v>854894</v>
       </c>
       <c r="B320" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>855802</v>
+        <v>851751</v>
       </c>
       <c r="B321" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>855822</v>
+        <v>849662</v>
       </c>
       <c r="B322" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>855703</v>
+        <v>853691</v>
       </c>
       <c r="B323" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>855518</v>
+        <v>849622</v>
       </c>
       <c r="B324" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>855524</v>
+        <v>849563</v>
       </c>
       <c r="B325" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>855843</v>
+        <v>855289</v>
       </c>
       <c r="B326" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>855811</v>
+        <v>854288</v>
       </c>
       <c r="B327" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>855893</v>
+        <v>854260</v>
       </c>
       <c r="B328" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>855819</v>
+        <v>854255</v>
       </c>
       <c r="B329" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>855517</v>
+        <v>854272</v>
       </c>
       <c r="B330" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331">
+        <v>849613</v>
+      </c>
+      <c r="B331" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>854308</v>
+      </c>
+      <c r="B332" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>854301</v>
+      </c>
+      <c r="B333" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>854306</v>
+      </c>
+      <c r="B334" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>854311</v>
+      </c>
+      <c r="B335" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>854312</v>
+      </c>
+      <c r="B336" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>854310</v>
+      </c>
+      <c r="B337" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>849183</v>
+      </c>
+      <c r="B338" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>849750</v>
+      </c>
+      <c r="B339" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>849603</v>
+      </c>
+      <c r="B340" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>852382</v>
+      </c>
+      <c r="B341" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>849376</v>
+      </c>
+      <c r="B342" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>849832</v>
+      </c>
+      <c r="B343" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>849559</v>
+      </c>
+      <c r="B344" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>849847</v>
+      </c>
+      <c r="B345" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>853295</v>
+      </c>
+      <c r="B346" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>849636</v>
+      </c>
+      <c r="B347" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>849652</v>
+      </c>
+      <c r="B348" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>849913</v>
+      </c>
+      <c r="B349" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>855554</v>
+      </c>
+      <c r="B350" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>855654</v>
+      </c>
+      <c r="B351" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>849940</v>
+      </c>
+      <c r="B352" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>849567</v>
+      </c>
+      <c r="B353" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>849780</v>
+      </c>
+      <c r="B354" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>849773</v>
+      </c>
+      <c r="B355" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>855650</v>
+      </c>
+      <c r="B356" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>849792</v>
+      </c>
+      <c r="B357" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>849812</v>
+      </c>
+      <c r="B358" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>849639</v>
+      </c>
+      <c r="B359" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>853427</v>
+      </c>
+      <c r="B360" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>853538</v>
+      </c>
+      <c r="B361" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>849821</v>
+      </c>
+      <c r="B362" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>848706</v>
+      </c>
+      <c r="B363" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>849882</v>
+      </c>
+      <c r="B364" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>852307</v>
+      </c>
+      <c r="B365" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>854060</v>
+      </c>
+      <c r="B366" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>853428</v>
+      </c>
+      <c r="B367" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>855963</v>
+      </c>
+      <c r="B368" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>853773</v>
+      </c>
+      <c r="B369" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>855806</v>
+      </c>
+      <c r="B370" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>855735</v>
+      </c>
+      <c r="B371" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>855774</v>
+      </c>
+      <c r="B372" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>855730</v>
+      </c>
+      <c r="B373" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>856039</v>
+      </c>
+      <c r="B374" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>855538</v>
+      </c>
+      <c r="B375" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>855901</v>
+      </c>
+      <c r="B376" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>855895</v>
+      </c>
+      <c r="B377" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>855461</v>
+      </c>
+      <c r="B378" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>855574</v>
+      </c>
+      <c r="B379" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>855579</v>
+      </c>
+      <c r="B380" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>855640</v>
+      </c>
+      <c r="B381" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>855642</v>
+      </c>
+      <c r="B382" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>855975</v>
+      </c>
+      <c r="B383" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>855809</v>
+      </c>
+      <c r="B384" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>855257</v>
+      </c>
+      <c r="B385" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>855436</v>
+      </c>
+      <c r="B386" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>855802</v>
+      </c>
+      <c r="B387" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>855822</v>
+      </c>
+      <c r="B388" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>855940</v>
+      </c>
+      <c r="B389" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>855920</v>
+      </c>
+      <c r="B390" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>855953</v>
+      </c>
+      <c r="B391" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>855703</v>
+      </c>
+      <c r="B392" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>856037</v>
+      </c>
+      <c r="B393" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>855518</v>
+      </c>
+      <c r="B394" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>855843</v>
+      </c>
+      <c r="B395" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>855811</v>
+      </c>
+      <c r="B396" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>855893</v>
+      </c>
+      <c r="B397" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>856031</v>
+      </c>
+      <c r="B398" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>855933</v>
+      </c>
+      <c r="B399" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>855991</v>
+      </c>
+      <c r="B400" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>855918</v>
+      </c>
+      <c r="B401" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>855819</v>
+      </c>
+      <c r="B402" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>855984</v>
+      </c>
+      <c r="B403" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>855517</v>
+      </c>
+      <c r="B404" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405">
         <v>855708</v>
       </c>
-      <c r="B331" t="s">
-        <v>106</v>
+      <c r="B405" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>855755</v>
+      </c>
+      <c r="B406" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>855952</v>
+      </c>
+      <c r="B407" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>855954</v>
+      </c>
+      <c r="B408" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>855724</v>
+      </c>
+      <c r="B409" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E52829F-B9C6-4A10-A782-D5164B8CC837}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2616BCC9-C7E6-4D09-BA1F-780824741963}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="180">
   <si>
     <t>Pedido</t>
   </si>
@@ -60,46 +60,6 @@
   </si>
   <si>
     <t>Novo Pedido</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 199,68_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 595,04_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 399,37_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.316,82_x000D_
-• Valor em ruptura: R$ 396,68_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.583,84_x000D_
-• Valor em ruptura: R$ 136,32_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -153,33 +113,9 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 447,52_x000D_
-• Valor em ruptura: R$ 137,40_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 188,17_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 237,46_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 60,61_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -238,14 +174,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -396,14 +324,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 23.378,18_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.188,31_x000D_
-• Valor em ruptura: R$ 182,50_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -454,46 +374,6 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.093,04_x000D_
-• Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.430,80_x000D_
-• Valor em ruptura: R$ 844,38_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.493,26_x000D_
-• Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.640,74_x000D_
-• Valor em ruptura: R$ 861,26_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.293,41_x000D_
-• Valor em ruptura: R$ 275,83_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -529,27 +409,11 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.599,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.057,80_x000D_
 • Valor em ruptura: R$ 4.102,09_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.920,53_x000D_
-• Valor em ruptura: R$ 1.125,83_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -566,62 +430,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 19.209,59_x000D_
-• Valor em ruptura: R$ 2.815,84_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 599,47_x000D_
-• Valor em ruptura: R$ 2.531,75_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.270,47_x000D_
-• Valor em ruptura: R$ 598,55_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.867,55_x000D_
-• Valor em ruptura: R$ 1.688,75_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 16.421,62_x000D_
-• Valor em ruptura: R$ 760,31_x000D_
-• Valor mínimo de frete: R$ 50,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 32.671,96_x000D_
-• Valor em ruptura: R$ 48.601,27_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.256,53_x000D_
-• Valor em ruptura: R$ 293,29_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -630,30 +438,6 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.438,97_x000D_
-• Valor em ruptura: R$ 296,94_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.151,19_x000D_
-• Valor em ruptura: R$ 836,96_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.698,31_x000D_
-• Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -675,14 +459,6 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 4.793,84_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 71.847,56_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -705,14 +481,6 @@
     <t>O valor do pedido encontra-se abaixo do mínimo estabelecido para a região, ficamos no aguarde de pedido complementar ou cancelamento do mesmo.</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.857,89_x000D_
-• Valor em ruptura: R$ 316,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -729,67 +497,11 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 1.115,94_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.275,34_x000D_
-• Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.783,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.409,86_x000D_
-• Valor em ruptura: R$ 2.231,89_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.614,85_x000D_
-• Valor em ruptura: R$ 2.111,07_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.774,36_x000D_
-• Valor em ruptura: R$ 281,58_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.990,28_x000D_
-• Valor em ruptura: R$ 583,65_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.307,31_x000D_
-• Valor em ruptura: R$ 168,42_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -812,32 +524,8 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.292,33_x000D_
-• Valor em ruptura: R$ 557,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.519,73_x000D_
-• Valor em ruptura: R$ 2.053,80_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.731,80_x000D_
 • Valor em ruptura: R$ 424,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 10.775,54_x000D_
-• Valor em ruptura: R$ 1.394,93_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -860,131 +548,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.676,55_x000D_
-• Valor em ruptura: R$ 5.177,12_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 10.020,81_x000D_
-• Valor em ruptura: R$ 552,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.498,27_x000D_
-• Valor em ruptura: R$ 836,96_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.048,73_x000D_
-• Valor em ruptura: R$ 3.266,47_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.199,01_x000D_
-• Valor em ruptura: R$ 278,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.427,02_x000D_
-• Valor em ruptura: R$ 588,41_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 984,68_x000D_
-• Valor em ruptura: R$ 6.924,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.079,08_x000D_
-• Valor em ruptura: R$ 12.053,17_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.471,65_x000D_
-• Valor em ruptura: R$ 1.071,25_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.032,71_x000D_
-• Valor em ruptura: R$ 7.269,85_x000D_
-• Valor mínimo de frete: R$ 50,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.218,80_x000D_
-• Valor em ruptura: R$ 1.081,21_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 19.672,77_x000D_
-• Valor em ruptura: R$ 5.811,10_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.370,95_x000D_
 • Valor em ruptura: R$ 2.917,89_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.614,17_x000D_
-• Valor em ruptura: R$ 3.782,93_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.175,61_x000D_
-• Valor em ruptura: R$ 1.325,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 10.465,95_x000D_
-• Valor em ruptura: R$ 778,37_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -996,14 +564,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 16.692,98_x000D_
-• Valor em ruptura: R$ 1.187,24_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.898,78_x000D_
 • Valor em ruptura: R$ 169,82_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -1017,35 +577,11 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.270,58_x000D_
-• Valor em ruptura: R$ 588,41_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.572,85_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 248,52_x000D_
 • Valor em ruptura: R$ 518,52_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 999,64_x000D_
-• Valor em ruptura: R$ 2.063,17_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1060,22 +596,6 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 485,21_x000D_
-• Valor em ruptura: R$ 5.296,31_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.070,36_x000D_
-• Valor em ruptura: R$ 2.311,78_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 965,31_x000D_
 • Valor em ruptura: R$ 13.017,23_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1087,46 +607,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 0,00_x000D_
 • Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.432,60_x000D_
-• Valor em ruptura: R$ 557,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.042,03_x000D_
-• Valor em ruptura: R$ 863,98_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.964,61_x000D_
-• Valor em ruptura: R$ 2.460,65_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.836,34_x000D_
-• Valor em ruptura: R$ 294,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 525,68_x000D_
-• Valor em ruptura: R$ 289,13_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
@@ -1153,44 +633,12 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.381,30_x000D_
-• Valor em ruptura: R$ 3.936,50_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 55.154,85_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.167,67_x000D_
-• Valor em ruptura: R$ 2.017,56_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.788,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 887,67_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -1332,99 +780,11 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.306,64_x000D_
-• Valor em ruptura: R$ 2.795,44_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.246,17_x000D_
-• Valor em ruptura: R$ 186,57_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 19.132,66_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.717,46_x000D_
-• Valor em ruptura: R$ 1.295,81_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.144,93_x000D_
 • Valor em ruptura: R$ 169,95_x000D_
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 9.311,94_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.176,51_x000D_
-• Valor em ruptura: R$ 1.394,93_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.944,27_x000D_
-• Valor em ruptura: R$ 276,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.465,21_x000D_
-• Valor em ruptura: R$ 294,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 11.563,71_x000D_
-• Valor em ruptura: R$ 281,46_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.223,85_x000D_
-• Valor em ruptura: R$ 1.012,70_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.927,11_x000D_
-• Valor em ruptura: R$ 4.164,43_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1449,14 +809,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.243,95_x000D_
-• Valor em ruptura: R$ 584,69_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1489,59 +841,11 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 23.312,97_x000D_
-• Valor em ruptura: R$ 1.125,83_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 8.548,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.783,52_x000D_
-• Valor em ruptura: R$ 1.533,32_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.972,20_x000D_
-• Valor em ruptura: R$ 289,11_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.712,70_x000D_
-• Valor em ruptura: R$ 308,29_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.663,09_x000D_
-• Valor em ruptura: R$ 4.712,07_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.497,17_x000D_
-• Valor em ruptura: R$ 4.269,02_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1577,54 +881,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.246,79_x000D_
-• Valor em ruptura: R$ 557,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.888,43_x000D_
-• Valor em ruptura: R$ 288,32_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.631,59_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.143,86_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 10.733,18_x000D_
-• Valor em ruptura: R$ 3.587,88_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.934,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1670,6 +926,526 @@
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.660,61_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.636,27_x000D_
+• Valor em ruptura: R$ 77,23_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 35.375,82_x000D_
+• Valor em ruptura: R$ 1.262,38_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 182,61_x000D_
+• Valor em ruptura: R$ 412,43_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.030,65_x000D_
+• Valor em ruptura: R$ 2.508,62_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.366,25_x000D_
+• Valor em ruptura: R$ 3.661,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.621,13_x000D_
+• Valor em ruptura: R$ 3.858,71_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.604,14_x000D_
+• Valor em ruptura: R$ 2.342,25_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.270,45_x000D_
+• Valor em ruptura: R$ 1.292,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.696,17_x000D_
+• Valor em ruptura: R$ 1.507,54_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.109,98_x000D_
+• Valor em ruptura: R$ 3.419,07_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.766,94_x000D_
+• Valor em ruptura: R$ 3.221,54_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.274,73_x000D_
+• Valor em ruptura: R$ 3.015,09_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.467,62_x000D_
+• Valor em ruptura: R$ 9.906,72_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.416,18_x000D_
+• Valor em ruptura: R$ 6.891,63_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.380,71_x000D_
+• Valor em ruptura: R$ 2.584,36_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.418,80_x000D_
+• Valor em ruptura: R$ 2.790,81_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.839,07_x000D_
+• Valor em ruptura: R$ 646,09_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.733,17_x000D_
+• Valor em ruptura: R$ 1.067,90_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.843,65_x000D_
+• Valor em ruptura: R$ 3.634,43_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.858,84_x000D_
+• Valor em ruptura: R$ 2.781,89_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.307,31_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.009,81_x000D_
+• Valor em ruptura: R$ 1.003,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.801,31_x000D_
+• Valor em ruptura: R$ 1.772,22_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.449,78_x000D_
+• Valor em ruptura: R$ 3.512,13_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.374,84_x000D_
+• Valor em ruptura: R$ 93,29_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.053,44_x000D_
+• Valor em ruptura: R$ 3.038,10_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.506,75_x000D_
+• Valor em ruptura: R$ 2.025,40_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.126,21_x000D_
+• Valor em ruptura: R$ 1.866,55_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.459,00_x000D_
+• Valor em ruptura: R$ 4.449,86_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.629,78_x000D_
+• Valor em ruptura: R$ 1.003,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.350,96_x000D_
+• Valor em ruptura: R$ 2.358,14_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.543,42_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.895,63_x000D_
+• Valor em ruptura: R$ 3.501,47_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.207,83_x000D_
+• Valor em ruptura: R$ 210,18_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.422,60_x000D_
+• Valor em ruptura: R$ 2.341,97_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.138,93_x000D_
+• Valor em ruptura: R$ 2.425,60_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 281,58_x000D_
+• Valor em ruptura: R$ 3.291,27_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.729,66_x000D_
+• Valor em ruptura: R$ 2.645,50_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 320,56_x000D_
+• Valor em ruptura: R$ 4.666,38_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 638,33_x000D_
+• Valor em ruptura: R$ 1.851,85_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.072,56_x000D_
+• Valor em ruptura: R$ 477,26_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.257,53_x000D_
+• Valor em ruptura: R$ 2.508,66_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.735,86_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.719,36_x000D_
+• Valor em ruptura: R$ 1.202,39_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.808,20_x000D_
+• Valor em ruptura: R$ 1.098,35_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.455,54_x000D_
+• Valor em ruptura: R$ 1.012,70_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.664,11_x000D_
+• Valor em ruptura: R$ 2.341,28_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 764,20_x000D_
+• Valor em ruptura: R$ 5.017,32_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.089,17_x000D_
+• Valor em ruptura: R$ 2.803,22_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.696,13_x000D_
+• Valor em ruptura: R$ 138,57_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.555,81_x000D_
+• Valor em ruptura: R$ 924,46_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 26.407,88_x000D_
+• Valor em ruptura: R$ 1.806,24_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 562,92_x000D_
+• Valor em ruptura: R$ 3.068,67_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.105,02_x000D_
+• Valor em ruptura: R$ 441,48_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.844,69_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 14.541,42_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 19.666,50_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.129,54_x000D_
+• Valor em ruptura: R$ 16.745,29_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 1.674,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.253,09_x000D_
+• Valor em ruptura: R$ 3.064,71_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 12.175,94_x000D_
+• Valor em ruptura: R$ 979,22_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.599,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.713,45_x000D_
+• Valor em ruptura: R$ 1.127,23_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 33.726,72_x000D_
+• Valor em ruptura: R$ 38.120,84_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
 </sst>
@@ -1715,7 +1491,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2046,7 +1833,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E409"/>
+  <dimension ref="A1:E414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -2074,7 +1861,7 @@
     </row>
     <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>853850</v>
+        <v>854781</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -2083,12 +1870,12 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>773</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>853854</v>
+        <v>848783</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -2097,12 +1884,12 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>773</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>853853</v>
+        <v>853426</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -2111,7 +1898,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>773</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
@@ -2119,7 +1906,7 @@
         <v>850631</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -2130,49 +1917,49 @@
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>855347</v>
+        <v>854985</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>134</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>855752</v>
+        <v>849811</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>593</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>853567</v>
+        <v>855293</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>3060</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>854781</v>
+        <v>849918</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
@@ -2181,505 +1968,505 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>3093</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>848783</v>
+        <v>856191</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>3075</v>
+        <v>922</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>853426</v>
+        <v>852593</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>3075</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>854985</v>
+        <v>853998</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>2090</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>849811</v>
+        <v>853854</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>3058</v>
+        <v>773</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>855293</v>
+        <v>853852</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>2072</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>849918</v>
+        <v>856033</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>750</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>849917</v>
+        <v>854933</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>3089</v>
+        <v>983</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>850200</v>
+        <v>854931</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>1021</v>
+        <v>983</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>852593</v>
+        <v>854585</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>632</v>
+        <v>933</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>852631</v>
+        <v>855295</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>3085</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>853998</v>
+        <v>854330</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>722</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>853852</v>
+        <v>855330</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>773</v>
+        <v>703</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>856033</v>
+        <v>855731</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>373</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>854933</v>
+        <v>856303</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>854931</v>
+        <v>854385</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>983</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>854585</v>
+        <v>855232</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>933</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>855295</v>
+        <v>855480</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>377</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>854330</v>
+        <v>855445</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>855330</v>
+        <v>854374</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>855731</v>
+        <v>856089</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>1021</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>854385</v>
+        <v>856122</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>2090</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>855232</v>
+        <v>856130</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>2084</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>855480</v>
+        <v>856103</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>3037</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>855445</v>
+        <v>856148</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>854374</v>
+        <v>856172</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>854940</v>
+        <v>856150</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35">
         <v>90</v>
-      </c>
-      <c r="D35" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35">
-        <v>703</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>855501</v>
+        <v>856157</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>855764</v>
+        <v>856161</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>855761</v>
+        <v>856168</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>855759</v>
+        <v>856182</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>855758</v>
+        <v>856192</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>855756</v>
+        <v>856291</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>855753</v>
+        <v>856215</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>855749</v>
+        <v>856282</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>855748</v>
+        <v>856221</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>855683</v>
+        <v>855764</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -2690,10 +2477,10 @@
     </row>
     <row r="46" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>855746</v>
+        <v>855761</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -2704,128 +2491,128 @@
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>856005</v>
+        <v>855759</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>773</v>
+        <v>642</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>855686</v>
+        <v>855758</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>856027</v>
+        <v>855756</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>855376</v>
+        <v>855753</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50">
-        <v>1021</v>
+        <v>642</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>855350</v>
+        <v>855749</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>854934</v>
+        <v>855748</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>855823</v>
+        <v>855746</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>614</v>
+        <v>642</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>855783</v>
+        <v>856005</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>748</v>
+        <v>773</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>855357</v>
+        <v>855783</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>699</v>
+        <v>748</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
@@ -2833,7 +2620,7 @@
         <v>855666</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
@@ -2847,7 +2634,7 @@
         <v>855872</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
@@ -2861,7 +2648,7 @@
         <v>856043</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -2872,52 +2659,52 @@
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>855484</v>
+        <v>855896</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>699</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>855896</v>
+        <v>855834</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
-        <v>2084</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>855834</v>
+        <v>855512</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>855359</v>
+        <v>856208</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
@@ -2926,250 +2713,250 @@
         <v>699</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>855512</v>
+        <v>855742</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
-        <v>3057</v>
+        <v>614</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>855659</v>
+        <v>855690</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64">
-        <v>669</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>855069</v>
+        <v>856194</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65">
-        <v>380</v>
+        <v>614</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>854773</v>
+        <v>856008</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>855596</v>
+        <v>855934</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>855742</v>
+        <v>856026</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>855690</v>
+        <v>855931</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>388</v>
+        <v>699</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>855553</v>
+        <v>856124</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>951</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>855949</v>
+        <v>856227</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>855033</v>
+        <v>853459</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>855766</v>
+        <v>850430</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>856008</v>
+        <v>855797</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>855934</v>
+        <v>856304</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>614</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>856026</v>
+        <v>856055</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>856000</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+      <c r="E77">
         <v>699</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>855737</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D77" t="s">
-        <v>5</v>
-      </c>
-      <c r="E77">
-        <v>614</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>855242</v>
+        <v>855997</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>380</v>
+        <v>699</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>855338</v>
+        <v>855999</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>614</v>
+        <v>699</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>855931</v>
+        <v>855996</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
@@ -3180,262 +2967,262 @@
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>855077</v>
+        <v>855998</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>380</v>
+        <v>699</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>855466</v>
+        <v>855994</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>855421</v>
+        <v>855995</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>2088</v>
+        <v>699</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>855635</v>
+        <v>855650</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>853459</v>
+        <v>855648</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>850430</v>
+        <v>855651</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>2081</v>
+        <v>916</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>855274</v>
+        <v>856289</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>856051</v>
+        <v>856034</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>855797</v>
+        <v>854263</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>90</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>855687</v>
+        <v>856283</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>699</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>855812</v>
+        <v>855699</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>2032</v>
+        <v>429</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>855616</v>
+        <v>856305</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>614</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>855549</v>
+        <v>855426</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>700</v>
+        <v>429</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>855580</v>
+        <v>855506</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>2027</v>
+        <v>569</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>855718</v>
+        <v>856068</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>856000</v>
+        <v>855790</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>699</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>855997</v>
+        <v>855794</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>699</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>855999</v>
+        <v>855890</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>855996</v>
+        <v>856189</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>183</v>
+        <v>9</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
@@ -3446,903 +3233,903 @@
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>855998</v>
+        <v>856003</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>699</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>855994</v>
+        <v>856306</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>182</v>
+        <v>9</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>699</v>
+        <v>653</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>855995</v>
+        <v>856181</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>699</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>855514</v>
+        <v>856287</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>951</v>
+        <v>699</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>855440</v>
+        <v>855498</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>922</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>855649</v>
+        <v>855985</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>916</v>
+        <v>699</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>855648</v>
+        <v>856011</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>855651</v>
+        <v>856203</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>916</v>
+        <v>967</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>854932</v>
+        <v>856056</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>699</v>
+        <v>669</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>855062</v>
+        <v>855496</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>3072</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>856034</v>
+        <v>856190</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>642</v>
+        <v>818</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>854263</v>
+        <v>856179</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>574</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>855384</v>
+        <v>855717</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>855787</v>
+        <v>856177</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>90</v>
+        <v>294</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>855699</v>
+        <v>856313</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>429</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>855560</v>
+        <v>853358</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>855876</v>
+        <v>855468</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>854319</v>
+        <v>856024</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>574</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>855426</v>
+        <v>855929</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>429</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>855506</v>
+        <v>856311</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>855051</v>
+        <v>855660</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>3078</v>
+        <v>703</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>855790</v>
+        <v>856206</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>2097</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>855794</v>
+        <v>856199</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>2097</v>
+        <v>589</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>855697</v>
+        <v>855001</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>189</v>
+        <v>9</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>855890</v>
+        <v>855887</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>856003</v>
+        <v>856128</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>190</v>
+        <v>9</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>90</v>
+        <v>625</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855498</v>
+        <v>855692</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>3097</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>855985</v>
+        <v>856300</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>699</v>
+        <v>773</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>856011</v>
+        <v>856023</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>192</v>
+        <v>15</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>2055</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>855136</v>
+        <v>856210</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>3037</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>855496</v>
+        <v>855914</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>811</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>855566</v>
+        <v>856209</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>855717</v>
+        <v>856198</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>853358</v>
+        <v>856090</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>855796</v>
+        <v>851354</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>855468</v>
+        <v>851357</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>294</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>856024</v>
+        <v>854953</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>3035</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>855929</v>
+        <v>854954</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>3034</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>855229</v>
+        <v>851359</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>3049</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>855660</v>
+        <v>854955</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>855352</v>
+        <v>854956</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>3060</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>855001</v>
+        <v>844931</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>854984</v>
+        <v>851348</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>855887</v>
+        <v>851349</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>855091</v>
+        <v>854602</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>855563</v>
+        <v>855576</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>855692</v>
+        <v>855261</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>856023</v>
+        <v>855254</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>3034</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>855237</v>
+        <v>855272</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>855248</v>
+        <v>855271</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>3060</v>
+        <v>906</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>855978</v>
+        <v>855438</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>855678</v>
+        <v>853930</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>855258</v>
+        <v>855494</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>855079</v>
+        <v>854939</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>855914</v>
+        <v>856162</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>3045</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>855816</v>
+        <v>855297</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>199</v>
+        <v>46</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>3</v>
+        <v>381</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>851354</v>
+        <v>854777</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>851356</v>
+        <v>856123</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>60</v>
+        <v>996</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>851357</v>
+        <v>856010</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>60</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>854953</v>
+        <v>856018</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>854954</v>
+        <v>855703</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>60</v>
+        <v>694</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>851359</v>
+        <v>855278</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>854955</v>
+        <v>855935</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>60</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>854956</v>
+        <v>853734</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>844931</v>
+        <v>853738</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>36</v>
@@ -4351,211 +4138,211 @@
         <v>5</v>
       </c>
       <c r="E164">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>851348</v>
+        <v>852720</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>60</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>851349</v>
+        <v>855884</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>854602</v>
+        <v>855583</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>60</v>
+        <v>778</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>855576</v>
+        <v>855990</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>855261</v>
+        <v>855374</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>906</v>
+        <v>293</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>855254</v>
+        <v>855636</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>906</v>
+        <v>851</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>855272</v>
+        <v>855987</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>855271</v>
+        <v>856174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>855438</v>
+        <v>856021</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>853930</v>
+        <v>854925</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>855494</v>
+        <v>856187</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>42</v>
+        <v>177</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>854939</v>
+        <v>856213</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>43</v>
+        <v>178</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>855492</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D177" t="s">
+        <v>5</v>
+      </c>
+      <c r="E177">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>855382</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D178" t="s">
+        <v>5</v>
+      </c>
+      <c r="E178">
         <v>1807</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>855297</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D177" t="s">
-        <v>5</v>
-      </c>
-      <c r="E177">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A178">
-        <v>855345</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D178" t="s">
-        <v>5</v>
-      </c>
-      <c r="E178">
-        <v>979</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>855671</v>
+        <v>855578</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
@@ -4566,2056 +4353,1955 @@
     </row>
     <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>854777</v>
+        <v>848786</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>3</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>856010</v>
+        <v>855815</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181">
-        <v>3081</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>856018</v>
+        <v>854839</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>855278</v>
+        <v>856299</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>855935</v>
+        <v>856301</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>204</v>
+        <v>57</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
       <c r="E184">
-        <v>2047</v>
+        <v>60</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>855781</v>
+        <v>855782</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185">
-        <v>694</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>853734</v>
+        <v>854835</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186">
-        <v>1019</v>
+        <v>851</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>853738</v>
+        <v>855906</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>852720</v>
+        <v>855310</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>855884</v>
+        <v>855847</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>856059</v>
+        <v>852886</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>855583</v>
+        <v>855350</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D191" t="s">
-        <v>5</v>
-      </c>
-      <c r="E191">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>855990</v>
+        <v>855072</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D192" t="s">
-        <v>5</v>
-      </c>
-      <c r="E192">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>855374</v>
+        <v>854500</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D193" t="s">
-        <v>5</v>
-      </c>
-      <c r="E193">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>855636</v>
+        <v>854895</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D194" t="s">
-        <v>5</v>
-      </c>
-      <c r="E194">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>855987</v>
+        <v>854917</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D195" t="s">
-        <v>5</v>
-      </c>
-      <c r="E195">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>856021</v>
+        <v>854503</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D196" t="s">
-        <v>5</v>
-      </c>
-      <c r="E196">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>854925</v>
+        <v>854506</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D197" t="s">
-        <v>5</v>
-      </c>
-      <c r="E197">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>855610</v>
+        <v>854903</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D198" t="s">
-        <v>5</v>
-      </c>
-      <c r="E198">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>855765</v>
+        <v>854494</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D199" t="s">
-        <v>5</v>
-      </c>
-      <c r="E199">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>855492</v>
+        <v>854911</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D200" t="s">
-        <v>5</v>
-      </c>
-      <c r="E200">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>855858</v>
+        <v>854499</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D201" t="s">
-        <v>5</v>
-      </c>
-      <c r="E201">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>855382</v>
+        <v>854504</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D202" t="s">
-        <v>5</v>
-      </c>
-      <c r="E202">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>855578</v>
+        <v>854908</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D203" t="s">
-        <v>5</v>
-      </c>
-      <c r="E203">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>848786</v>
+        <v>854910</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D204" t="s">
-        <v>5</v>
-      </c>
-      <c r="E204">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>855355</v>
+        <v>854496</v>
       </c>
       <c r="B205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D205" t="s">
-        <v>5</v>
-      </c>
-      <c r="E205">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>855815</v>
+        <v>854507</v>
       </c>
       <c r="B206" t="s">
-        <v>148</v>
-      </c>
-      <c r="D206" t="s">
-        <v>5</v>
-      </c>
-      <c r="E206">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>856057</v>
+        <v>854900</v>
       </c>
       <c r="B207" t="s">
-        <v>14</v>
-      </c>
-      <c r="D207" t="s">
-        <v>5</v>
-      </c>
-      <c r="E207">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>854839</v>
+        <v>854906</v>
       </c>
       <c r="B208" t="s">
-        <v>84</v>
-      </c>
-      <c r="D208" t="s">
-        <v>5</v>
-      </c>
-      <c r="E208">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>855782</v>
+        <v>854907</v>
       </c>
       <c r="B209" t="s">
-        <v>85</v>
-      </c>
-      <c r="D209" t="s">
-        <v>5</v>
-      </c>
-      <c r="E209">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>854835</v>
+        <v>855903</v>
       </c>
       <c r="B210" t="s">
-        <v>149</v>
-      </c>
-      <c r="D210" t="s">
-        <v>5</v>
-      </c>
-      <c r="E210">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>855906</v>
+        <v>850108</v>
       </c>
       <c r="B211" t="s">
-        <v>150</v>
-      </c>
-      <c r="D211" t="s">
-        <v>5</v>
-      </c>
-      <c r="E211">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>855310</v>
+        <v>850002</v>
       </c>
       <c r="B212" t="s">
-        <v>65</v>
-      </c>
-      <c r="D212" t="s">
-        <v>5</v>
-      </c>
-      <c r="E212">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>855847</v>
+        <v>851031</v>
       </c>
       <c r="B213" t="s">
-        <v>151</v>
-      </c>
-      <c r="D213" t="s">
-        <v>5</v>
-      </c>
-      <c r="E213">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>852886</v>
+        <v>856131</v>
       </c>
       <c r="B214" t="s">
-        <v>47</v>
-      </c>
-      <c r="D214" t="s">
-        <v>5</v>
-      </c>
-      <c r="E214">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>855072</v>
+        <v>853850</v>
       </c>
       <c r="B215" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>854500</v>
+        <v>853853</v>
       </c>
       <c r="B216" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>854895</v>
+        <v>843776</v>
       </c>
       <c r="B217" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>854917</v>
+        <v>843780</v>
       </c>
       <c r="B218" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>854503</v>
+        <v>843785</v>
       </c>
       <c r="B219" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>854506</v>
+        <v>844518</v>
       </c>
       <c r="B220" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>854903</v>
+        <v>844527</v>
       </c>
       <c r="B221" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>854494</v>
+        <v>846411</v>
       </c>
       <c r="B222" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>854911</v>
+        <v>846414</v>
       </c>
       <c r="B223" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>854499</v>
+        <v>847008</v>
       </c>
       <c r="B224" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>854504</v>
+        <v>851106</v>
       </c>
       <c r="B225" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>854908</v>
+        <v>851109</v>
       </c>
       <c r="B226" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>854910</v>
+        <v>851875</v>
       </c>
       <c r="B227" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>854496</v>
+        <v>851876</v>
       </c>
       <c r="B228" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>854507</v>
+        <v>851881</v>
       </c>
       <c r="B229" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>854900</v>
+        <v>852454</v>
       </c>
       <c r="B230" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>854906</v>
+        <v>846997</v>
       </c>
       <c r="B231" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>854907</v>
+        <v>847009</v>
       </c>
       <c r="B232" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>855903</v>
+        <v>848642</v>
       </c>
       <c r="B233" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>850108</v>
+        <v>851100</v>
       </c>
       <c r="B234" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>850002</v>
+        <v>851115</v>
       </c>
       <c r="B235" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>851031</v>
+        <v>852345</v>
       </c>
       <c r="B236" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>843776</v>
+        <v>852346</v>
       </c>
       <c r="B237" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>843780</v>
+        <v>852352</v>
       </c>
       <c r="B238" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>843785</v>
+        <v>852452</v>
       </c>
       <c r="B239" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>844518</v>
+        <v>854898</v>
       </c>
       <c r="B240" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>844527</v>
+        <v>856246</v>
       </c>
       <c r="B241" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>846411</v>
+        <v>856274</v>
       </c>
       <c r="B242" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>846414</v>
+        <v>856279</v>
       </c>
       <c r="B243" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>847008</v>
+        <v>856230</v>
       </c>
       <c r="B244" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>851106</v>
+        <v>856242</v>
       </c>
       <c r="B245" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>851109</v>
+        <v>856273</v>
       </c>
       <c r="B246" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>851875</v>
+        <v>856256</v>
       </c>
       <c r="B247" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>851876</v>
+        <v>856234</v>
       </c>
       <c r="B248" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>851881</v>
+        <v>856253</v>
       </c>
       <c r="B249" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>852454</v>
+        <v>856229</v>
       </c>
       <c r="B250" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>846997</v>
+        <v>856243</v>
       </c>
       <c r="B251" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>847009</v>
+        <v>856275</v>
       </c>
       <c r="B252" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>848642</v>
+        <v>856252</v>
       </c>
       <c r="B253" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>851100</v>
+        <v>856272</v>
       </c>
       <c r="B254" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>851115</v>
+        <v>856268</v>
       </c>
       <c r="B255" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>852345</v>
+        <v>856265</v>
       </c>
       <c r="B256" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>852346</v>
+        <v>855882</v>
       </c>
       <c r="B257" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>852352</v>
+        <v>855880</v>
       </c>
       <c r="B258" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>852452</v>
+        <v>855877</v>
       </c>
       <c r="B259" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>854898</v>
+        <v>855831</v>
       </c>
       <c r="B260" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>855882</v>
+        <v>855874</v>
       </c>
       <c r="B261" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>855880</v>
+        <v>855871</v>
       </c>
       <c r="B262" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>855877</v>
+        <v>855868</v>
       </c>
       <c r="B263" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>855831</v>
+        <v>855865</v>
       </c>
       <c r="B264" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>855874</v>
+        <v>855861</v>
       </c>
       <c r="B265" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>855871</v>
+        <v>855827</v>
       </c>
       <c r="B266" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>855868</v>
+        <v>855824</v>
       </c>
       <c r="B267" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>855865</v>
+        <v>855857</v>
       </c>
       <c r="B268" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>855861</v>
+        <v>855855</v>
       </c>
       <c r="B269" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>855827</v>
+        <v>855891</v>
       </c>
       <c r="B270" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>855824</v>
+        <v>855885</v>
       </c>
       <c r="B271" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>855820</v>
+        <v>855835</v>
       </c>
       <c r="B272" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>855857</v>
+        <v>855888</v>
       </c>
       <c r="B273" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>855855</v>
+        <v>855853</v>
       </c>
       <c r="B274" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>855891</v>
+        <v>855838</v>
       </c>
       <c r="B275" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>855885</v>
+        <v>856110</v>
       </c>
       <c r="B276" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>855835</v>
+        <v>855785</v>
       </c>
       <c r="B277" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>855888</v>
+        <v>855972</v>
       </c>
       <c r="B278" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>855853</v>
+        <v>856163</v>
       </c>
       <c r="B279" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>855838</v>
+        <v>848673</v>
       </c>
       <c r="B280" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>855785</v>
+        <v>855246</v>
       </c>
       <c r="B281" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>855830</v>
+        <v>854940</v>
       </c>
       <c r="B282" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>855957</v>
+        <v>849969</v>
       </c>
       <c r="B283" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>855983</v>
+        <v>856277</v>
       </c>
       <c r="B284" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>855972</v>
+        <v>856278</v>
       </c>
       <c r="B285" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>848673</v>
+        <v>856276</v>
       </c>
       <c r="B286" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>855246</v>
+        <v>856257</v>
       </c>
       <c r="B287" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>855662</v>
+        <v>856238</v>
       </c>
       <c r="B288" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>849969</v>
+        <v>856232</v>
       </c>
       <c r="B289" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>849444</v>
+        <v>856241</v>
       </c>
       <c r="B290" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>855178</v>
+        <v>856258</v>
       </c>
       <c r="B291" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>855180</v>
+        <v>856255</v>
       </c>
       <c r="B292" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>855181</v>
+        <v>856233</v>
       </c>
       <c r="B293" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>855182</v>
+        <v>856263</v>
       </c>
       <c r="B294" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>855185</v>
+        <v>856237</v>
       </c>
       <c r="B295" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>855189</v>
+        <v>856240</v>
       </c>
       <c r="B296" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>855191</v>
+        <v>856259</v>
       </c>
       <c r="B297" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>855192</v>
+        <v>856270</v>
       </c>
       <c r="B298" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>855193</v>
+        <v>856235</v>
       </c>
       <c r="B299" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>855194</v>
+        <v>856269</v>
       </c>
       <c r="B300" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>855195</v>
+        <v>856271</v>
       </c>
       <c r="B301" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>855196</v>
+        <v>856266</v>
       </c>
       <c r="B302" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>855197</v>
+        <v>856236</v>
       </c>
       <c r="B303" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>855198</v>
+        <v>856267</v>
       </c>
       <c r="B304" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>855199</v>
+        <v>849444</v>
       </c>
       <c r="B305" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>855200</v>
+        <v>856295</v>
       </c>
       <c r="B306" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>855201</v>
+        <v>855178</v>
       </c>
       <c r="B307" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>855202</v>
+        <v>855180</v>
       </c>
       <c r="B308" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>855204</v>
+        <v>855181</v>
       </c>
       <c r="B309" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>855205</v>
+        <v>855182</v>
       </c>
       <c r="B310" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>855206</v>
+        <v>855185</v>
       </c>
       <c r="B311" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>855207</v>
+        <v>855189</v>
       </c>
       <c r="B312" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>855208</v>
+        <v>855191</v>
       </c>
       <c r="B313" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>855209</v>
+        <v>855192</v>
       </c>
       <c r="B314" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>854887</v>
+        <v>855193</v>
       </c>
       <c r="B315" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>854890</v>
+        <v>855194</v>
       </c>
       <c r="B316" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>854493</v>
+        <v>855195</v>
       </c>
       <c r="B317" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>854498</v>
+        <v>855196</v>
       </c>
       <c r="B318" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>854896</v>
+        <v>855197</v>
       </c>
       <c r="B319" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>854894</v>
+        <v>855198</v>
       </c>
       <c r="B320" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>851751</v>
+        <v>855199</v>
       </c>
       <c r="B321" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>849662</v>
+        <v>855200</v>
       </c>
       <c r="B322" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>853691</v>
+        <v>855201</v>
       </c>
       <c r="B323" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>849622</v>
+        <v>855202</v>
       </c>
       <c r="B324" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>849563</v>
+        <v>855204</v>
       </c>
       <c r="B325" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>855289</v>
+        <v>855205</v>
       </c>
       <c r="B326" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>854288</v>
+        <v>855206</v>
       </c>
       <c r="B327" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>854260</v>
+        <v>855207</v>
       </c>
       <c r="B328" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>854255</v>
+        <v>855208</v>
       </c>
       <c r="B329" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>854272</v>
+        <v>855209</v>
       </c>
       <c r="B330" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>849613</v>
+        <v>854887</v>
       </c>
       <c r="B331" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>854308</v>
+        <v>854890</v>
       </c>
       <c r="B332" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>854301</v>
+        <v>854493</v>
       </c>
       <c r="B333" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>854306</v>
+        <v>854498</v>
       </c>
       <c r="B334" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>854311</v>
+        <v>854896</v>
       </c>
       <c r="B335" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>854312</v>
+        <v>854894</v>
       </c>
       <c r="B336" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>854310</v>
+        <v>851751</v>
       </c>
       <c r="B337" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>849183</v>
+        <v>849662</v>
       </c>
       <c r="B338" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>849750</v>
+        <v>853691</v>
       </c>
       <c r="B339" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>849603</v>
+        <v>849622</v>
       </c>
       <c r="B340" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>852382</v>
+        <v>849563</v>
       </c>
       <c r="B341" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>849376</v>
+        <v>855289</v>
       </c>
       <c r="B342" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>849832</v>
+        <v>854288</v>
       </c>
       <c r="B343" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>849559</v>
+        <v>854260</v>
       </c>
       <c r="B344" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>849847</v>
+        <v>854255</v>
       </c>
       <c r="B345" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>853295</v>
+        <v>854272</v>
       </c>
       <c r="B346" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>849636</v>
+        <v>855766</v>
       </c>
       <c r="B347" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>849652</v>
+        <v>849613</v>
       </c>
       <c r="B348" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>849913</v>
+        <v>854308</v>
       </c>
       <c r="B349" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>855554</v>
+        <v>854311</v>
       </c>
       <c r="B350" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>855654</v>
+        <v>854310</v>
       </c>
       <c r="B351" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>849940</v>
+        <v>849183</v>
       </c>
       <c r="B352" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>849567</v>
+        <v>849750</v>
       </c>
       <c r="B353" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>849780</v>
+        <v>849603</v>
       </c>
       <c r="B354" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>849773</v>
+        <v>852382</v>
       </c>
       <c r="B355" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>855650</v>
+        <v>849376</v>
       </c>
       <c r="B356" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>849792</v>
+        <v>849832</v>
       </c>
       <c r="B357" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>849812</v>
+        <v>849559</v>
       </c>
       <c r="B358" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>849639</v>
+        <v>856064</v>
       </c>
       <c r="B359" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>853427</v>
+        <v>849847</v>
       </c>
       <c r="B360" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>853538</v>
+        <v>849636</v>
       </c>
       <c r="B361" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>849821</v>
+        <v>849652</v>
       </c>
       <c r="B362" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>848706</v>
+        <v>849913</v>
       </c>
       <c r="B363" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>849882</v>
+        <v>855616</v>
       </c>
       <c r="B364" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>852307</v>
+        <v>855554</v>
       </c>
       <c r="B365" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>854060</v>
+        <v>855654</v>
       </c>
       <c r="B366" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>853428</v>
+        <v>849940</v>
       </c>
       <c r="B367" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>855963</v>
+        <v>849567</v>
       </c>
       <c r="B368" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369">
-        <v>853773</v>
+        <v>849780</v>
       </c>
       <c r="B369" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370">
-        <v>855806</v>
+        <v>849773</v>
       </c>
       <c r="B370" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371">
-        <v>855735</v>
+        <v>849792</v>
       </c>
       <c r="B371" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372">
-        <v>855774</v>
+        <v>849812</v>
       </c>
       <c r="B372" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373">
-        <v>855730</v>
+        <v>849639</v>
       </c>
       <c r="B373" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374">
-        <v>856039</v>
+        <v>853427</v>
       </c>
       <c r="B374" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375">
-        <v>855538</v>
+        <v>853538</v>
       </c>
       <c r="B375" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376">
-        <v>855901</v>
+        <v>849821</v>
       </c>
       <c r="B376" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377">
-        <v>855895</v>
+        <v>854060</v>
       </c>
       <c r="B377" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378">
-        <v>855461</v>
+        <v>853428</v>
       </c>
       <c r="B378" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>855574</v>
+        <v>855697</v>
       </c>
       <c r="B379" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>855579</v>
+        <v>853773</v>
       </c>
       <c r="B380" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>855640</v>
+        <v>856166</v>
       </c>
       <c r="B381" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>855642</v>
+        <v>856219</v>
       </c>
       <c r="B382" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>855975</v>
+        <v>856202</v>
       </c>
       <c r="B383" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>855809</v>
+        <v>856039</v>
       </c>
       <c r="B384" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>855257</v>
+        <v>856153</v>
       </c>
       <c r="B385" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386">
-        <v>855436</v>
+        <v>855678</v>
       </c>
       <c r="B386" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387">
-        <v>855802</v>
+        <v>856099</v>
       </c>
       <c r="B387" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388">
-        <v>855822</v>
+        <v>855079</v>
       </c>
       <c r="B388" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389">
-        <v>855940</v>
+        <v>856173</v>
       </c>
       <c r="B389" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390">
-        <v>855920</v>
+        <v>856296</v>
       </c>
       <c r="B390" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391">
-        <v>855953</v>
+        <v>855640</v>
       </c>
       <c r="B391" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392">
-        <v>855703</v>
+        <v>855642</v>
       </c>
       <c r="B392" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393">
-        <v>856037</v>
+        <v>856074</v>
       </c>
       <c r="B393" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394">
-        <v>855518</v>
+        <v>855257</v>
       </c>
       <c r="B394" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395">
-        <v>855843</v>
+        <v>855436</v>
       </c>
       <c r="B395" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396">
-        <v>855811</v>
+        <v>855822</v>
       </c>
       <c r="B396" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397">
-        <v>855893</v>
+        <v>856065</v>
       </c>
       <c r="B397" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>856031</v>
+        <v>856037</v>
       </c>
       <c r="B398" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>855933</v>
+        <v>855518</v>
       </c>
       <c r="B399" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>855991</v>
+        <v>856226</v>
       </c>
       <c r="B400" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>855918</v>
+        <v>856211</v>
       </c>
       <c r="B401" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>855819</v>
+        <v>855781</v>
       </c>
       <c r="B402" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>855984</v>
+        <v>856059</v>
       </c>
       <c r="B403" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>855517</v>
+        <v>856093</v>
       </c>
       <c r="B404" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>855708</v>
+        <v>856031</v>
       </c>
       <c r="B405" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>855755</v>
+        <v>855858</v>
       </c>
       <c r="B406" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407">
-        <v>855952</v>
+        <v>855933</v>
       </c>
       <c r="B407" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408">
-        <v>855954</v>
+        <v>855991</v>
       </c>
       <c r="B408" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409">
-        <v>855724</v>
+        <v>856084</v>
       </c>
       <c r="B409" t="s">
-        <v>86</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>855517</v>
+      </c>
+      <c r="B410" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>855952</v>
+      </c>
+      <c r="B411" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>856087</v>
+      </c>
+      <c r="B412" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>856077</v>
+      </c>
+      <c r="B413" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>855954</v>
+      </c>
+      <c r="B414" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E233" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2616BCC9-C7E6-4D09-BA1F-780824741963}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC3AE4E-9E90-4D4B-B70E-CD71D4983E5F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="161">
   <si>
     <t>Pedido</t>
   </si>
@@ -74,14 +74,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.952,16_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 1.060,14_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
@@ -124,14 +116,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 146,14_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 971,18_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -342,46 +326,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.250,78_x000D_
-• Valor em ruptura: R$ 55,78_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.270,03_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 17.096,86_x000D_
-• Valor em ruptura: R$ 206,22_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.675,68_x000D_
-• Valor em ruptura: R$ 515,54_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 10.522,24_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -398,22 +342,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 96.400,69_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.057,80_x000D_
-• Valor em ruptura: R$ 4.102,09_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -438,27 +366,11 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 22.974,12_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 2.550,81_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.793,84_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -484,14 +396,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.876,49_x000D_
-• Valor em ruptura: R$ 50,56_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.684,16_x000D_
 • Valor em ruptura: R$ 39,37_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -513,44 +417,12 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.776,04_x000D_
-• Valor em ruptura: R$ 4.808,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 5.731,80_x000D_
 • Valor em ruptura: R$ 424,75_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.091,33_x000D_
-• Valor em ruptura: R$ 6.329,37_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.341,23_x000D_
-• Valor em ruptura: R$ 376,99_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.370,95_x000D_
-• Valor em ruptura: R$ 2.917,89_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -577,14 +449,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 248,52_x000D_
-• Valor em ruptura: R$ 518,52_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -617,14 +481,6 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.603,21_x000D_
-• Valor em ruptura: R$ 6.271,65_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -689,14 +545,6 @@
 • Valor mínimo de frete: R$ 7.175,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.388,00_x000D_
-• Valor em ruptura: R$ 130,31_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -705,14 +553,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.175,20_x000D_
-• Valor em ruptura: R$ 488,86_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -785,14 +625,6 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 526,59_x000D_
-• Valor em ruptura: R$ 12.658,73_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -805,7 +637,15 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.017,32_x000D_
+• Valor em ruptura: R$ 10.743,59_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.411,83_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -813,39 +653,7 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 10.743,59_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.411,83_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 6.577,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 15.012,05_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 8.548,75_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -857,30 +665,6 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.924,67_x000D_
-• Valor em ruptura: R$ 2.668,16_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 12.428,70_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.064,07_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -917,14 +701,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 11.030,97_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.660,61_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -937,30 +713,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 35.375,82_x000D_
-• Valor em ruptura: R$ 1.262,38_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 182,61_x000D_
-• Valor em ruptura: R$ 412,43_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.030,65_x000D_
-• Valor em ruptura: R$ 2.508,62_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -969,30 +721,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.621,13_x000D_
-• Valor em ruptura: R$ 3.858,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.604,14_x000D_
-• Valor em ruptura: R$ 2.342,25_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.270,45_x000D_
-• Valor em ruptura: R$ 1.292,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1001,22 +729,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.109,98_x000D_
-• Valor em ruptura: R$ 3.419,07_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.766,94_x000D_
-• Valor em ruptura: R$ 3.221,54_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1052,81 +764,17 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.418,80_x000D_
-• Valor em ruptura: R$ 2.790,81_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.839,07_x000D_
 • Valor em ruptura: R$ 646,09_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.733,17_x000D_
-• Valor em ruptura: R$ 1.067,90_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.843,65_x000D_
-• Valor em ruptura: R$ 3.634,43_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.858,84_x000D_
-• Valor em ruptura: R$ 2.781,89_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.307,31_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.009,81_x000D_
-• Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.801,31_x000D_
-• Valor em ruptura: R$ 1.772,22_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.449,78_x000D_
 • Valor em ruptura: R$ 3.512,13_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.374,84_x000D_
-• Valor em ruptura: R$ 93,29_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -1145,22 +793,6 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.126,21_x000D_
-• Valor em ruptura: R$ 1.866,55_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.459,00_x000D_
-• Valor em ruptura: R$ 4.449,86_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1185,46 +817,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.895,63_x000D_
-• Valor em ruptura: R$ 3.501,47_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.207,83_x000D_
-• Valor em ruptura: R$ 210,18_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.422,60_x000D_
-• Valor em ruptura: R$ 2.341,97_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.138,93_x000D_
-• Valor em ruptura: R$ 2.425,60_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 281,58_x000D_
-• Valor em ruptura: R$ 3.291,27_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1233,60 +825,12 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 320,56_x000D_
-• Valor em ruptura: R$ 4.666,38_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 638,33_x000D_
 • Valor em ruptura: R$ 1.851,85_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.072,56_x000D_
-• Valor em ruptura: R$ 477,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.257,53_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.735,86_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.719,36_x000D_
-• Valor em ruptura: R$ 1.202,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.808,20_x000D_
-• Valor em ruptura: R$ 1.098,35_x000D_
-• Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -1305,68 +849,12 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.664,11_x000D_
-• Valor em ruptura: R$ 2.341,28_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 764,20_x000D_
 • Valor em ruptura: R$ 5.017,32_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.089,17_x000D_
-• Valor em ruptura: R$ 2.803,22_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.696,13_x000D_
-• Valor em ruptura: R$ 138,57_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.555,81_x000D_
-• Valor em ruptura: R$ 924,46_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 26.407,88_x000D_
-• Valor em ruptura: R$ 1.806,24_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 562,92_x000D_
-• Valor em ruptura: R$ 3.068,67_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.105,02_x000D_
-• Valor em ruptura: R$ 441,48_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -1404,27 +892,11 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 1.674,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.253,09_x000D_
 • Valor em ruptura: R$ 3.064,71_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 12.175,94_x000D_
-• Valor em ruptura: R$ 979,22_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1436,16 +908,392 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.713,45_x000D_
-• Valor em ruptura: R$ 1.127,23_x000D_
+• Valor em estoque: R$ 2.446,15_x000D_
+• Valor em ruptura: R$ 5.401,58_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 11.530,27_x000D_
+• Valor em ruptura: R$ 733,61_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.970,95_x000D_
+• Valor em ruptura: R$ 440,87_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.322,30_x000D_
+• Valor em ruptura: R$ 462,50_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.293,81_x000D_
+• Valor em ruptura: R$ 540,89_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.606,01_x000D_
+• Valor em ruptura: R$ 3.926,18_x000D_
+• Valor mínimo de frete: R$ 6.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.963,89_x000D_
+• Valor em ruptura: R$ 988,27_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.199,50_x000D_
+• Valor em ruptura: R$ 802,75_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.889,71_x000D_
+• Valor em ruptura: R$ 1.364,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 36.458,51_x000D_
+• Valor em ruptura: R$ 179,69_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.925,61_x000D_
+• Valor em ruptura: R$ 622,83_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 927,97_x000D_
+• Valor em ruptura: R$ 43,21_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.876,49_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.530,58_x000D_
+• Valor em ruptura: R$ 202,24_x000D_
+• Valor mínimo de frete: R$ 7.175,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.372,62_x000D_
+• Valor em ruptura: R$ 166,65_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.034,02_x000D_
+• Valor em ruptura: R$ 3.445,82_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.223,48_x000D_
+• Valor em ruptura: R$ 1.722,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 33.726,72_x000D_
-• Valor em ruptura: R$ 38.120,84_x000D_
+• Valor em estoque: R$ 11.905,22_x000D_
+• Valor em ruptura: R$ 8.614,54_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.729,32_x000D_
+• Valor em ruptura: R$ 2.799,73_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.973,39_x000D_
+• Valor em ruptura: R$ 3.015,09_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.625,25_x000D_
+• Valor em ruptura: R$ 2.584,36_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.939,62_x000D_
+• Valor em ruptura: R$ 861,45_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.462,99_x000D_
+• Valor em ruptura: R$ 3.015,09_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.271,73_x000D_
+• Valor em ruptura: R$ 2.369,00_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.549,48_x000D_
+• Valor em ruptura: R$ 183,55_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.769,04_x000D_
+• Valor em ruptura: R$ 250,87_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.297,94_x000D_
+• Valor em ruptura: R$ 2.508,66_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.504,06_x000D_
+• Valor em ruptura: R$ 506,35_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.745,68_x000D_
+• Valor em ruptura: R$ 13.546,77_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.908,34_x000D_
+• Valor em ruptura: R$ 3.174,60_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.408,47_x000D_
+• Valor em ruptura: R$ 169,95_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.660,96_x000D_
+• Valor em ruptura: R$ 4.449,86_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 39.903,57_x000D_
+• Valor em ruptura: R$ 189,43_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.389,94_x000D_
+• Valor em ruptura: R$ 2.383,23_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.316,01_x000D_
+• Valor em ruptura: R$ 506,35_x000D_
+• Valor mínimo de frete: R$ 7.175,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 11.423,28_x000D_
+• Valor em ruptura: R$ 1.770,98_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.458,05_x000D_
+• Valor em ruptura: R$ 1.851,85_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 552,39_x000D_
+• Valor em ruptura: R$ 1.986,86_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 25.879,72_x000D_
+• Valor em ruptura: R$ 1.770,11_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 1.423,29_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.472,82_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.098,16_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 9.225,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.019,23_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.517,44_x000D_
+• Valor em ruptura: R$ 5.524,09_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 11.034,88_x000D_
+• Valor em ruptura: R$ 11.048,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.988,26_x000D_
+• Valor em ruptura: R$ 2.101,78_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 33.802,88_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 901,20_x000D_
+• Valor em ruptura: R$ 12.104,38_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
 </sst>
@@ -1833,7 +1681,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E414"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -1861,231 +1709,231 @@
     </row>
     <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>854781</v>
+        <v>856373</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>3093</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>848783</v>
+        <v>856468</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>853426</v>
+        <v>856458</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>3075</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>850631</v>
+        <v>856511</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>147</v>
+        <v>773</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>854985</v>
+        <v>856456</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>2090</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>849811</v>
+        <v>856199</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>3058</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>855293</v>
+        <v>856376</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>2072</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>849918</v>
+        <v>854781</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>750</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>856191</v>
+        <v>848783</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>922</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>852593</v>
+        <v>853426</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>632</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>853998</v>
+        <v>850631</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>722</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>853854</v>
+        <v>856565</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>773</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>853852</v>
+        <v>854985</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>773</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>856033</v>
+        <v>856547</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>373</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>854933</v>
+        <v>856434</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>983</v>
+        <v>703</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>854931</v>
+        <v>849811</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>983</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>854585</v>
+        <v>855293</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>41</v>
@@ -2094,253 +1942,253 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>933</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>855295</v>
+        <v>849918</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>377</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>854330</v>
+        <v>856191</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>281</v>
+        <v>922</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>855330</v>
+        <v>852593</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>703</v>
+        <v>632</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>855731</v>
+        <v>853998</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>1021</v>
+        <v>722</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>856303</v>
+        <v>856550</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>854385</v>
+        <v>855692</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>2090</v>
+        <v>574</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>855232</v>
+        <v>856570</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>2084</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>855480</v>
+        <v>853852</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>3037</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>855445</v>
+        <v>856033</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>284</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>854374</v>
+        <v>854933</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>856089</v>
+        <v>854931</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>856122</v>
+        <v>855295</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>90</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>856130</v>
+        <v>854330</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>856103</v>
+        <v>855731</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>90</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>856148</v>
+        <v>856447</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>856172</v>
+        <v>856303</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>856150</v>
+        <v>855480</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>856157</v>
+        <v>856089</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -2349,9 +2197,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>856161</v>
+        <v>856122</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>127</v>
@@ -2365,7 +2213,7 @@
     </row>
     <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>856168</v>
+        <v>856130</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>128</v>
@@ -2379,7 +2227,7 @@
     </row>
     <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>856182</v>
+        <v>856452</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>129</v>
@@ -2393,10 +2241,10 @@
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>856192</v>
+        <v>856148</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
@@ -2407,10 +2255,10 @@
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>856291</v>
+        <v>856172</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2421,10 +2269,10 @@
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>856215</v>
+        <v>856150</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -2433,12 +2281,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>856282</v>
+        <v>856157</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2449,10 +2297,10 @@
     </row>
     <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>856221</v>
+        <v>856161</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
@@ -2461,124 +2309,124 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>855764</v>
+        <v>856168</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>855761</v>
+        <v>856182</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>855759</v>
+        <v>856192</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>855758</v>
+        <v>856291</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>855756</v>
+        <v>856215</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>855753</v>
+        <v>856282</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>855749</v>
+        <v>856221</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>855748</v>
+        <v>856440</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>642</v>
+        <v>756</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>855746</v>
+        <v>855764</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -2587,222 +2435,222 @@
         <v>642</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>856005</v>
+        <v>855761</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>773</v>
+        <v>642</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>855783</v>
+        <v>855759</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>748</v>
+        <v>642</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855666</v>
+        <v>855758</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>855872</v>
+        <v>855756</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>856043</v>
+        <v>855753</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>737</v>
+        <v>642</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>855896</v>
+        <v>855749</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>855834</v>
+        <v>855748</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>855746</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>856005</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>856559</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D60" t="s">
-        <v>5</v>
-      </c>
-      <c r="E60">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>855512</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61">
-        <v>3057</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>856208</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>855742</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
-        <v>614</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>855690</v>
+        <v>856437</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64">
-        <v>388</v>
+        <v>703</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>856194</v>
+        <v>855666</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65">
-        <v>614</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>856008</v>
+        <v>856500</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>855934</v>
+        <v>855896</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>614</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>856026</v>
+        <v>855512</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>699</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>855931</v>
+        <v>856208</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
@@ -2813,178 +2661,178 @@
     </row>
     <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>856124</v>
+        <v>856539</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>2051</v>
+        <v>699</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>856227</v>
+        <v>856008</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>853459</v>
+        <v>856026</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>850430</v>
+        <v>856558</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>2081</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>855797</v>
+        <v>856560</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>90</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>856304</v>
+        <v>856124</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>856055</v>
+        <v>853459</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>3078</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>856000</v>
+        <v>850430</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>699</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>855997</v>
+        <v>856489</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>699</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>855999</v>
+        <v>856520</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>855996</v>
+        <v>856304</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>699</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>855998</v>
+        <v>856055</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>855994</v>
+        <v>856000</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
@@ -2993,12 +2841,12 @@
         <v>699</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>855995</v>
+        <v>855999</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
@@ -3007,40 +2855,40 @@
         <v>699</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>855650</v>
+        <v>855996</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>916</v>
+        <v>699</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>855648</v>
+        <v>856555</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>916</v>
+        <v>564</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>855651</v>
+        <v>855650</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
@@ -3051,66 +2899,66 @@
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>856289</v>
+        <v>856531</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>856034</v>
+        <v>854263</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>642</v>
+        <v>574</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>854263</v>
+        <v>855699</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>574</v>
+        <v>429</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>856283</v>
+        <v>856438</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>2084</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>855699</v>
+        <v>855426</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
@@ -3121,203 +2969,203 @@
     </row>
     <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>856305</v>
+        <v>855506</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>2040</v>
+        <v>569</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>855426</v>
+        <v>856421</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>429</v>
+        <v>829</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>855506</v>
+        <v>856189</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>569</v>
+        <v>699</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>856068</v>
+        <v>856453</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>3037</v>
+        <v>699</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>855790</v>
+        <v>856003</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>2097</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>855794</v>
+        <v>856306</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>2097</v>
+        <v>653</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>855890</v>
+        <v>856287</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>856189</v>
+        <v>856011</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>699</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>856003</v>
+        <v>855496</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>90</v>
+        <v>811</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>856306</v>
+        <v>856450</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>856181</v>
+        <v>856179</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>3037</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>856287</v>
+        <v>856177</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>699</v>
+        <v>294</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>855498</v>
+        <v>853358</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>3097</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>855985</v>
+        <v>855468</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>856011</v>
+        <v>855660</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>105</v>
@@ -3326,82 +3174,82 @@
         <v>5</v>
       </c>
       <c r="E106">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>856203</v>
+        <v>855001</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>157</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>856056</v>
+        <v>855887</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>669</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>855496</v>
+        <v>856470</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>811</v>
+        <v>951</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>856190</v>
+        <v>856023</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>818</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>856179</v>
+        <v>856210</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>855717</v>
+        <v>856198</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>106</v>
@@ -3410,614 +3258,614 @@
         <v>5</v>
       </c>
       <c r="E112">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>856177</v>
+        <v>856090</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>856313</v>
+        <v>851354</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>3062</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>853358</v>
+        <v>851356</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>855468</v>
+        <v>851357</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>294</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>856024</v>
+        <v>854953</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>3035</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>855929</v>
+        <v>854954</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>3034</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>856311</v>
+        <v>851359</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>2072</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>855660</v>
+        <v>854955</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>856206</v>
+        <v>854956</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>2034</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>856199</v>
+        <v>844931</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>855001</v>
+        <v>851348</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>874</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>855887</v>
+        <v>851349</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>856128</v>
+        <v>854602</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855692</v>
+        <v>855254</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>856300</v>
+        <v>855272</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>856023</v>
+        <v>855271</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>3034</v>
+        <v>906</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>856210</v>
+        <v>855438</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>855914</v>
+        <v>856530</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>3045</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>856209</v>
+        <v>855494</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>3034</v>
+        <v>979</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>856198</v>
+        <v>856405</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>2047</v>
+        <v>979</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>856090</v>
+        <v>854939</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>851354</v>
+        <v>856486</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>60</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>851357</v>
+        <v>856162</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>854953</v>
+        <v>855297</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>60</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>854954</v>
+        <v>854777</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>851359</v>
+        <v>856533</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>854955</v>
+        <v>856123</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>854956</v>
+        <v>856471</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>844931</v>
+        <v>856010</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>60</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>851348</v>
+        <v>856018</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>851349</v>
+        <v>856378</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>854602</v>
+        <v>855278</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>855576</v>
+        <v>855935</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>407</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>855261</v>
+        <v>853734</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>906</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>855254</v>
+        <v>853738</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>855272</v>
+        <v>852720</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>855271</v>
+        <v>855583</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>855438</v>
+        <v>855990</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>853930</v>
+        <v>855374</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>979</v>
+        <v>293</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>855494</v>
+        <v>855636</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>979</v>
+        <v>851</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>854939</v>
+        <v>856021</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>856162</v>
+        <v>854925</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>2047</v>
+        <v>904</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>855297</v>
+        <v>856187</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>381</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>854777</v>
+        <v>848786</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>35</v>
@@ -4026,2275 +3874,1787 @@
         <v>5</v>
       </c>
       <c r="E156">
-        <v>3</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>856123</v>
+        <v>856367</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>856010</v>
+        <v>856466</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>3081</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>856018</v>
+        <v>856515</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>855703</v>
+        <v>855815</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>855278</v>
+        <v>854839</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>293</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>855935</v>
+        <v>856299</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>2047</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>853734</v>
+        <v>856301</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>853738</v>
+        <v>855782</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>852720</v>
+        <v>856406</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>1019</v>
+        <v>968</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>855884</v>
+        <v>854835</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>639</v>
+        <v>851</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>855583</v>
+        <v>856372</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>778</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>855990</v>
+        <v>855906</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>979</v>
+        <v>293</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>855374</v>
+        <v>855847</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>293</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>855636</v>
+        <v>852886</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>855987</v>
+        <v>856414</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D171" t="s">
-        <v>5</v>
-      </c>
-      <c r="E171">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>856174</v>
+        <v>856427</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D172" t="s">
-        <v>5</v>
-      </c>
-      <c r="E172">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>856021</v>
+        <v>856383</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D173" t="s">
-        <v>5</v>
-      </c>
-      <c r="E173">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>854925</v>
+        <v>856390</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>856187</v>
+        <v>856377</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D175" t="s">
-        <v>5</v>
-      </c>
-      <c r="E175">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>856213</v>
+        <v>856401</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D176" t="s">
-        <v>5</v>
-      </c>
-      <c r="E176">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>855492</v>
+        <v>855903</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D177" t="s">
-        <v>5</v>
-      </c>
-      <c r="E177">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>855382</v>
+        <v>856522</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D178" t="s">
-        <v>5</v>
-      </c>
-      <c r="E178">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>855578</v>
+        <v>856449</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="E179">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>848786</v>
+        <v>856472</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D180" t="s">
-        <v>5</v>
-      </c>
-      <c r="E180">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>855815</v>
+        <v>856465</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D181" t="s">
-        <v>5</v>
-      </c>
-      <c r="E181">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>854839</v>
+        <v>856507</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D182" t="s">
-        <v>5</v>
-      </c>
-      <c r="E182">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>856299</v>
+        <v>856491</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D183" t="s">
-        <v>5</v>
-      </c>
-      <c r="E183">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>856301</v>
+        <v>856469</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D184" t="s">
-        <v>5</v>
-      </c>
-      <c r="E184">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>855782</v>
+        <v>850108</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D185" t="s">
-        <v>5</v>
-      </c>
-      <c r="E185">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>854835</v>
+        <v>850002</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D186" t="s">
-        <v>5</v>
-      </c>
-      <c r="E186">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>855906</v>
+        <v>851031</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
-      </c>
-      <c r="E187">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>855310</v>
+        <v>856420</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D188" t="s">
-        <v>5</v>
-      </c>
-      <c r="E188">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>855847</v>
+        <v>856506</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D189" t="s">
-        <v>5</v>
-      </c>
-      <c r="E189">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>852886</v>
+        <v>853850</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D190" t="s">
-        <v>5</v>
-      </c>
-      <c r="E190">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>855350</v>
+        <v>853854</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>855072</v>
+        <v>853853</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>854500</v>
+        <v>856394</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>854895</v>
+        <v>856246</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>854917</v>
+        <v>856274</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>854503</v>
+        <v>856347</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>854506</v>
+        <v>856339</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>854903</v>
+        <v>856330</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>854494</v>
+        <v>856340</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>854911</v>
+        <v>856279</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>854499</v>
+        <v>856230</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>854504</v>
+        <v>856242</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>854908</v>
+        <v>856273</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>854910</v>
+        <v>856355</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>854496</v>
+        <v>856327</v>
       </c>
       <c r="B205" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>854507</v>
+        <v>856256</v>
       </c>
       <c r="B206" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>854900</v>
+        <v>856234</v>
       </c>
       <c r="B207" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>854906</v>
+        <v>856354</v>
       </c>
       <c r="B208" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>854907</v>
+        <v>856253</v>
       </c>
       <c r="B209" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>855903</v>
+        <v>856229</v>
       </c>
       <c r="B210" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>850108</v>
+        <v>856243</v>
       </c>
       <c r="B211" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>850002</v>
+        <v>856275</v>
       </c>
       <c r="B212" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>851031</v>
+        <v>856252</v>
       </c>
       <c r="B213" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>856131</v>
+        <v>856272</v>
       </c>
       <c r="B214" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>853850</v>
+        <v>856268</v>
       </c>
       <c r="B215" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>853853</v>
+        <v>856265</v>
       </c>
       <c r="B216" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>843776</v>
+        <v>855785</v>
       </c>
       <c r="B217" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>843780</v>
+        <v>856451</v>
       </c>
       <c r="B218" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>843785</v>
+        <v>856423</v>
       </c>
       <c r="B219" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>844518</v>
+        <v>848673</v>
       </c>
       <c r="B220" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>844527</v>
+        <v>854385</v>
       </c>
       <c r="B221" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>846411</v>
+        <v>855246</v>
       </c>
       <c r="B222" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>846414</v>
+        <v>854940</v>
       </c>
       <c r="B223" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>847008</v>
+        <v>849969</v>
       </c>
       <c r="B224" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>851106</v>
+        <v>856328</v>
       </c>
       <c r="B225" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>851109</v>
+        <v>856277</v>
       </c>
       <c r="B226" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>851875</v>
+        <v>856278</v>
       </c>
       <c r="B227" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>851876</v>
+        <v>856318</v>
       </c>
       <c r="B228" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>851881</v>
+        <v>856324</v>
       </c>
       <c r="B229" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>852454</v>
+        <v>856276</v>
       </c>
       <c r="B230" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>846997</v>
+        <v>856357</v>
       </c>
       <c r="B231" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>847009</v>
+        <v>856257</v>
       </c>
       <c r="B232" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>848642</v>
+        <v>856238</v>
       </c>
       <c r="B233" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>851100</v>
+        <v>856232</v>
       </c>
       <c r="B234" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>851115</v>
+        <v>856241</v>
       </c>
       <c r="B235" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>852345</v>
+        <v>856326</v>
       </c>
       <c r="B236" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>852346</v>
+        <v>856258</v>
       </c>
       <c r="B237" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>852352</v>
+        <v>856337</v>
       </c>
       <c r="B238" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>852452</v>
+        <v>856255</v>
       </c>
       <c r="B239" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>854898</v>
+        <v>856338</v>
       </c>
       <c r="B240" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>856246</v>
+        <v>856233</v>
       </c>
       <c r="B241" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>856274</v>
+        <v>856317</v>
       </c>
       <c r="B242" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>856279</v>
+        <v>856321</v>
       </c>
       <c r="B243" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>856230</v>
+        <v>856263</v>
       </c>
       <c r="B244" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>856242</v>
+        <v>856346</v>
       </c>
       <c r="B245" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>856273</v>
+        <v>856237</v>
       </c>
       <c r="B246" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>856256</v>
+        <v>856319</v>
       </c>
       <c r="B247" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>856234</v>
+        <v>856333</v>
       </c>
       <c r="B248" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>856253</v>
+        <v>856240</v>
       </c>
       <c r="B249" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>856229</v>
+        <v>856259</v>
       </c>
       <c r="B250" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>856243</v>
+        <v>856336</v>
       </c>
       <c r="B251" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>856275</v>
+        <v>856335</v>
       </c>
       <c r="B252" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>856252</v>
+        <v>856270</v>
       </c>
       <c r="B253" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>856272</v>
+        <v>856351</v>
       </c>
       <c r="B254" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>856268</v>
+        <v>856235</v>
       </c>
       <c r="B255" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>856265</v>
+        <v>856315</v>
       </c>
       <c r="B256" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>855882</v>
+        <v>856316</v>
       </c>
       <c r="B257" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>855880</v>
+        <v>856269</v>
       </c>
       <c r="B258" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>855877</v>
+        <v>856353</v>
       </c>
       <c r="B259" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>855831</v>
+        <v>856271</v>
       </c>
       <c r="B260" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>855874</v>
+        <v>856341</v>
       </c>
       <c r="B261" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>855871</v>
+        <v>856266</v>
       </c>
       <c r="B262" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>855868</v>
+        <v>856358</v>
       </c>
       <c r="B263" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>855865</v>
+        <v>856323</v>
       </c>
       <c r="B264" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>855861</v>
+        <v>856322</v>
       </c>
       <c r="B265" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>855827</v>
+        <v>856352</v>
       </c>
       <c r="B266" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>855824</v>
+        <v>856342</v>
       </c>
       <c r="B267" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>855857</v>
+        <v>856325</v>
       </c>
       <c r="B268" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>855855</v>
+        <v>856334</v>
       </c>
       <c r="B269" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>855891</v>
+        <v>856350</v>
       </c>
       <c r="B270" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>855885</v>
+        <v>856359</v>
       </c>
       <c r="B271" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>855835</v>
+        <v>856348</v>
       </c>
       <c r="B272" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>855888</v>
+        <v>856236</v>
       </c>
       <c r="B273" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>855853</v>
+        <v>856320</v>
       </c>
       <c r="B274" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>855838</v>
+        <v>856349</v>
       </c>
       <c r="B275" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>856110</v>
+        <v>856267</v>
       </c>
       <c r="B276" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>855785</v>
+        <v>856356</v>
       </c>
       <c r="B277" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>855972</v>
+        <v>849444</v>
       </c>
       <c r="B278" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>856163</v>
+        <v>856397</v>
       </c>
       <c r="B279" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>848673</v>
+        <v>856386</v>
       </c>
       <c r="B280" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>855246</v>
+        <v>856392</v>
       </c>
       <c r="B281" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>854940</v>
+        <v>851751</v>
       </c>
       <c r="B282" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>849969</v>
+        <v>849662</v>
       </c>
       <c r="B283" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>856277</v>
+        <v>853691</v>
       </c>
       <c r="B284" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>856278</v>
+        <v>849622</v>
       </c>
       <c r="B285" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>856276</v>
+        <v>849563</v>
       </c>
       <c r="B286" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>856257</v>
+        <v>855289</v>
       </c>
       <c r="B287" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>856238</v>
+        <v>854288</v>
       </c>
       <c r="B288" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>856232</v>
+        <v>854260</v>
       </c>
       <c r="B289" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>856241</v>
+        <v>854255</v>
       </c>
       <c r="B290" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>856258</v>
+        <v>856448</v>
       </c>
       <c r="B291" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>856255</v>
+        <v>856509</v>
       </c>
       <c r="B292" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>856233</v>
+        <v>854272</v>
       </c>
       <c r="B293" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>856263</v>
+        <v>855766</v>
       </c>
       <c r="B294" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>856237</v>
+        <v>849613</v>
       </c>
       <c r="B295" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>856240</v>
+        <v>849183</v>
       </c>
       <c r="B296" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>856259</v>
+        <v>849750</v>
       </c>
       <c r="B297" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>856270</v>
+        <v>849603</v>
       </c>
       <c r="B298" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>856235</v>
+        <v>852382</v>
       </c>
       <c r="B299" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>856269</v>
+        <v>849376</v>
       </c>
       <c r="B300" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>856271</v>
+        <v>849832</v>
       </c>
       <c r="B301" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>856266</v>
+        <v>849559</v>
       </c>
       <c r="B302" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>856236</v>
+        <v>856064</v>
       </c>
       <c r="B303" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>856267</v>
+        <v>849847</v>
       </c>
       <c r="B304" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>849444</v>
+        <v>849636</v>
       </c>
       <c r="B305" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>856295</v>
+        <v>855807</v>
       </c>
       <c r="B306" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>855178</v>
+        <v>849652</v>
       </c>
       <c r="B307" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>855180</v>
+        <v>849913</v>
       </c>
       <c r="B308" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>855181</v>
+        <v>855654</v>
       </c>
       <c r="B309" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>855182</v>
+        <v>856499</v>
       </c>
       <c r="B310" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>855185</v>
+        <v>849940</v>
       </c>
       <c r="B311" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>855189</v>
+        <v>856312</v>
       </c>
       <c r="B312" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>855191</v>
+        <v>849567</v>
       </c>
       <c r="B313" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>855192</v>
+        <v>849780</v>
       </c>
       <c r="B314" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>855193</v>
+        <v>849773</v>
       </c>
       <c r="B315" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>855194</v>
+        <v>849792</v>
       </c>
       <c r="B316" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>855195</v>
+        <v>849812</v>
       </c>
       <c r="B317" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>855196</v>
+        <v>849639</v>
       </c>
       <c r="B318" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>855197</v>
+        <v>853427</v>
       </c>
       <c r="B319" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>855198</v>
+        <v>853538</v>
       </c>
       <c r="B320" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>855199</v>
+        <v>849821</v>
       </c>
       <c r="B321" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>855200</v>
+        <v>854060</v>
       </c>
       <c r="B322" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>855201</v>
+        <v>853428</v>
       </c>
       <c r="B323" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>855202</v>
+        <v>855697</v>
       </c>
       <c r="B324" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>855204</v>
+        <v>855890</v>
       </c>
       <c r="B325" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>855205</v>
+        <v>853773</v>
       </c>
       <c r="B326" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>855206</v>
+        <v>856496</v>
       </c>
       <c r="B327" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>855207</v>
+        <v>856418</v>
       </c>
       <c r="B328" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>855208</v>
+        <v>856202</v>
       </c>
       <c r="B329" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>855209</v>
+        <v>856546</v>
       </c>
       <c r="B330" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>854887</v>
+        <v>856413</v>
       </c>
       <c r="B331" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>854890</v>
+        <v>856526</v>
       </c>
       <c r="B332" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>854493</v>
+        <v>856431</v>
       </c>
       <c r="B333" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>854498</v>
+        <v>856564</v>
       </c>
       <c r="B334" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>854896</v>
+        <v>855929</v>
       </c>
       <c r="B335" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>854894</v>
+        <v>856424</v>
       </c>
       <c r="B336" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>851751</v>
+        <v>856552</v>
       </c>
       <c r="B337" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>849662</v>
+        <v>856366</v>
       </c>
       <c r="B338" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>853691</v>
+        <v>855461</v>
       </c>
       <c r="B339" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>849622</v>
+        <v>855678</v>
       </c>
       <c r="B340" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>849563</v>
+        <v>856481</v>
       </c>
       <c r="B341" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>855289</v>
+        <v>855079</v>
       </c>
       <c r="B342" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>854288</v>
+        <v>855914</v>
       </c>
       <c r="B343" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>854260</v>
+        <v>856296</v>
       </c>
       <c r="B344" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>854255</v>
+        <v>855640</v>
       </c>
       <c r="B345" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>854272</v>
+        <v>855642</v>
       </c>
       <c r="B346" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>855766</v>
+        <v>856074</v>
       </c>
       <c r="B347" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>849613</v>
+        <v>855257</v>
       </c>
       <c r="B348" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>854308</v>
+        <v>855436</v>
       </c>
       <c r="B349" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>854311</v>
+        <v>855822</v>
       </c>
       <c r="B350" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>854310</v>
+        <v>856441</v>
       </c>
       <c r="B351" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>849183</v>
+        <v>856364</v>
       </c>
       <c r="B352" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>849750</v>
+        <v>856562</v>
       </c>
       <c r="B353" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>849603</v>
+        <v>855703</v>
       </c>
       <c r="B354" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>852382</v>
+        <v>856516</v>
       </c>
       <c r="B355" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>849376</v>
+        <v>856417</v>
       </c>
       <c r="B356" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>849832</v>
+        <v>855518</v>
       </c>
       <c r="B357" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>849559</v>
+        <v>856226</v>
       </c>
       <c r="B358" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>856064</v>
+        <v>856363</v>
       </c>
       <c r="B359" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>849847</v>
+        <v>855781</v>
       </c>
       <c r="B360" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>849636</v>
+        <v>855858</v>
       </c>
       <c r="B361" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>849652</v>
+        <v>855933</v>
       </c>
       <c r="B362" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>849913</v>
+        <v>856369</v>
       </c>
       <c r="B363" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>855616</v>
+        <v>856521</v>
       </c>
       <c r="B364" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>855554</v>
+        <v>855708</v>
       </c>
       <c r="B365" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>855654</v>
+        <v>856087</v>
       </c>
       <c r="B366" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>849940</v>
+        <v>856077</v>
       </c>
       <c r="B367" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>849567</v>
+        <v>856428</v>
       </c>
       <c r="B368" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369">
-        <v>849780</v>
-      </c>
-      <c r="B369" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370">
-        <v>849773</v>
-      </c>
-      <c r="B370" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371">
-        <v>849792</v>
-      </c>
-      <c r="B371" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372">
-        <v>849812</v>
-      </c>
-      <c r="B372" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373">
-        <v>849639</v>
-      </c>
-      <c r="B373" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374">
-        <v>853427</v>
-      </c>
-      <c r="B374" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375">
-        <v>853538</v>
-      </c>
-      <c r="B375" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376">
-        <v>849821</v>
-      </c>
-      <c r="B376" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377">
-        <v>854060</v>
-      </c>
-      <c r="B377" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A378">
-        <v>853428</v>
-      </c>
-      <c r="B378" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A379">
-        <v>855697</v>
-      </c>
-      <c r="B379" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A380">
-        <v>853773</v>
-      </c>
-      <c r="B380" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A381">
-        <v>856166</v>
-      </c>
-      <c r="B381" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A382">
-        <v>856219</v>
-      </c>
-      <c r="B382" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A383">
-        <v>856202</v>
-      </c>
-      <c r="B383" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A384">
-        <v>856039</v>
-      </c>
-      <c r="B384" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A385">
-        <v>856153</v>
-      </c>
-      <c r="B385" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A386">
-        <v>855678</v>
-      </c>
-      <c r="B386" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A387">
-        <v>856099</v>
-      </c>
-      <c r="B387" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A388">
-        <v>855079</v>
-      </c>
-      <c r="B388" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A389">
-        <v>856173</v>
-      </c>
-      <c r="B389" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A390">
-        <v>856296</v>
-      </c>
-      <c r="B390" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A391">
-        <v>855640</v>
-      </c>
-      <c r="B391" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A392">
-        <v>855642</v>
-      </c>
-      <c r="B392" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A393">
-        <v>856074</v>
-      </c>
-      <c r="B393" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A394">
-        <v>855257</v>
-      </c>
-      <c r="B394" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A395">
-        <v>855436</v>
-      </c>
-      <c r="B395" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396">
-        <v>855822</v>
-      </c>
-      <c r="B396" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A397">
-        <v>856065</v>
-      </c>
-      <c r="B397" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A398">
-        <v>856037</v>
-      </c>
-      <c r="B398" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A399">
-        <v>855518</v>
-      </c>
-      <c r="B399" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A400">
-        <v>856226</v>
-      </c>
-      <c r="B400" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A401">
-        <v>856211</v>
-      </c>
-      <c r="B401" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A402">
-        <v>855781</v>
-      </c>
-      <c r="B402" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A403">
-        <v>856059</v>
-      </c>
-      <c r="B403" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A404">
-        <v>856093</v>
-      </c>
-      <c r="B404" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A405">
-        <v>856031</v>
-      </c>
-      <c r="B405" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A406">
-        <v>855858</v>
-      </c>
-      <c r="B406" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A407">
-        <v>855933</v>
-      </c>
-      <c r="B407" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408">
-        <v>855991</v>
-      </c>
-      <c r="B408" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A409">
-        <v>856084</v>
-      </c>
-      <c r="B409" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A410">
-        <v>855517</v>
-      </c>
-      <c r="B410" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A411">
-        <v>855952</v>
-      </c>
-      <c r="B411" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A412">
-        <v>856087</v>
-      </c>
-      <c r="B412" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413">
-        <v>856077</v>
-      </c>
-      <c r="B413" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414">
-        <v>855954</v>
-      </c>
-      <c r="B414" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC3AE4E-9E90-4D4B-B70E-CD71D4983E5F}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{084C9A86-E875-4BE2-B237-F76BDDBC1122}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="183">
   <si>
     <t>Pedido</t>
   </si>
@@ -60,14 +60,6 @@
   </si>
   <si>
     <t>Novo Pedido</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 18.414,16_x000D_
-• Valor em ruptura: R$ 145,26_x000D_
-• Valor mínimo de frete: R$ 9.225,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -142,14 +134,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 73.543,24_x000D_
-• Valor em ruptura: R$ 15.459,97_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -302,14 +286,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 23.378,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -334,22 +310,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 18.487,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.174,99_x000D_
-• Valor em ruptura: R$ 252,48_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -366,14 +326,6 @@
 • Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.550,81_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -393,28 +345,12 @@
     <t>O valor do pedido encontra-se abaixo do mínimo estabelecido para a região, ficamos no aguarde de pedido complementar ou cancelamento do mesmo.</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.684,16_x000D_
-• Valor em ruptura: R$ 39,37_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.783,99_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 64.407,33_x000D_
-• Valor em ruptura: R$ 2.163,98_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -493,22 +429,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 55.154,85_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 10.167,26_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.676,72_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -529,14 +449,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.282,45_x000D_
-• Valor em ruptura: R$ 239,79_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -633,30 +545,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 10.743,59_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.411,83_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 6.577,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -684,22 +572,6 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.086,03_x000D_
-• Valor em ruptura: R$ 4.624,99_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.327,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 3.660,61_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -780,48 +652,8 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.053,44_x000D_
-• Valor em ruptura: R$ 3.038,10_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.506,75_x000D_
-• Valor em ruptura: R$ 2.025,40_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.629,78_x000D_
 • Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.350,96_x000D_
-• Valor em ruptura: R$ 2.358,14_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.543,42_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.729,66_x000D_
-• Valor em ruptura: R$ 2.645,50_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -861,72 +693,8 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.844,69_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 14.541,42_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 19.666,50_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.129,54_x000D_
-• Valor em ruptura: R$ 16.745,29_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.253,09_x000D_
-• Valor em ruptura: R$ 3.064,71_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.599,19_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.446,15_x000D_
-• Valor em ruptura: R$ 5.401,58_x000D_
-• Valor mínimo de frete: R$ 7.325,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 11.530,27_x000D_
-• Valor em ruptura: R$ 733,61_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.970,95_x000D_
-• Valor em ruptura: R$ 440,87_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
@@ -948,14 +716,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.606,01_x000D_
-• Valor em ruptura: R$ 3.926,18_x000D_
-• Valor mínimo de frete: R$ 6.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.963,89_x000D_
 • Valor em ruptura: R$ 988,27_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -964,35 +724,11 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.199,50_x000D_
-• Valor em ruptura: R$ 802,75_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.889,71_x000D_
-• Valor em ruptura: R$ 1.364,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 36.458,51_x000D_
 • Valor em ruptura: R$ 179,69_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.925,61_x000D_
-• Valor em ruptura: R$ 622,83_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1164,14 +900,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 39.903,57_x000D_
-• Valor em ruptura: R$ 189,43_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 7.389,94_x000D_
 • Valor em ruptura: R$ 2.383,23_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1225,46 +953,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 5.472,82_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.098,16_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 9.225,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 4.019,23_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.517,44_x000D_
-• Valor em ruptura: R$ 5.524,09_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1273,14 +961,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.988,26_x000D_
-• Valor em ruptura: R$ 2.101,78_x000D_
-• Valor mínimo de frete: R$ 6.250,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1295,6 +975,502 @@
 • Valor em estoque: R$ 901,20_x000D_
 • Valor em ruptura: R$ 12.104,38_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.129,11_x000D_
+• Valor em ruptura: R$ 1.841,44_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.280,71_x000D_
+• Valor em ruptura: R$ 1.178,13_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.518,88_x000D_
+• Valor em ruptura: R$ 291,49_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.720,72_x000D_
+• Valor em ruptura: R$ 999,20_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 11.762,18_x000D_
+• Valor em ruptura: R$ 501,70_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.668,24_x000D_
+• Valor em ruptura: R$ 4.370,46_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.068,92_x000D_
+• Valor em ruptura: R$ 804,51_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.125,40_x000D_
+• Valor em ruptura: R$ 286,42_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.527,75_x000D_
+• Valor em ruptura: R$ 1.004,44_x000D_
+• Valor mínimo de frete: R$ 6.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 18.414,16_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 9.225,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.852,48_x000D_
+• Valor em ruptura: R$ 1.149,77_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.450,87_x000D_
+• Valor em ruptura: R$ 71,37_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.357,76_x000D_
+• Valor em ruptura: R$ 2.112,75_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.165,09_x000D_
+• Valor em ruptura: R$ 89,53_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.344,81_x000D_
+• Valor em ruptura: R$ 82,66_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.762,64_x000D_
+• Valor em ruptura: R$ 785,80_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.550,48_x000D_
+• Valor em ruptura: R$ 38,58_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 15.382,29_x000D_
+• Valor em ruptura: R$ 7.525,98_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.241,23_x000D_
+• Valor em ruptura: R$ 3.762,99_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 64.407,33_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 7.325,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.029,49_x000D_
+• Valor em ruptura: R$ 496,71_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.533,60_x000D_
+• Valor em ruptura: R$ 169,95_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.790,30_x000D_
+• Valor em ruptura: R$ 250,87_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.268,72_x000D_
+• Valor em ruptura: R$ 743,18_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.349,30_x000D_
+• Valor em ruptura: R$ 5.076,03_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.646,09_x000D_
+• Valor em ruptura: R$ 672,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.595,24_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.572,36_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.780,72_x000D_
+• Valor em ruptura: R$ 752,93_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.652,38_x000D_
+• Valor em ruptura: R$ 2.257,79_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 411,58_x000D_
+• Valor em ruptura: R$ 4.766,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.556,82_x000D_
+• Valor em ruptura: R$ 3.703,70_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 3.792,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.304,54_x000D_
+• Valor em ruptura: R$ 358,17_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.850,80_x000D_
+• Valor em ruptura: R$ 679,30_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 16.601,93_x000D_
+• Valor em ruptura: R$ 1.012,70_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 107.581,14_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.020,74_x000D_
+• Valor em ruptura: R$ 2.116,40_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.344,31_x000D_
+• Valor em ruptura: R$ 186,80_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.861,84_x000D_
+• Valor em ruptura: R$ 793,65_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 240,48_x000D_
+• Valor em ruptura: R$ 3.512,13_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.757,95_x000D_
+• Valor em ruptura: R$ 2.331,62_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.345,51_x000D_
+• Valor em ruptura: R$ 274,28_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 11.882,04_x000D_
+• Valor em ruptura: R$ 800,39_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.619,65_x000D_
+• Valor em ruptura: R$ 1.003,46_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.442,87_x000D_
+• Valor em ruptura: R$ 1.254,33_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 141,64_x000D_
+• Valor em ruptura: R$ 2.950,19_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.758,82_x000D_
+• Valor em ruptura: R$ 529,10_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.830,22_x000D_
+• Valor em ruptura: R$ 1.456,49_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 29.320,19_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 2.669,57_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 37.480,00_x000D_
+• Valor em ruptura: R$ 3.226,14_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 53.329,19_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.732,81_x000D_
+• Valor em ruptura: R$ 7.840,15_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 14.891,74_x000D_
+• Valor em ruptura: R$ 181,08_x000D_
+• Valor mínimo de frete: R$ 9.225,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.972,53_x000D_
+• Valor em ruptura: R$ 4.013,46_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 98.208,32_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.931,08_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 22.069,77_x000D_
+• Valor em ruptura: R$ 11.048,19_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 4.024,95_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 11.273,63_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1857,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E376"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -1709,10 +1885,10 @@
     </row>
     <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>856373</v>
+        <v>856811</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1723,584 +1899,584 @@
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>856468</v>
+        <v>856661</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>3076</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>856458</v>
+        <v>856781</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>1097</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>856511</v>
+        <v>856847</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>773</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>856456</v>
+        <v>856468</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>3034</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>856199</v>
+        <v>856738</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>589</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>856376</v>
+        <v>856748</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>729</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>854781</v>
+        <v>856676</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>3093</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>848783</v>
+        <v>856458</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>3075</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>853426</v>
+        <v>856511</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>3075</v>
+        <v>773</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>850631</v>
+        <v>856456</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>147</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>856565</v>
+        <v>856199</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>2026</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>854985</v>
+        <v>856376</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>2090</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>856547</v>
+        <v>854781</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>614</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>856434</v>
+        <v>848783</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>703</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>849811</v>
+        <v>853426</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>3058</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>855293</v>
+        <v>850631</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>2072</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>849918</v>
+        <v>856565</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>750</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>856191</v>
+        <v>854985</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>922</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>852593</v>
+        <v>856547</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>632</v>
+        <v>614</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>853998</v>
+        <v>856434</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>722</v>
+        <v>703</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>856550</v>
+        <v>849811</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>429</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>855692</v>
+        <v>855293</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>574</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>856570</v>
+        <v>856768</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>3029</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>853852</v>
+        <v>849918</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>773</v>
+        <v>750</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>856033</v>
+        <v>856191</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>373</v>
+        <v>922</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>854933</v>
+        <v>852593</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>983</v>
+        <v>632</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>854931</v>
+        <v>853998</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>983</v>
+        <v>722</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>855295</v>
+        <v>856550</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>377</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>854330</v>
+        <v>856800</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>281</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>855731</v>
+        <v>855692</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>1021</v>
+        <v>574</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>856447</v>
+        <v>853852</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>3093</v>
+        <v>773</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>856303</v>
+        <v>856033</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>2040</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>855480</v>
+        <v>854933</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>856089</v>
+        <v>854931</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>856122</v>
+        <v>855295</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>90</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>856130</v>
+        <v>854330</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>90</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>856452</v>
+        <v>855731</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
-        <v>90</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>856148</v>
+        <v>856447</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40">
-        <v>90</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>856172</v>
+        <v>856303</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>90</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>856150</v>
+        <v>855480</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>90</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>856157</v>
+        <v>856664</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>856161</v>
+        <v>856089</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
@@ -2309,12 +2485,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>856168</v>
+        <v>856122</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -2325,10 +2501,10 @@
     </row>
     <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>856182</v>
+        <v>856130</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -2339,10 +2515,10 @@
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>856192</v>
+        <v>856452</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -2353,10 +2529,10 @@
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>856291</v>
+        <v>856148</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -2367,10 +2543,10 @@
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>856215</v>
+        <v>856172</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
@@ -2381,10 +2557,10 @@
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>856282</v>
+        <v>856150</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -2395,10 +2571,10 @@
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>856221</v>
+        <v>856157</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -2409,315 +2585,315 @@
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>856440</v>
+        <v>856161</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>855764</v>
+        <v>856168</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>855761</v>
+        <v>856182</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>855759</v>
+        <v>856192</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>855758</v>
+        <v>856291</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>855756</v>
+        <v>856215</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>855753</v>
+        <v>856282</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>855749</v>
+        <v>856221</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>642</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>855748</v>
+        <v>856832</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>856440</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>855764</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62">
         <v>642</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>855746</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61">
+    <row r="63" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>855761</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63">
         <v>642</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>856005</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D62" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>856559</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63">
-        <v>3078</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>856437</v>
+        <v>855759</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>855666</v>
+        <v>855758</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>856500</v>
+        <v>855756</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>855896</v>
+        <v>855753</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>2084</v>
+        <v>642</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>855512</v>
+        <v>855749</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>3057</v>
+        <v>642</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>856208</v>
+        <v>855748</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>856539</v>
+        <v>855746</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>699</v>
+        <v>642</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>856008</v>
+        <v>856005</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>2051</v>
+        <v>773</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>856026</v>
+        <v>856559</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>699</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>856558</v>
+        <v>856437</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>3076</v>
+        <v>703</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>856560</v>
+        <v>855666</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>141</v>
@@ -2726,68 +2902,68 @@
         <v>5</v>
       </c>
       <c r="E74">
-        <v>3078</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>856124</v>
+        <v>856500</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>853459</v>
+        <v>856619</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>850430</v>
+        <v>855896</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>2081</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>856489</v>
+        <v>855512</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>2084</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>856520</v>
+        <v>856631</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>143</v>
@@ -2796,239 +2972,239 @@
         <v>5</v>
       </c>
       <c r="E79">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>856304</v>
+        <v>856208</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>90</v>
+        <v>699</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>856055</v>
+        <v>856821</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>856000</v>
+        <v>856809</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>855999</v>
+        <v>856813</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>855996</v>
+        <v>856643</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>856555</v>
+        <v>856539</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>564</v>
+        <v>699</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>855650</v>
+        <v>856026</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>916</v>
+        <v>699</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>856531</v>
+        <v>856558</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>854263</v>
+        <v>856739</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>574</v>
+        <v>614</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>855699</v>
+        <v>856886</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>429</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>856438</v>
+        <v>856560</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>3093</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>855426</v>
+        <v>853459</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>855506</v>
+        <v>850430</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>856421</v>
+        <v>856690</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>829</v>
+        <v>703</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>856189</v>
+        <v>856489</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>699</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>856453</v>
+        <v>856777</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>699</v>
+        <v>722</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>856003</v>
+        <v>856520</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
@@ -3039,2622 +3215,2800 @@
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>856306</v>
+        <v>856633</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>856287</v>
+        <v>856637</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>856011</v>
+        <v>856304</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>855496</v>
+        <v>856883</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>856450</v>
+        <v>856866</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>867</v>
+        <v>90</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>856179</v>
+        <v>856531</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>2051</v>
+        <v>699</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>856177</v>
+        <v>855699</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>294</v>
+        <v>429</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>853358</v>
+        <v>856438</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>855468</v>
+        <v>856797</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>855660</v>
+        <v>856759</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>703</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>855001</v>
+        <v>856796</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>874</v>
+        <v>294</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>855887</v>
+        <v>856804</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>3060</v>
+        <v>574</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>856470</v>
+        <v>855426</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109">
-        <v>951</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>856023</v>
+        <v>855506</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>3034</v>
+        <v>569</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>856210</v>
+        <v>856421</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>856198</v>
+        <v>856189</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>856090</v>
+        <v>856453</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>851354</v>
+        <v>856306</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>60</v>
+        <v>653</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>851356</v>
+        <v>856287</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>851357</v>
+        <v>856624</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>854953</v>
+        <v>856620</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>854954</v>
+        <v>856011</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>851359</v>
+        <v>855496</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>854955</v>
+        <v>856450</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>854956</v>
+        <v>856594</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>60</v>
+        <v>703</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>844931</v>
+        <v>856179</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>851348</v>
+        <v>856812</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>851349</v>
+        <v>856694</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>854602</v>
+        <v>853358</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855254</v>
+        <v>855468</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>855272</v>
+        <v>856860</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>906</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>855271</v>
+        <v>855660</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>855438</v>
+        <v>855887</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>856530</v>
+        <v>856470</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>855494</v>
+        <v>856853</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>856405</v>
+        <v>856651</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>854939</v>
+        <v>856814</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>1807</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>856486</v>
+        <v>856210</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>856162</v>
+        <v>856657</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>2047</v>
+        <v>874</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>855297</v>
+        <v>856859</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>381</v>
+        <v>564</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>854777</v>
+        <v>856611</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>856533</v>
+        <v>856641</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>856123</v>
+        <v>851354</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>996</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>856471</v>
+        <v>851356</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140">
-        <v>3081</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>856010</v>
+        <v>851357</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>3081</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>856018</v>
+        <v>854953</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>856378</v>
+        <v>854954</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>293</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>855278</v>
+        <v>851359</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>293</v>
+        <v>60</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>855935</v>
+        <v>854955</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>2047</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>853734</v>
+        <v>854956</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>853738</v>
+        <v>844931</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>852720</v>
+        <v>851348</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>855583</v>
+        <v>851349</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>778</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>855990</v>
+        <v>854602</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>979</v>
+        <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>855374</v>
+        <v>856692</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>293</v>
+        <v>375</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>855636</v>
+        <v>855254</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>851</v>
+        <v>906</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>856021</v>
+        <v>855272</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>854925</v>
+        <v>855271</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>856187</v>
+        <v>855494</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>293</v>
+        <v>979</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>848786</v>
+        <v>856405</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>854939</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D157" t="s">
+        <v>5</v>
+      </c>
+      <c r="E157">
         <v>1807</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A157">
-        <v>856367</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D157" t="s">
-        <v>5</v>
-      </c>
-      <c r="E157">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>856466</v>
+        <v>856663</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>293</v>
+        <v>118</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>856515</v>
+        <v>856486</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>966</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>855815</v>
+        <v>856162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>1807</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>854839</v>
+        <v>855297</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>60</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>856299</v>
+        <v>856584</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>60</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>856301</v>
+        <v>854777</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>855782</v>
+        <v>856471</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>3069</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>856406</v>
+        <v>856010</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>968</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>854835</v>
+        <v>856018</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>851</v>
+        <v>375</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>856372</v>
+        <v>856868</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>293</v>
+        <v>749</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A168">
+        <v>853734</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D168" t="s">
+        <v>5</v>
+      </c>
+      <c r="E168">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>853738</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D169" t="s">
+        <v>5</v>
+      </c>
+      <c r="E169">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>852720</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D170" t="s">
+        <v>5</v>
+      </c>
+      <c r="E170">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>855583</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D171" t="s">
+        <v>5</v>
+      </c>
+      <c r="E171">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>856415</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" t="s">
+        <v>5</v>
+      </c>
+      <c r="E172">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>856021</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>856697</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>848786</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D175" t="s">
+        <v>5</v>
+      </c>
+      <c r="E175">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>853703</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D176" t="s">
+        <v>5</v>
+      </c>
+      <c r="E176">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>856466</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D177" t="s">
+        <v>5</v>
+      </c>
+      <c r="E177">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>856823</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D178" t="s">
+        <v>5</v>
+      </c>
+      <c r="E178">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>854839</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="E179">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>856299</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D180" t="s">
+        <v>5</v>
+      </c>
+      <c r="E180">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>856301</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D181" t="s">
+        <v>5</v>
+      </c>
+      <c r="E181">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>855782</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D182" t="s">
+        <v>5</v>
+      </c>
+      <c r="E182">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>856406</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D183" t="s">
+        <v>5</v>
+      </c>
+      <c r="E183">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>854835</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D184" t="s">
+        <v>5</v>
+      </c>
+      <c r="E184">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>856737</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D185" t="s">
+        <v>5</v>
+      </c>
+      <c r="E185">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>856372</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D186" t="s">
+        <v>5</v>
+      </c>
+      <c r="E186">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>856721</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D187" t="s">
+        <v>5</v>
+      </c>
+      <c r="E187">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A188">
         <v>855906</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D168" t="s">
-        <v>5</v>
-      </c>
-      <c r="E168">
+      <c r="B188" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D188" t="s">
+        <v>5</v>
+      </c>
+      <c r="E188">
         <v>293</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A169">
+    <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A189">
         <v>855847</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D169" t="s">
-        <v>5</v>
-      </c>
-      <c r="E169">
+      <c r="B189" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D189" t="s">
+        <v>5</v>
+      </c>
+      <c r="E189">
         <v>2024</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>852886</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D170" t="s">
-        <v>5</v>
-      </c>
-      <c r="E170">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171">
-        <v>856414</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172">
-        <v>856427</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190">
         <v>856383</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174">
+      <c r="B190" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191">
         <v>856390</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175">
+      <c r="B191" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192">
         <v>856377</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>856401</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>855903</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178">
-        <v>856522</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179">
-        <v>856449</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180">
-        <v>856472</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181">
-        <v>856465</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182">
-        <v>856507</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183">
-        <v>856491</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184">
-        <v>856469</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185">
-        <v>850108</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186">
-        <v>850002</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187">
-        <v>851031</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>856420</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189">
-        <v>856506</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>853850</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>853854</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192">
-        <v>853853</v>
-      </c>
       <c r="B192" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>856394</v>
+        <v>856401</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>856246</v>
+        <v>855903</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>856274</v>
+        <v>856605</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>856347</v>
+        <v>856607</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>856339</v>
+        <v>856522</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>856330</v>
+        <v>856449</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>856340</v>
+        <v>856472</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>856279</v>
+        <v>856465</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>856230</v>
+        <v>856507</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>856242</v>
+        <v>856491</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>856273</v>
+        <v>856469</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>856355</v>
+        <v>856484</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>856327</v>
+        <v>850108</v>
       </c>
       <c r="B205" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>856256</v>
+        <v>851031</v>
       </c>
       <c r="B206" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>856234</v>
+        <v>856570</v>
       </c>
       <c r="B207" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>856354</v>
+        <v>853850</v>
       </c>
       <c r="B208" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>856253</v>
+        <v>853854</v>
       </c>
       <c r="B209" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>856229</v>
+        <v>853853</v>
       </c>
       <c r="B210" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>856243</v>
+        <v>856394</v>
       </c>
       <c r="B211" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>856275</v>
+        <v>856246</v>
       </c>
       <c r="B212" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>856252</v>
+        <v>856274</v>
       </c>
       <c r="B213" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>856272</v>
+        <v>856347</v>
       </c>
       <c r="B214" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>856268</v>
+        <v>856339</v>
       </c>
       <c r="B215" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>856265</v>
+        <v>856330</v>
       </c>
       <c r="B216" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>855785</v>
+        <v>856340</v>
       </c>
       <c r="B217" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>856451</v>
+        <v>856279</v>
       </c>
       <c r="B218" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>856423</v>
+        <v>856230</v>
       </c>
       <c r="B219" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>848673</v>
+        <v>856242</v>
       </c>
       <c r="B220" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>854385</v>
+        <v>856273</v>
       </c>
       <c r="B221" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>855246</v>
+        <v>856355</v>
       </c>
       <c r="B222" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>854940</v>
+        <v>856327</v>
       </c>
       <c r="B223" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>849969</v>
+        <v>856256</v>
       </c>
       <c r="B224" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>856328</v>
+        <v>856234</v>
       </c>
       <c r="B225" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>856277</v>
+        <v>856354</v>
       </c>
       <c r="B226" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>856278</v>
+        <v>856253</v>
       </c>
       <c r="B227" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>856318</v>
+        <v>856229</v>
       </c>
       <c r="B228" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>856324</v>
+        <v>856243</v>
       </c>
       <c r="B229" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>856276</v>
+        <v>856275</v>
       </c>
       <c r="B230" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>856357</v>
+        <v>856252</v>
       </c>
       <c r="B231" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>856257</v>
+        <v>856272</v>
       </c>
       <c r="B232" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>856238</v>
+        <v>856268</v>
       </c>
       <c r="B233" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>856232</v>
+        <v>856265</v>
       </c>
       <c r="B234" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>856241</v>
+        <v>855785</v>
       </c>
       <c r="B235" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>856326</v>
+        <v>856451</v>
       </c>
       <c r="B236" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>856258</v>
+        <v>856693</v>
       </c>
       <c r="B237" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>856337</v>
+        <v>856794</v>
       </c>
       <c r="B238" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>856255</v>
+        <v>856730</v>
       </c>
       <c r="B239" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>856338</v>
+        <v>848673</v>
       </c>
       <c r="B240" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>856233</v>
+        <v>856744</v>
       </c>
       <c r="B241" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>856317</v>
+        <v>856627</v>
       </c>
       <c r="B242" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>856321</v>
+        <v>854940</v>
       </c>
       <c r="B243" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>856263</v>
+        <v>849969</v>
       </c>
       <c r="B244" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>856346</v>
+        <v>856328</v>
       </c>
       <c r="B245" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>856237</v>
+        <v>856277</v>
       </c>
       <c r="B246" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>856319</v>
+        <v>856278</v>
       </c>
       <c r="B247" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>856333</v>
+        <v>856318</v>
       </c>
       <c r="B248" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>856240</v>
+        <v>856324</v>
       </c>
       <c r="B249" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>856259</v>
+        <v>856276</v>
       </c>
       <c r="B250" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>856336</v>
+        <v>856357</v>
       </c>
       <c r="B251" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>856335</v>
+        <v>856257</v>
       </c>
       <c r="B252" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>856270</v>
+        <v>856585</v>
       </c>
       <c r="B253" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>856351</v>
+        <v>856238</v>
       </c>
       <c r="B254" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>856235</v>
+        <v>856232</v>
       </c>
       <c r="B255" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>856315</v>
+        <v>856241</v>
       </c>
       <c r="B256" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>856316</v>
+        <v>856326</v>
       </c>
       <c r="B257" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>856269</v>
+        <v>856258</v>
       </c>
       <c r="B258" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>856353</v>
+        <v>856337</v>
       </c>
       <c r="B259" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>856271</v>
+        <v>856255</v>
       </c>
       <c r="B260" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>856341</v>
+        <v>856338</v>
       </c>
       <c r="B261" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>856266</v>
+        <v>856233</v>
       </c>
       <c r="B262" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>856358</v>
+        <v>856317</v>
       </c>
       <c r="B263" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>856323</v>
+        <v>856321</v>
       </c>
       <c r="B264" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>856322</v>
+        <v>856263</v>
       </c>
       <c r="B265" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>856352</v>
+        <v>856346</v>
       </c>
       <c r="B266" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>856342</v>
+        <v>856237</v>
       </c>
       <c r="B267" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>856325</v>
+        <v>856319</v>
       </c>
       <c r="B268" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>856334</v>
+        <v>856333</v>
       </c>
       <c r="B269" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>856350</v>
+        <v>856240</v>
       </c>
       <c r="B270" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>856359</v>
+        <v>856259</v>
       </c>
       <c r="B271" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>856348</v>
+        <v>856336</v>
       </c>
       <c r="B272" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>856236</v>
+        <v>856335</v>
       </c>
       <c r="B273" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>856320</v>
+        <v>856270</v>
       </c>
       <c r="B274" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>856349</v>
+        <v>856351</v>
       </c>
       <c r="B275" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>856267</v>
+        <v>856235</v>
       </c>
       <c r="B276" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>856356</v>
+        <v>856315</v>
       </c>
       <c r="B277" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>849444</v>
+        <v>856316</v>
       </c>
       <c r="B278" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>856397</v>
+        <v>856269</v>
       </c>
       <c r="B279" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>856386</v>
+        <v>856353</v>
       </c>
       <c r="B280" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>856392</v>
+        <v>856271</v>
       </c>
       <c r="B281" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>851751</v>
+        <v>856341</v>
       </c>
       <c r="B282" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>849662</v>
+        <v>856266</v>
       </c>
       <c r="B283" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>853691</v>
+        <v>856358</v>
       </c>
       <c r="B284" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>849622</v>
+        <v>856323</v>
       </c>
       <c r="B285" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>849563</v>
+        <v>856322</v>
       </c>
       <c r="B286" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>855289</v>
+        <v>856352</v>
       </c>
       <c r="B287" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>854288</v>
+        <v>856342</v>
       </c>
       <c r="B288" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>854260</v>
+        <v>856325</v>
       </c>
       <c r="B289" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>854255</v>
+        <v>856334</v>
       </c>
       <c r="B290" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>856448</v>
+        <v>856350</v>
       </c>
       <c r="B291" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>856509</v>
+        <v>856359</v>
       </c>
       <c r="B292" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>854272</v>
+        <v>856593</v>
       </c>
       <c r="B293" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>855766</v>
+        <v>856348</v>
       </c>
       <c r="B294" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>849613</v>
+        <v>856236</v>
       </c>
       <c r="B295" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>849183</v>
+        <v>856320</v>
       </c>
       <c r="B296" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>849750</v>
+        <v>856349</v>
       </c>
       <c r="B297" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>849603</v>
+        <v>856267</v>
       </c>
       <c r="B298" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>852382</v>
+        <v>856356</v>
       </c>
       <c r="B299" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>849376</v>
+        <v>849444</v>
       </c>
       <c r="B300" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>849832</v>
+        <v>856397</v>
       </c>
       <c r="B301" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>849559</v>
+        <v>856386</v>
       </c>
       <c r="B302" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>856064</v>
+        <v>856392</v>
       </c>
       <c r="B303" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>849847</v>
+        <v>851751</v>
       </c>
       <c r="B304" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>849636</v>
+        <v>849662</v>
       </c>
       <c r="B305" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>855807</v>
+        <v>853691</v>
       </c>
       <c r="B306" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>849652</v>
+        <v>849622</v>
       </c>
       <c r="B307" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>849913</v>
+        <v>849563</v>
       </c>
       <c r="B308" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>855654</v>
+        <v>855289</v>
       </c>
       <c r="B309" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>856499</v>
+        <v>856642</v>
       </c>
       <c r="B310" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>849940</v>
+        <v>854260</v>
       </c>
       <c r="B311" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>856312</v>
+        <v>856454</v>
       </c>
       <c r="B312" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>849567</v>
+        <v>854255</v>
       </c>
       <c r="B313" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>849780</v>
+        <v>856448</v>
       </c>
       <c r="B314" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>849773</v>
+        <v>856509</v>
       </c>
       <c r="B315" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>849792</v>
+        <v>854272</v>
       </c>
       <c r="B316" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>849812</v>
+        <v>849613</v>
       </c>
       <c r="B317" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>849639</v>
+        <v>849183</v>
       </c>
       <c r="B318" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>853427</v>
+        <v>849750</v>
       </c>
       <c r="B319" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>853538</v>
+        <v>849603</v>
       </c>
       <c r="B320" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>849821</v>
+        <v>852382</v>
       </c>
       <c r="B321" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>854060</v>
+        <v>849376</v>
       </c>
       <c r="B322" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>853428</v>
+        <v>856815</v>
       </c>
       <c r="B323" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>855697</v>
+        <v>849832</v>
       </c>
       <c r="B324" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>855890</v>
+        <v>849559</v>
       </c>
       <c r="B325" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>853773</v>
+        <v>856064</v>
       </c>
       <c r="B326" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>856496</v>
+        <v>849847</v>
       </c>
       <c r="B327" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>856418</v>
+        <v>849636</v>
       </c>
       <c r="B328" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>856202</v>
+        <v>849652</v>
       </c>
       <c r="B329" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>856546</v>
+        <v>849913</v>
       </c>
       <c r="B330" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>856413</v>
+        <v>855654</v>
       </c>
       <c r="B331" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>856526</v>
+        <v>856499</v>
       </c>
       <c r="B332" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>856431</v>
+        <v>849940</v>
       </c>
       <c r="B333" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>856564</v>
+        <v>856312</v>
       </c>
       <c r="B334" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>855929</v>
+        <v>849567</v>
       </c>
       <c r="B335" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>856424</v>
+        <v>849780</v>
       </c>
       <c r="B336" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>856552</v>
+        <v>849773</v>
       </c>
       <c r="B337" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>856366</v>
+        <v>849792</v>
       </c>
       <c r="B338" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>855461</v>
+        <v>849812</v>
       </c>
       <c r="B339" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>855678</v>
+        <v>849821</v>
       </c>
       <c r="B340" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>856481</v>
+        <v>854060</v>
       </c>
       <c r="B341" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>855079</v>
+        <v>856851</v>
       </c>
       <c r="B342" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>855914</v>
+        <v>856791</v>
       </c>
       <c r="B343" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>856296</v>
+        <v>856884</v>
       </c>
       <c r="B344" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>855640</v>
+        <v>856639</v>
       </c>
       <c r="B345" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>855642</v>
+        <v>856840</v>
       </c>
       <c r="B346" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>856074</v>
+        <v>853773</v>
       </c>
       <c r="B347" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>855257</v>
+        <v>856575</v>
       </c>
       <c r="B348" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>855436</v>
+        <v>856818</v>
       </c>
       <c r="B349" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>855822</v>
+        <v>856871</v>
       </c>
       <c r="B350" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>856441</v>
+        <v>856685</v>
       </c>
       <c r="B351" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>856364</v>
+        <v>856655</v>
       </c>
       <c r="B352" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>856562</v>
+        <v>855461</v>
       </c>
       <c r="B353" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>855703</v>
+        <v>856807</v>
       </c>
       <c r="B354" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>856516</v>
+        <v>856861</v>
       </c>
       <c r="B355" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>856417</v>
+        <v>856658</v>
       </c>
       <c r="B356" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>855518</v>
+        <v>856849</v>
       </c>
       <c r="B357" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>856226</v>
+        <v>856609</v>
       </c>
       <c r="B358" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>856363</v>
+        <v>855640</v>
       </c>
       <c r="B359" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>855781</v>
+        <v>855642</v>
       </c>
       <c r="B360" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>855858</v>
+        <v>856784</v>
       </c>
       <c r="B361" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>855933</v>
+        <v>856839</v>
       </c>
       <c r="B362" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>856369</v>
+        <v>856680</v>
       </c>
       <c r="B363" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>856521</v>
+        <v>856873</v>
       </c>
       <c r="B364" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>855708</v>
+        <v>856727</v>
       </c>
       <c r="B365" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>856087</v>
+        <v>856723</v>
       </c>
       <c r="B366" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>856077</v>
+        <v>856790</v>
       </c>
       <c r="B367" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368">
+        <v>856612</v>
+      </c>
+      <c r="B368" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>856795</v>
+      </c>
+      <c r="B369" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>856516</v>
+      </c>
+      <c r="B370" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>855518</v>
+      </c>
+      <c r="B371" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>856793</v>
+      </c>
+      <c r="B372" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>856698</v>
+      </c>
+      <c r="B373" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>856656</v>
+      </c>
+      <c r="B374" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>856087</v>
+      </c>
+      <c r="B375" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376">
         <v>856428</v>
       </c>
-      <c r="B368" t="s">
-        <v>47</v>
+      <c r="B376" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Ação.xlsx
+++ b/Ação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{084C9A86-E875-4BE2-B237-F76BDDBC1122}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{14687F51-C3B4-45CC-87DD-84C072187371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33CF93BD-ED71-4232-B15D-8B7A90470C14}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{25504561-8B24-4A04-B0A2-C6234687AA31}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="174">
   <si>
     <t>Pedido</t>
   </si>
@@ -74,14 +74,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 180,45_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
@@ -100,14 +92,6 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 237,46_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 146,14_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
@@ -134,14 +118,6 @@
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.394,93_x000D_
-• Valor em ruptura: R$ 1.881,50_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -154,14 +130,6 @@
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 31.786,92_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 63.573,84_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
@@ -278,14 +246,6 @@
 • Valor mínimo de frete: R$ 300,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 275.948,41_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -356,14 +316,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.731,80_x000D_
-• Valor em ruptura: R$ 424,75_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.178,85_x000D_
 • Valor em ruptura: R$ 188,35_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -377,14 +329,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.098,78_x000D_
-• Valor em ruptura: R$ 249,32_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -393,14 +337,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 965,31_x000D_
-• Valor em ruptura: R$ 13.017,23_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -457,14 +393,6 @@
 • Valor mínimo de frete: R$ 7.175,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.812,61_x000D_
-• Valor em ruptura: R$ 394,53_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -540,14 +468,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.476,60_x000D_
-• Valor em ruptura: R$ 3.010,39_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.768,09_x000D_
 • Valor em ruptura: R$ 169,95_x000D_
 • Valor mínimo de frete: R$ 5.150,00</t>
@@ -585,94 +505,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.366,25_x000D_
-• Valor em ruptura: R$ 3.661,18_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.696,17_x000D_
-• Valor em ruptura: R$ 1.507,54_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.274,73_x000D_
-• Valor em ruptura: R$ 3.015,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.467,62_x000D_
-• Valor em ruptura: R$ 9.906,72_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.416,18_x000D_
-• Valor em ruptura: R$ 6.891,63_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.380,71_x000D_
-• Valor em ruptura: R$ 2.584,36_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.839,07_x000D_
-• Valor em ruptura: R$ 646,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.449,78_x000D_
-• Valor em ruptura: R$ 3.512,13_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.629,78_x000D_
-• Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 638,33_x000D_
-• Valor em ruptura: R$ 1.851,85_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.455,54_x000D_
-• Valor em ruptura: R$ 1.012,70_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -684,14 +516,6 @@
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 764,20_x000D_
-• Valor em ruptura: R$ 5.017,32_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 19.666,50_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -761,78 +585,6 @@
 • Valor mínimo de frete: R$ 5.150,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.034,02_x000D_
-• Valor em ruptura: R$ 3.445,82_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.223,48_x000D_
-• Valor em ruptura: R$ 1.722,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 11.905,22_x000D_
-• Valor em ruptura: R$ 8.614,54_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.729,32_x000D_
-• Valor em ruptura: R$ 2.799,73_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.973,39_x000D_
-• Valor em ruptura: R$ 3.015,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.625,25_x000D_
-• Valor em ruptura: R$ 2.584,36_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.939,62_x000D_
-• Valor em ruptura: R$ 861,45_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.462,99_x000D_
-• Valor em ruptura: R$ 3.015,09_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.271,73_x000D_
-• Valor em ruptura: R$ 2.369,00_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -841,46 +593,6 @@
 • Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.769,04_x000D_
-• Valor em ruptura: R$ 250,87_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.297,94_x000D_
-• Valor em ruptura: R$ 2.508,66_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.504,06_x000D_
-• Valor em ruptura: R$ 506,35_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 8.745,68_x000D_
-• Valor em ruptura: R$ 13.546,77_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.908,34_x000D_
-• Valor em ruptura: R$ 3.174,60_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -889,62 +601,6 @@
 • Valor mínimo de frete: R$ 4.075,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.660,96_x000D_
-• Valor em ruptura: R$ 4.449,86_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.389,94_x000D_
-• Valor em ruptura: R$ 2.383,23_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.316,01_x000D_
-• Valor em ruptura: R$ 506,35_x000D_
-• Valor mínimo de frete: R$ 7.175,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 11.423,28_x000D_
-• Valor em ruptura: R$ 1.770,98_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.458,05_x000D_
-• Valor em ruptura: R$ 1.851,85_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 552,39_x000D_
-• Valor em ruptura: R$ 1.986,86_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 25.879,72_x000D_
-• Valor em ruptura: R$ 1.770,11_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1004,14 +660,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.720,72_x000D_
-• Valor em ruptura: R$ 999,20_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 11.762,18_x000D_
 • Valor em ruptura: R$ 501,70_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -1020,22 +668,6 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.668,24_x000D_
-• Valor em ruptura: R$ 4.370,46_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.068,92_x000D_
-• Valor em ruptura: R$ 804,51_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.125,40_x000D_
 • Valor em ruptura: R$ 286,42_x000D_
 • Valor mínimo de frete: R$ 5.200,00</t>
@@ -1052,14 +684,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 18.414,16_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 9.225,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.852,48_x000D_
 • Valor em ruptura: R$ 1.149,77_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
@@ -1068,22 +692,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 7.450,87_x000D_
-• Valor em ruptura: R$ 71,37_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.357,76_x000D_
-• Valor em ruptura: R$ 2.112,75_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 4.165,09_x000D_
 • Valor em ruptura: R$ 89,53_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
@@ -1097,46 +705,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 5.150,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.762,64_x000D_
-• Valor em ruptura: R$ 785,80_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.550,48_x000D_
-• Valor em ruptura: R$ 38,58_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 15.382,29_x000D_
-• Valor em ruptura: R$ 7.525,98_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.241,23_x000D_
-• Valor em ruptura: R$ 3.762,99_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1148,14 +716,6 @@
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 6.029,49_x000D_
-• Valor em ruptura: R$ 496,71_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 6.533,60_x000D_
 • Valor em ruptura: R$ 169,95_x000D_
 • Valor mínimo de frete: R$ 4.075,00</t>
@@ -1164,41 +724,9 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.790,30_x000D_
-• Valor em ruptura: R$ 250,87_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.268,72_x000D_
-• Valor em ruptura: R$ 743,18_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.349,30_x000D_
-• Valor em ruptura: R$ 5.076,03_x000D_
-• Valor mínimo de frete: R$ 4.075,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 1.646,09_x000D_
 • Valor em ruptura: R$ 672,91_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 7.595,24_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
@@ -1217,38 +745,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.652,38_x000D_
-• Valor em ruptura: R$ 2.257,79_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 411,58_x000D_
-• Valor em ruptura: R$ 4.766,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.556,82_x000D_
-• Valor em ruptura: R$ 3.703,70_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 3.792,91_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1265,14 +761,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 16.601,93_x000D_
-• Valor em ruptura: R$ 1.012,70_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1284,88 +772,16 @@
     <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
 _x000D_
 Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.020,74_x000D_
-• Valor em ruptura: R$ 2.116,40_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
 • Valor em estoque: R$ 2.344,31_x000D_
 • Valor em ruptura: R$ 186,80_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.861,84_x000D_
-• Valor em ruptura: R$ 793,65_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 240,48_x000D_
-• Valor em ruptura: R$ 3.512,13_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 3.757,95_x000D_
 • Valor em ruptura: R$ 2.331,62_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 5.345,51_x000D_
-• Valor em ruptura: R$ 274,28_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 11.882,04_x000D_
-• Valor em ruptura: R$ 800,39_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.619,65_x000D_
-• Valor em ruptura: R$ 1.003,46_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 1.442,87_x000D_
-• Valor em ruptura: R$ 1.254,33_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 141,64_x000D_
-• Valor em ruptura: R$ 2.950,19_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 2.758,82_x000D_
-• Valor em ruptura: R$ 529,10_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
   </si>
   <si>
@@ -1377,22 +793,6 @@
 • Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 29.320,19_x000D_
-• Valor mínimo de frete: R$ 5.200,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 0,00_x000D_
-• Valor em ruptura: R$ 2.669,57_x000D_
-• Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
 _x000D_
 Resumo financeiro:_x000D_
@@ -1425,28 +825,12 @@
 • Valor mínimo de frete: R$ 9.225,00</t>
   </si>
   <si>
-    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 4.972,53_x000D_
-• Valor em ruptura: R$ 4.013,46_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
-  </si>
-  <si>
     <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
 _x000D_
 Resumo financeiro:_x000D_
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 98.208,32_x000D_
 • Valor mínimo de frete: R$ 3.125,00</t>
-  </si>
-  <si>
-    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
-_x000D_
-Resumo financeiro:_x000D_
-• Valor em estoque: R$ 3.931,08_x000D_
-• Valor em ruptura: R$ 0,00_x000D_
-• Valor mínimo de frete: R$ 4.100,00</t>
   </si>
   <si>
     <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
@@ -1471,6 +855,550 @@
 • Valor em estoque: R$ 0,00_x000D_
 • Valor em ruptura: R$ 11.273,63_x000D_
 • Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 20.142,24_x000D_
+• Valor em ruptura: R$ 11.023,58_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.909,81_x000D_
+• Valor em ruptura: R$ 1.385,79_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.400,02_x000D_
+• Valor em ruptura: R$ 630,44_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.921,99_x000D_
+• Valor em ruptura: R$ 595,13_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.002,28_x000D_
+• Valor em ruptura: R$ 693,67_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.151,74_x000D_
+• Valor em ruptura: R$ 286,42_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.222,45_x000D_
+• Valor em ruptura: R$ 497,47_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.067,82_x000D_
+• Valor em ruptura: R$ 286,13_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.465,86_x000D_
+• Valor em ruptura: R$ 572,84_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.075,24_x000D_
+• Valor em ruptura: R$ 804,51_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.435,39_x000D_
+• Valor em ruptura: R$ 211,26_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.871,90_x000D_
+• Valor em ruptura: R$ 5.115,99_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.450,87_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.383,16_x000D_
+• Valor em ruptura: R$ 87,35_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.253,70_x000D_
+• Valor em ruptura: R$ 77,86_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.412,36_x000D_
+• Valor em ruptura: R$ 769,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 51.009,03_x000D_
+• Valor em ruptura: R$ 138,96_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 27.307,25_x000D_
+• Valor em ruptura: R$ 4.763,04_x000D_
+• Valor mínimo de frete: R$ 6.250,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.425,97_x000D_
+• Valor em ruptura: R$ 1.122,47_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.812,61_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 29.682,05_x000D_
+• Valor em ruptura: R$ 1.289,86_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.608,11_x000D_
+• Valor em ruptura: R$ 1.336,18_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.402,38_x000D_
+• Valor em ruptura: R$ 1.969,96_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.534,47_x000D_
+• Valor em ruptura: R$ 7.749,87_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 10.418,39_x000D_
+• Valor em ruptura: R$ 336,85_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.978,94_x000D_
+• Valor em ruptura: R$ 177,61_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.843,64_x000D_
+• Valor em ruptura: R$ 336,45_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.855,36_x000D_
+• Valor em ruptura: R$ 970,24_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.629,85_x000D_
+• Valor em ruptura: R$ 1.419,22_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.920,79_x000D_
+• Valor em ruptura: R$ 1.698,28_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.387,40_x000D_
+• Valor em ruptura: R$ 2.037,93_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.833,99_x000D_
+• Valor em ruptura: R$ 2.037,93_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.457,16_x000D_
+• Valor em ruptura: R$ 2.037,93_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.199,11_x000D_
+• Valor em ruptura: R$ 673,92_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.279,07_x000D_
+• Valor em ruptura: R$ 2.705,13_x000D_
+• Valor mínimo de frete: R$ 300,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.620,75_x000D_
+• Valor em ruptura: R$ 749,50_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.609,14_x000D_
+• Valor em ruptura: R$ 1.682,26_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.293,46_x000D_
+• Valor em ruptura: R$ 336,45_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 60.402,48_x000D_
+• Valor em ruptura: R$ 5.383,25_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.168,26_x000D_
+• Valor em ruptura: R$ 672,91_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 69.325,03_x000D_
+• Valor em ruptura: R$ 15.005,49_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.235,85_x000D_
+• Valor em ruptura: R$ 1.119,47_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 12.776,56_x000D_
+• Valor em ruptura: R$ 22.880,06_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.202,93_x000D_
+• Valor em ruptura: R$ 169,95_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 2.799,85_x000D_
+• Valor em ruptura: R$ 1.476,29_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 8.715,16_x000D_
+• Valor em ruptura: R$ 339,91_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 61.554,36_x000D_
+• Valor em ruptura: R$ 704,53_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 18.795,52_x000D_
+• Valor em ruptura: R$ 453,30_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.037,60_x000D_
+• Valor em ruptura: R$ 339,44_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 15.745,57_x000D_
+• Valor em ruptura: R$ 2.134,65_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.949,72_x000D_
+• Valor em ruptura: R$ 294,80_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.822,88_x000D_
+• Valor em ruptura: R$ 261,24_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.688,24_x000D_
+• Valor em ruptura: R$ 322,67_x000D_
+• Valor mínimo de frete: R$ 5.150,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 13.733,17_x000D_
+• Valor em ruptura: R$ 4.008,55_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 6.236,07_x000D_
+• Valor em ruptura: R$ 678,87_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.722,98_x000D_
+• Valor em ruptura: R$ 679,31_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 0,00_x000D_
+• Valor mínimo de frete: R$ 4.075,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 7.777,48_x000D_
+• Valor em ruptura: R$ 1.345,81_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 1.143,09_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 4.367,07_x000D_
+• Valor em ruptura: R$ 178,16_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 3.513,53_x000D_
+• Valor em ruptura: R$ 36.866,76_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 7.625,45_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque e os itens em ruptura atendem ao valor mínimo estabelecido. Podemos prosseguir com o faturamento parcial, mantendo o saldo para faturamento futuro?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 61.190,18_x000D_
+• Valor em ruptura: R$ 26.459,47_x000D_
+• Valor mínimo de frete: R$ 4.100,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.113,98_x000D_
+• Valor em ruptura: R$ 26.950,52_x000D_
+• Valor mínimo de frete: R$ 5.200,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 11.904,13_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque atendem ao valor mínimo para faturamento parcial; entretanto, os itens em ruptura estão abaixo do mínimo. Podemos prosseguir com o faturamento parcial e cancelar o saldo remanescente?_x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 5.400,89_x000D_
+• Valor em ruptura: R$ 168,42_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>Os itens disponíveis em estoque não atingem o valor mínimo para faturamento parcial. Será necessário aguardar a entrada dos itens atualmente em ruptura._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 0,00_x000D_
+• Valor em ruptura: R$ 5.381,13_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
+  </si>
+  <si>
+    <t>O pedido não atinge o valor mínimo de faturamento, considerando tanto os itens em estoque quanto os itens em ruptura. Assim, será necessário aguardar a consolidação integral do pedido._x000D_
+_x000D_
+Resumo financeiro:_x000D_
+• Valor em estoque: R$ 1.024,20_x000D_
+• Valor em ruptura: R$ 242,74_x000D_
+• Valor mínimo de frete: R$ 3.125,00</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1785,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CE3A2-3FBD-42C4-897C-224FCCF0E0F8}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E376"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="166.7109375" customWidth="1"/>
@@ -1885,850 +1813,850 @@
     </row>
     <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>856811</v>
+        <v>857113</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>388</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>856661</v>
+        <v>857160</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>748</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>856781</v>
+        <v>857066</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>703</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>856847</v>
+        <v>856941</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>2019</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>856468</v>
+        <v>857038</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>3076</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>856738</v>
+        <v>856966</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>134</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>856748</v>
+        <v>856811</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>614</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>856676</v>
+        <v>856971</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>704</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>856458</v>
+        <v>856661</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>1097</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>856511</v>
+        <v>856781</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11">
-        <v>773</v>
+        <v>703</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>856456</v>
+        <v>857179</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>3034</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>856199</v>
+        <v>856847</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>589</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>856376</v>
+        <v>856468</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>729</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>854781</v>
+        <v>856738</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>3093</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>848783</v>
+        <v>856748</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>3075</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>853426</v>
+        <v>857079</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>3075</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>850631</v>
+        <v>856458</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>147</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>856565</v>
+        <v>856511</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>2026</v>
+        <v>773</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>854985</v>
+        <v>856456</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>2090</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>856547</v>
+        <v>856199</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>614</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>856434</v>
+        <v>856376</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>703</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>849811</v>
+        <v>857123</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>3058</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>855293</v>
+        <v>857183</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>135</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>2072</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>856768</v>
+        <v>848783</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>2055</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>849918</v>
+        <v>853426</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>750</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>856191</v>
+        <v>856954</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>922</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>852593</v>
+        <v>850631</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>632</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>853998</v>
+        <v>856565</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>722</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>856550</v>
+        <v>854985</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>429</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>856800</v>
+        <v>856547</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>3037</v>
+        <v>614</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>855692</v>
+        <v>856972</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>574</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>853852</v>
+        <v>856434</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>773</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>856033</v>
+        <v>849811</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>373</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>854933</v>
+        <v>855293</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>983</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>854931</v>
+        <v>849918</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>983</v>
+        <v>750</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>855295</v>
+        <v>856191</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>377</v>
+        <v>922</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>854330</v>
+        <v>852593</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>281</v>
+        <v>632</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>855731</v>
+        <v>856906</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
-        <v>1021</v>
+        <v>632</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>856447</v>
+        <v>857058</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40">
-        <v>3093</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>856303</v>
+        <v>857096</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>2040</v>
+        <v>574</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>855480</v>
+        <v>856550</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>3037</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>856664</v>
+        <v>856907</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>856089</v>
+        <v>855692</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>856122</v>
+        <v>853852</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>90</v>
+        <v>773</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>856130</v>
+        <v>856033</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46">
-        <v>90</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>856452</v>
+        <v>854933</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47">
-        <v>90</v>
+        <v>983</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>856148</v>
+        <v>854931</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
-        <v>90</v>
+        <v>983</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>856172</v>
+        <v>855295</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>90</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>856150</v>
+        <v>855731</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50">
-        <v>90</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>856157</v>
+        <v>856447</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
-        <v>90</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>856161</v>
+        <v>856303</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
       <c r="E52">
-        <v>90</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>856168</v>
+        <v>855480</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
       <c r="E53">
-        <v>90</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>856182</v>
+        <v>856440</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>856192</v>
+        <v>855764</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>856291</v>
+        <v>855761</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>90</v>
+        <v>642</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>856215</v>
+        <v>855759</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
-        <v>90</v>
+        <v>642</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>856282</v>
+        <v>855758</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>856221</v>
+        <v>855756</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>856832</v>
+        <v>856990</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>856440</v>
+        <v>855753</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61">
-        <v>756</v>
+        <v>642</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>855764</v>
+        <v>856988</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
@@ -2737,12 +2665,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>855761</v>
+        <v>855749</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
@@ -2751,12 +2679,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>855759</v>
+        <v>855748</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
@@ -2765,12 +2693,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>855758</v>
+        <v>855746</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
@@ -2779,460 +2707,460 @@
         <v>642</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>855756</v>
+        <v>856005</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>855753</v>
+        <v>857086</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
       <c r="E67">
-        <v>642</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>855749</v>
+        <v>855666</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>855748</v>
+        <v>857153</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>855746</v>
+        <v>856891</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>856005</v>
+        <v>856936</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="E71">
-        <v>773</v>
+        <v>951</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>856559</v>
+        <v>855896</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
-        <v>3078</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>856437</v>
+        <v>856979</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73">
-        <v>703</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>855666</v>
+        <v>855512</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74">
-        <v>388</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>856500</v>
+        <v>857026</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
-        <v>614</v>
+        <v>703</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>856619</v>
+        <v>856897</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
       <c r="E76">
-        <v>699</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>855896</v>
+        <v>857156</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77">
-        <v>2084</v>
+        <v>703</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>855512</v>
+        <v>856631</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>3057</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>856631</v>
+        <v>857072</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>856208</v>
+        <v>857054</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80">
-        <v>699</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>856821</v>
+        <v>857018</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
-        <v>2032</v>
+        <v>377</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>856809</v>
+        <v>856813</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>856813</v>
+        <v>856643</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83">
-        <v>2051</v>
+        <v>703</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>856643</v>
+        <v>856558</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
-        <v>703</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>856539</v>
+        <v>856888</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="E85">
-        <v>699</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>856026</v>
+        <v>856885</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86">
-        <v>699</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>856558</v>
+        <v>856756</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
-        <v>3076</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>856739</v>
+        <v>856886</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
       <c r="E88">
-        <v>614</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>856886</v>
+        <v>856915</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89">
-        <v>2027</v>
+        <v>983</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>856560</v>
+        <v>857109</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>853459</v>
+        <v>857106</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>850430</v>
+        <v>857111</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>856690</v>
+        <v>857101</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
-        <v>703</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>856489</v>
+        <v>856942</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>856777</v>
+        <v>853459</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>856520</v>
+        <v>850430</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
-        <v>90</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>856633</v>
+        <v>857095</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97">
-        <v>703</v>
+        <v>580</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>856637</v>
+        <v>856690</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
@@ -3243,150 +3171,150 @@
     </row>
     <row r="99" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>856304</v>
+        <v>856489</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>856883</v>
+        <v>856777</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>856866</v>
+        <v>857108</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
       </c>
       <c r="E101">
-        <v>90</v>
+        <v>703</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>856531</v>
+        <v>857084</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
-        <v>699</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>855699</v>
+        <v>856768</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103">
-        <v>429</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>856438</v>
+        <v>856926</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104">
-        <v>3093</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>856797</v>
+        <v>856976</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
-        <v>429</v>
+        <v>773</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>856759</v>
+        <v>857142</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
       <c r="E106">
-        <v>3076</v>
+        <v>836</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>856796</v>
+        <v>857145</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
       </c>
       <c r="E107">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>856804</v>
+        <v>855699</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
-        <v>574</v>
+        <v>429</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>855426</v>
+        <v>856797</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
@@ -3397,416 +3325,416 @@
     </row>
     <row r="110" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>855506</v>
+        <v>856759</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>569</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>856421</v>
+        <v>856970</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
-        <v>829</v>
+        <v>564</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>856189</v>
+        <v>857163</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>856453</v>
+        <v>856804</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113">
-        <v>699</v>
+        <v>574</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>856306</v>
+        <v>855426</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
-        <v>653</v>
+        <v>429</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>856287</v>
+        <v>857139</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115">
-        <v>699</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>856624</v>
+        <v>856306</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>856620</v>
+        <v>857170</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
-        <v>90</v>
+        <v>569</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>856011</v>
+        <v>856930</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118">
-        <v>2055</v>
+        <v>377</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>855496</v>
+        <v>856011</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119">
-        <v>811</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>856450</v>
+        <v>856594</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
-        <v>867</v>
+        <v>703</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>856594</v>
+        <v>857136</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>856179</v>
+        <v>857025</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>856812</v>
+        <v>855468</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
-        <v>3034</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>856694</v>
+        <v>857119</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124">
-        <v>829</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>853358</v>
+        <v>857089</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>855468</v>
+        <v>856983</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
-        <v>294</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>856860</v>
+        <v>856814</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>855660</v>
+        <v>856859</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>855887</v>
+        <v>857010</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>856470</v>
+        <v>851354</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130">
-        <v>951</v>
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>856853</v>
+        <v>851356</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>856651</v>
+        <v>854953</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>856814</v>
+        <v>854954</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>856210</v>
+        <v>851359</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>856657</v>
+        <v>854955</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>856859</v>
+        <v>854956</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>856611</v>
+        <v>844931</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>856641</v>
+        <v>851348</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>118</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>851354</v>
+        <v>851349</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -3815,12 +3743,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>851356</v>
+        <v>854602</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -3831,528 +3759,528 @@
     </row>
     <row r="141" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>851357</v>
+        <v>857177</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>854953</v>
+        <v>856692</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142">
-        <v>60</v>
+        <v>375</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>854954</v>
+        <v>855254</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="E143">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>851359</v>
+        <v>855272</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>854955</v>
+        <v>855271</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>60</v>
+        <v>906</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>854956</v>
+        <v>855494</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>844931</v>
+        <v>856405</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147">
-        <v>60</v>
+        <v>979</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>851348</v>
+        <v>857121</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148">
-        <v>60</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>851349</v>
+        <v>854939</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149">
-        <v>60</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>854602</v>
+        <v>856663</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150">
-        <v>60</v>
+        <v>118</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>856692</v>
+        <v>856486</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151">
-        <v>375</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>855254</v>
+        <v>856162</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>855272</v>
+        <v>855297</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153">
-        <v>906</v>
+        <v>381</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>855271</v>
+        <v>856584</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154">
-        <v>906</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>855494</v>
+        <v>854777</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>856405</v>
+        <v>856471</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156">
-        <v>979</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>854939</v>
+        <v>856010</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157">
-        <v>1807</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>856663</v>
+        <v>856018</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>856486</v>
+        <v>856887</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159">
-        <v>2047</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>856162</v>
+        <v>853738</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160">
-        <v>2047</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>855297</v>
+        <v>852720</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>856584</v>
+        <v>853734</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>854777</v>
+        <v>855583</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163">
-        <v>3</v>
+        <v>778</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>856471</v>
+        <v>856415</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164">
-        <v>3081</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>856010</v>
+        <v>856021</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165">
-        <v>3081</v>
+        <v>694</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>856018</v>
+        <v>857005</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>856868</v>
+        <v>856697</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>853734</v>
+        <v>856466</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>853738</v>
+        <v>856823</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169">
-        <v>1019</v>
+        <v>293</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>852720</v>
+        <v>857102</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170">
-        <v>1019</v>
+        <v>257</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>855583</v>
+        <v>854839</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>856415</v>
+        <v>856299</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
       </c>
       <c r="E172">
-        <v>2047</v>
+        <v>60</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>856021</v>
+        <v>856301</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>856697</v>
+        <v>855782</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174">
-        <v>257</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>848786</v>
+        <v>856406</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>853703</v>
+        <v>854835</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>856466</v>
+        <v>856737</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
       <c r="E177">
-        <v>293</v>
+        <v>979</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>856823</v>
+        <v>856372</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -4361,1654 +4289,1490 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>854839</v>
+        <v>856721</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="E179">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>856299</v>
+        <v>855906</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>856301</v>
+        <v>855847</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>855782</v>
+        <v>857103</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>40</v>
+        <v>172</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182">
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>856406</v>
+        <v>857023</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>854835</v>
+        <v>856383</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D184" t="s">
-        <v>5</v>
-      </c>
-      <c r="E184">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>856737</v>
+        <v>856390</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D185" t="s">
-        <v>5</v>
-      </c>
-      <c r="E185">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>856372</v>
+        <v>856377</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D186" t="s">
-        <v>5</v>
-      </c>
-      <c r="E186">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>856721</v>
+        <v>856401</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
-      </c>
-      <c r="E187">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>855906</v>
+        <v>855903</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D188" t="s">
-        <v>5</v>
-      </c>
-      <c r="E188">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>855847</v>
+        <v>856605</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D189" t="s">
-        <v>5</v>
-      </c>
-      <c r="E189">
-        <v>2024</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>856383</v>
+        <v>856607</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>856390</v>
+        <v>856449</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>856377</v>
+        <v>856484</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>856401</v>
+        <v>850108</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>855903</v>
+        <v>851031</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>856605</v>
+        <v>853850</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>856607</v>
+        <v>853854</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>856522</v>
+        <v>853853</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>856449</v>
+        <v>856394</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>856472</v>
+        <v>856246</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>856465</v>
+        <v>856274</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>856507</v>
+        <v>856347</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>856491</v>
+        <v>856339</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>856469</v>
+        <v>856330</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>856484</v>
+        <v>856340</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>850108</v>
+        <v>856279</v>
       </c>
       <c r="B205" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>851031</v>
+        <v>856230</v>
       </c>
       <c r="B206" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>856570</v>
+        <v>856242</v>
       </c>
       <c r="B207" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>853850</v>
+        <v>856273</v>
       </c>
       <c r="B208" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>853854</v>
+        <v>856355</v>
       </c>
       <c r="B209" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>853853</v>
+        <v>856327</v>
       </c>
       <c r="B210" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>856394</v>
+        <v>856256</v>
       </c>
       <c r="B211" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>856246</v>
+        <v>856234</v>
       </c>
       <c r="B212" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>856274</v>
+        <v>856354</v>
       </c>
       <c r="B213" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>856347</v>
+        <v>856253</v>
       </c>
       <c r="B214" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>856339</v>
+        <v>856229</v>
       </c>
       <c r="B215" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>856330</v>
+        <v>856243</v>
       </c>
       <c r="B216" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>856340</v>
+        <v>856275</v>
       </c>
       <c r="B217" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>856279</v>
+        <v>856252</v>
       </c>
       <c r="B218" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>856230</v>
+        <v>856272</v>
       </c>
       <c r="B219" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>856242</v>
+        <v>856268</v>
       </c>
       <c r="B220" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>856273</v>
+        <v>856265</v>
       </c>
       <c r="B221" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>856355</v>
+        <v>857044</v>
       </c>
       <c r="B222" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>856327</v>
+        <v>856451</v>
       </c>
       <c r="B223" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>856256</v>
+        <v>857050</v>
       </c>
       <c r="B224" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>856234</v>
+        <v>848673</v>
       </c>
       <c r="B225" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>856354</v>
+        <v>854940</v>
       </c>
       <c r="B226" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>856253</v>
+        <v>849969</v>
       </c>
       <c r="B227" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>856229</v>
+        <v>856328</v>
       </c>
       <c r="B228" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>856243</v>
+        <v>856277</v>
       </c>
       <c r="B229" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>856275</v>
+        <v>856278</v>
       </c>
       <c r="B230" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>856252</v>
+        <v>856318</v>
       </c>
       <c r="B231" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>856272</v>
+        <v>856324</v>
       </c>
       <c r="B232" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>856268</v>
+        <v>856276</v>
       </c>
       <c r="B233" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>856265</v>
+        <v>856357</v>
       </c>
       <c r="B234" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>855785</v>
+        <v>856257</v>
       </c>
       <c r="B235" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>856451</v>
+        <v>856585</v>
       </c>
       <c r="B236" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>856693</v>
+        <v>856238</v>
       </c>
       <c r="B237" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>856794</v>
+        <v>856232</v>
       </c>
       <c r="B238" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>856730</v>
+        <v>856241</v>
       </c>
       <c r="B239" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>848673</v>
+        <v>856326</v>
       </c>
       <c r="B240" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>856744</v>
+        <v>856258</v>
       </c>
       <c r="B241" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>856627</v>
+        <v>856337</v>
       </c>
       <c r="B242" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>854940</v>
+        <v>856255</v>
       </c>
       <c r="B243" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>849969</v>
+        <v>856338</v>
       </c>
       <c r="B244" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>856328</v>
+        <v>856233</v>
       </c>
       <c r="B245" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>856277</v>
+        <v>856317</v>
       </c>
       <c r="B246" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>856278</v>
+        <v>856321</v>
       </c>
       <c r="B247" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>856318</v>
+        <v>856263</v>
       </c>
       <c r="B248" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>856324</v>
+        <v>856346</v>
       </c>
       <c r="B249" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>856276</v>
+        <v>856237</v>
       </c>
       <c r="B250" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>856357</v>
+        <v>856319</v>
       </c>
       <c r="B251" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>856257</v>
+        <v>856333</v>
       </c>
       <c r="B252" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>856585</v>
+        <v>856240</v>
       </c>
       <c r="B253" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>856238</v>
+        <v>856259</v>
       </c>
       <c r="B254" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>856232</v>
+        <v>856336</v>
       </c>
       <c r="B255" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>856241</v>
+        <v>856335</v>
       </c>
       <c r="B256" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>856326</v>
+        <v>856270</v>
       </c>
       <c r="B257" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>856258</v>
+        <v>856351</v>
       </c>
       <c r="B258" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>856337</v>
+        <v>856235</v>
       </c>
       <c r="B259" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>856255</v>
+        <v>856315</v>
       </c>
       <c r="B260" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>856338</v>
+        <v>856316</v>
       </c>
       <c r="B261" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>856233</v>
+        <v>856269</v>
       </c>
       <c r="B262" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>856317</v>
+        <v>856353</v>
       </c>
       <c r="B263" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>856321</v>
+        <v>856271</v>
       </c>
       <c r="B264" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>856263</v>
+        <v>856341</v>
       </c>
       <c r="B265" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>856346</v>
+        <v>856266</v>
       </c>
       <c r="B266" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>856237</v>
+        <v>856358</v>
       </c>
       <c r="B267" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>856319</v>
+        <v>856323</v>
       </c>
       <c r="B268" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>856333</v>
+        <v>856322</v>
       </c>
       <c r="B269" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>856240</v>
+        <v>856352</v>
       </c>
       <c r="B270" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>856259</v>
+        <v>856342</v>
       </c>
       <c r="B271" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>856336</v>
+        <v>856325</v>
       </c>
       <c r="B272" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>856335</v>
+        <v>856334</v>
       </c>
       <c r="B273" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>856270</v>
+        <v>856350</v>
       </c>
       <c r="B274" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>856351</v>
+        <v>856359</v>
       </c>
       <c r="B275" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>856235</v>
+        <v>856593</v>
       </c>
       <c r="B276" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>856315</v>
+        <v>856348</v>
       </c>
       <c r="B277" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>856316</v>
+        <v>856236</v>
       </c>
       <c r="B278" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>856269</v>
+        <v>856320</v>
       </c>
       <c r="B279" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>856353</v>
+        <v>856349</v>
       </c>
       <c r="B280" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>856271</v>
+        <v>856267</v>
       </c>
       <c r="B281" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>856341</v>
+        <v>856356</v>
       </c>
       <c r="B282" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>856266</v>
+        <v>857182</v>
       </c>
       <c r="B283" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>856358</v>
+        <v>849444</v>
       </c>
       <c r="B284" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>856323</v>
+        <v>856397</v>
       </c>
       <c r="B285" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>856322</v>
+        <v>856386</v>
       </c>
       <c r="B286" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>856352</v>
+        <v>856392</v>
       </c>
       <c r="B287" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>856342</v>
+        <v>851751</v>
       </c>
       <c r="B288" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>856325</v>
+        <v>857124</v>
       </c>
       <c r="B289" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>856334</v>
+        <v>856500</v>
       </c>
       <c r="B290" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>856350</v>
+        <v>849662</v>
       </c>
       <c r="B291" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>856359</v>
+        <v>849622</v>
       </c>
       <c r="B292" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>856593</v>
+        <v>849563</v>
       </c>
       <c r="B293" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>856348</v>
+        <v>855289</v>
       </c>
       <c r="B294" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>856236</v>
+        <v>856642</v>
       </c>
       <c r="B295" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>856320</v>
+        <v>854260</v>
       </c>
       <c r="B296" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>856349</v>
+        <v>856454</v>
       </c>
       <c r="B297" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>856267</v>
+        <v>854255</v>
       </c>
       <c r="B298" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>856356</v>
+        <v>856509</v>
       </c>
       <c r="B299" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>849444</v>
+        <v>854272</v>
       </c>
       <c r="B300" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>856397</v>
+        <v>849613</v>
       </c>
       <c r="B301" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>856386</v>
+        <v>849183</v>
       </c>
       <c r="B302" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>856392</v>
+        <v>849750</v>
       </c>
       <c r="B303" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>851751</v>
+        <v>849603</v>
       </c>
       <c r="B304" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>849662</v>
+        <v>852382</v>
       </c>
       <c r="B305" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>853691</v>
+        <v>849376</v>
       </c>
       <c r="B306" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>849622</v>
+        <v>849832</v>
       </c>
       <c r="B307" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>849563</v>
+        <v>849559</v>
       </c>
       <c r="B308" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>855289</v>
+        <v>849847</v>
       </c>
       <c r="B309" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>856642</v>
+        <v>849636</v>
       </c>
       <c r="B310" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>854260</v>
+        <v>849652</v>
       </c>
       <c r="B311" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>856454</v>
+        <v>849913</v>
       </c>
       <c r="B312" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>854255</v>
+        <v>855654</v>
       </c>
       <c r="B313" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>856448</v>
+        <v>849940</v>
       </c>
       <c r="B314" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>856509</v>
+        <v>849567</v>
       </c>
       <c r="B315" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>854272</v>
+        <v>849780</v>
       </c>
       <c r="B316" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>849613</v>
+        <v>849773</v>
       </c>
       <c r="B317" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>849183</v>
+        <v>849792</v>
       </c>
       <c r="B318" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>849750</v>
+        <v>849812</v>
       </c>
       <c r="B319" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>849603</v>
+        <v>849821</v>
       </c>
       <c r="B320" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>852382</v>
+        <v>857171</v>
       </c>
       <c r="B321" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>849376</v>
+        <v>853773</v>
       </c>
       <c r="B322" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>856815</v>
+        <v>855496</v>
       </c>
       <c r="B323" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>849832</v>
+        <v>857110</v>
       </c>
       <c r="B324" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>849559</v>
+        <v>857143</v>
       </c>
       <c r="B325" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>856064</v>
+        <v>857065</v>
       </c>
       <c r="B326" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>849847</v>
+        <v>857115</v>
       </c>
       <c r="B327" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>849636</v>
+        <v>857100</v>
       </c>
       <c r="B328" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>849652</v>
+        <v>857013</v>
       </c>
       <c r="B329" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>849913</v>
+        <v>857052</v>
       </c>
       <c r="B330" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>855654</v>
+        <v>856905</v>
       </c>
       <c r="B331" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>856499</v>
+        <v>855461</v>
       </c>
       <c r="B332" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>849940</v>
+        <v>857022</v>
       </c>
       <c r="B333" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>856312</v>
+        <v>856997</v>
       </c>
       <c r="B334" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>849567</v>
+        <v>857140</v>
       </c>
       <c r="B335" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>849780</v>
+        <v>856609</v>
       </c>
       <c r="B336" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>849773</v>
+        <v>855640</v>
       </c>
       <c r="B337" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>849792</v>
+        <v>855642</v>
       </c>
       <c r="B338" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>849812</v>
+        <v>857061</v>
       </c>
       <c r="B339" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>849821</v>
+        <v>857062</v>
       </c>
       <c r="B340" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>854060</v>
+        <v>857024</v>
       </c>
       <c r="B341" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>856851</v>
+        <v>857059</v>
       </c>
       <c r="B342" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>856791</v>
+        <v>856998</v>
       </c>
       <c r="B343" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>856884</v>
+        <v>856955</v>
       </c>
       <c r="B344" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>856639</v>
+        <v>855518</v>
       </c>
       <c r="B345" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>856840</v>
+        <v>857099</v>
       </c>
       <c r="B346" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>853773</v>
+        <v>856978</v>
       </c>
       <c r="B347" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>856575</v>
+        <v>857158</v>
       </c>
       <c r="B348" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>856818</v>
+        <v>857056</v>
       </c>
       <c r="B349" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>856871</v>
+        <v>857120</v>
       </c>
       <c r="B350" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>856685</v>
+        <v>856981</v>
       </c>
       <c r="B351" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>856655</v>
+        <v>857166</v>
       </c>
       <c r="B352" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>855461</v>
+        <v>856896</v>
       </c>
       <c r="B353" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>856807</v>
+        <v>856656</v>
       </c>
       <c r="B354" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>856861</v>
+        <v>857131</v>
       </c>
       <c r="B355" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>856658</v>
+        <v>857093</v>
       </c>
       <c r="B356" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>856849</v>
+        <v>857081</v>
       </c>
       <c r="B357" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>856609</v>
+        <v>856944</v>
       </c>
       <c r="B358" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>855640</v>
+        <v>856946</v>
       </c>
       <c r="B359" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>855642</v>
+        <v>856994</v>
       </c>
       <c r="B360" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361">
-        <v>856784</v>
-      </c>
-      <c r="B361" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362">
-        <v>856839</v>
-      </c>
-      <c r="B362" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A363">
-        <v>856680</v>
-      </c>
-      <c r="B363" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A364">
-        <v>856873</v>
-      </c>
-      <c r="B364" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A365">
-        <v>856727</v>
-      </c>
-      <c r="B365" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A366">
-        <v>856723</v>
-      </c>
-      <c r="B366" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A367">
-        <v>856790</v>
-      </c>
-      <c r="B367" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A368">
-        <v>856612</v>
-      </c>
-      <c r="B368" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369">
-        <v>856795</v>
-      </c>
-      <c r="B369" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370">
-        <v>856516</v>
-      </c>
-      <c r="B370" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371">
-        <v>855518</v>
-      </c>
-      <c r="B371" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372">
-        <v>856793</v>
-      </c>
-      <c r="B372" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373">
-        <v>856698</v>
-      </c>
-      <c r="B373" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374">
-        <v>856656</v>
-      </c>
-      <c r="B374" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375">
-        <v>856087</v>
-      </c>
-      <c r="B375" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376">
-        <v>856428</v>
-      </c>
-      <c r="B376" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
